--- a/data/workbooks/2015.xlsx
+++ b/data/workbooks/2015.xlsx
@@ -3,23 +3,23 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24332"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BA5401C-7F92-412C-9825-8BD0A1B91902}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2944409B-3544-42F2-ACF5-E7D628A42B6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" firstSheet="7" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Январь 2015" sheetId="28" r:id="rId1"/>
-    <sheet name="Февраль 2015" sheetId="30" r:id="rId2"/>
-    <sheet name="Март 2015" sheetId="31" r:id="rId3"/>
-    <sheet name="Апрель 2015" sheetId="32" r:id="rId4"/>
-    <sheet name="Май 2015" sheetId="33" r:id="rId5"/>
-    <sheet name="Июнь 2015" sheetId="34" r:id="rId6"/>
-    <sheet name="Июль 2015" sheetId="35" r:id="rId7"/>
-    <sheet name="Август 2015" sheetId="36" r:id="rId8"/>
-    <sheet name="Сентябрь 2015" sheetId="37" r:id="rId9"/>
-    <sheet name="Октябрь 2015" sheetId="38" r:id="rId10"/>
-    <sheet name="Ноябрь 2015" sheetId="39" r:id="rId11"/>
-    <sheet name="Декабрь 2015" sheetId="40" r:id="rId12"/>
+    <sheet name="Січень 2015" sheetId="28" r:id="rId1"/>
+    <sheet name="Лютий 2015" sheetId="30" r:id="rId2"/>
+    <sheet name="Березень 2015" sheetId="31" r:id="rId3"/>
+    <sheet name="Квітень 2015" sheetId="32" r:id="rId4"/>
+    <sheet name="Травень 2015" sheetId="33" r:id="rId5"/>
+    <sheet name="Червень 2015" sheetId="34" r:id="rId6"/>
+    <sheet name="Липень 2015" sheetId="35" r:id="rId7"/>
+    <sheet name="Серпень 2015" sheetId="36" r:id="rId8"/>
+    <sheet name="Вересень 2015" sheetId="37" r:id="rId9"/>
+    <sheet name="Жовтень 2015" sheetId="38" r:id="rId10"/>
+    <sheet name="Листопад 2015" sheetId="39" r:id="rId11"/>
+    <sheet name="Грудень 2015" sheetId="40" r:id="rId12"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,42 +37,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="668" uniqueCount="31">
-  <si>
-    <t>Доходы</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="668" uniqueCount="32">
   <si>
     <t>Зарплата</t>
-  </si>
-  <si>
-    <t>Расходы</t>
-  </si>
-  <si>
-    <t>Потребности</t>
-  </si>
-  <si>
-    <t>Развлечения</t>
   </si>
   <si>
     <t>Квартира</t>
   </si>
   <si>
-    <t>Проезд</t>
-  </si>
-  <si>
-    <t>Долги</t>
-  </si>
-  <si>
-    <t>Другое</t>
-  </si>
-  <si>
     <t>Алкоголь</t>
-  </si>
-  <si>
-    <t>Всего</t>
-  </si>
-  <si>
-    <t>вс</t>
   </si>
   <si>
     <t>сб</t>
@@ -93,43 +66,73 @@
     <t>пн</t>
   </si>
   <si>
-    <t>Всего за месяц</t>
-  </si>
-  <si>
     <t>%</t>
-  </si>
-  <si>
-    <t>Прибыль</t>
-  </si>
-  <si>
-    <t>Здоровье</t>
-  </si>
-  <si>
-    <t>Хоз.Товары</t>
-  </si>
-  <si>
-    <t>В среднем</t>
-  </si>
-  <si>
-    <t>Питание</t>
-  </si>
-  <si>
-    <t>Другие доходы</t>
-  </si>
-  <si>
-    <t>Баланс на нач. мес.</t>
-  </si>
-  <si>
-    <t>Баланс на кон. мес.</t>
-  </si>
-  <si>
-    <t>Мероприятия</t>
   </si>
   <si>
     <t xml:space="preserve"> </t>
   </si>
   <si>
-    <t>Закуски</t>
+    <t>Доходи</t>
+  </si>
+  <si>
+    <t>Інші доходи</t>
+  </si>
+  <si>
+    <t>Витрати</t>
+  </si>
+  <si>
+    <t>Потреби</t>
+  </si>
+  <si>
+    <t>Харчування</t>
+  </si>
+  <si>
+    <t>Проїзд</t>
+  </si>
+  <si>
+    <t>Здоров'я</t>
+  </si>
+  <si>
+    <t>Госп.Товари</t>
+  </si>
+  <si>
+    <t>Борги</t>
+  </si>
+  <si>
+    <t>Інші витрати</t>
+  </si>
+  <si>
+    <t>Необов'язкове</t>
+  </si>
+  <si>
+    <t>Заходи</t>
+  </si>
+  <si>
+    <t>Розваги</t>
+  </si>
+  <si>
+    <t>Всього</t>
+  </si>
+  <si>
+    <t>Баланс на поч. міс.</t>
+  </si>
+  <si>
+    <t>Прибуток</t>
+  </si>
+  <si>
+    <t>Баланс на кін. міс.</t>
+  </si>
+  <si>
+    <t>В середньому</t>
+  </si>
+  <si>
+    <t>Всього за місяць</t>
+  </si>
+  <si>
+    <t>нд</t>
+  </si>
+  <si>
+    <t>Смаколики</t>
   </si>
 </sst>
 </file>
@@ -449,7 +452,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="121">
+  <cellXfs count="124">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -666,47 +669,44 @@
     <xf numFmtId="0" fontId="2" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="90"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -750,44 +750,56 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1140,123 +1152,123 @@
     <col min="2" max="2" width="6.140625" style="1" customWidth="1"/>
     <col min="3" max="3" width="19.28515625" style="1" customWidth="1"/>
     <col min="4" max="34" width="5.7109375" style="1" customWidth="1"/>
-    <col min="35" max="35" width="8.85546875" style="1" customWidth="1"/>
+    <col min="35" max="35" width="11.28515625" style="1" customWidth="1"/>
     <col min="36" max="36" width="10.140625" style="1" customWidth="1"/>
     <col min="37" max="37" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="83"/>
-      <c r="B1" s="83"/>
-      <c r="C1" s="84"/>
+      <c r="A1" s="110"/>
+      <c r="B1" s="110"/>
+      <c r="C1" s="111"/>
       <c r="D1" s="36" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E1" s="36" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="F1" s="36" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="G1" s="37" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="H1" s="55" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="I1" s="36" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="J1" s="37" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="K1" s="36" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="L1" s="36" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="M1" s="36" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="N1" s="37" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="O1" s="55" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="P1" s="36" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="Q1" s="37" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="R1" s="36" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="S1" s="36" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="T1" s="36" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="U1" s="37" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="V1" s="55" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="W1" s="36" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="X1" s="37" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="Y1" s="36" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="Z1" s="36" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="AA1" s="36" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="AB1" s="37" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="AC1" s="55" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="AD1" s="36" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="AE1" s="37" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="AF1" s="36" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="AG1" s="36" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="AH1" s="36" t="s">
-        <v>12</v>
-      </c>
-      <c r="AI1" s="94" t="s">
-        <v>23</v>
-      </c>
-      <c r="AJ1" s="96" t="s">
-        <v>18</v>
-      </c>
-      <c r="AK1" s="98" t="s">
-        <v>19</v>
+        <v>3</v>
+      </c>
+      <c r="AI1" s="93" t="s">
+        <v>28</v>
+      </c>
+      <c r="AJ1" s="95" t="s">
+        <v>29</v>
+      </c>
+      <c r="AK1" s="97" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="85"/>
-      <c r="B2" s="85"/>
-      <c r="C2" s="86"/>
+      <c r="A2" s="112"/>
+      <c r="B2" s="112"/>
+      <c r="C2" s="113"/>
       <c r="D2" s="11">
         <v>1</v>
       </c>
@@ -1350,17 +1362,17 @@
       <c r="AH2" s="12">
         <v>31</v>
       </c>
-      <c r="AI2" s="95"/>
-      <c r="AJ2" s="97"/>
-      <c r="AK2" s="99"/>
+      <c r="AI2" s="94"/>
+      <c r="AJ2" s="96"/>
+      <c r="AK2" s="98"/>
     </row>
     <row r="3" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="100" t="s">
+      <c r="A3" s="99" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="100"/>
+      <c r="C3" s="57" t="s">
         <v>0</v>
-      </c>
-      <c r="B3" s="101"/>
-      <c r="C3" s="57" t="s">
-        <v>1</v>
       </c>
       <c r="D3" s="14"/>
       <c r="E3" s="15"/>
@@ -1397,7 +1409,7 @@
       <c r="AF3" s="15"/>
       <c r="AG3" s="17"/>
       <c r="AH3" s="15"/>
-      <c r="AI3" s="104">
+      <c r="AI3" s="103">
         <f>(AJ3+AJ4)/31</f>
         <v>43.70967741935484</v>
       </c>
@@ -1405,15 +1417,15 @@
         <f>SUM(D3:AH3)</f>
         <v>1225</v>
       </c>
-      <c r="AK3" s="106">
+      <c r="AK3" s="105">
         <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="102"/>
-      <c r="B4" s="103"/>
+      <c r="A4" s="101"/>
+      <c r="B4" s="102"/>
       <c r="C4" s="58" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="D4" s="18"/>
       <c r="E4" s="18"/>
@@ -1452,22 +1464,22 @@
       </c>
       <c r="AG4" s="19"/>
       <c r="AH4" s="18"/>
-      <c r="AI4" s="105"/>
+      <c r="AI4" s="104"/>
       <c r="AJ4" s="48">
         <f>SUM(D4:AH4)</f>
         <v>130</v>
       </c>
-      <c r="AK4" s="107"/>
+      <c r="AK4" s="106"/>
     </row>
     <row r="5" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="87" t="s">
-        <v>2</v>
-      </c>
-      <c r="B5" s="90" t="s">
-        <v>3</v>
+      <c r="A5" s="114" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="117" t="s">
+        <v>14</v>
       </c>
       <c r="C5" s="59" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="D5" s="21"/>
       <c r="E5" s="2"/>
@@ -1530,10 +1542,10 @@
       </c>
     </row>
     <row r="6" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="88"/>
-      <c r="B6" s="90"/>
+      <c r="A6" s="115"/>
+      <c r="B6" s="117"/>
       <c r="C6" s="60" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="4">
@@ -1604,10 +1616,10 @@
       </c>
     </row>
     <row r="7" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="88"/>
-      <c r="B7" s="90"/>
+      <c r="A7" s="115"/>
+      <c r="B7" s="117"/>
       <c r="C7" s="60" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D7" s="25"/>
       <c r="E7" s="4">
@@ -1656,10 +1668,10 @@
       </c>
     </row>
     <row r="8" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="88"/>
-      <c r="B8" s="90"/>
+      <c r="A8" s="115"/>
+      <c r="B8" s="117"/>
       <c r="C8" s="61" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D8" s="38"/>
       <c r="E8" s="39"/>
@@ -1708,10 +1720,10 @@
       </c>
     </row>
     <row r="9" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="88"/>
-      <c r="B9" s="90"/>
+      <c r="A9" s="115"/>
+      <c r="B9" s="117"/>
       <c r="C9" s="59" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D9" s="21"/>
       <c r="E9" s="2">
@@ -1762,10 +1774,10 @@
       </c>
     </row>
     <row r="10" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="88"/>
-      <c r="B10" s="90"/>
+      <c r="A10" s="115"/>
+      <c r="B10" s="117"/>
       <c r="C10" s="60" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="4"/>
@@ -1812,10 +1824,10 @@
       </c>
     </row>
     <row r="11" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="88"/>
-      <c r="B11" s="90"/>
+      <c r="A11" s="115"/>
+      <c r="B11" s="117"/>
       <c r="C11" s="60" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="D11" s="21"/>
       <c r="E11" s="2"/>
@@ -1870,12 +1882,12 @@
       </c>
     </row>
     <row r="12" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="88"/>
-      <c r="B12" s="91" t="s">
-        <v>4</v>
+      <c r="A12" s="115"/>
+      <c r="B12" s="118" t="s">
+        <v>21</v>
       </c>
       <c r="C12" s="62" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D12" s="6"/>
       <c r="E12" s="6"/>
@@ -1940,10 +1952,10 @@
       </c>
     </row>
     <row r="13" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="88"/>
-      <c r="B13" s="92"/>
+      <c r="A13" s="115"/>
+      <c r="B13" s="119"/>
       <c r="C13" s="62" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D13" s="28"/>
       <c r="E13" s="8"/>
@@ -1990,10 +2002,10 @@
       </c>
     </row>
     <row r="14" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="88"/>
-      <c r="B14" s="92"/>
+      <c r="A14" s="115"/>
+      <c r="B14" s="119"/>
       <c r="C14" s="56" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D14" s="6"/>
       <c r="E14" s="6">
@@ -2046,10 +2058,10 @@
       </c>
     </row>
     <row r="15" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="88"/>
-      <c r="B15" s="93"/>
+      <c r="A15" s="115"/>
+      <c r="B15" s="120"/>
       <c r="C15" s="62" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="D15" s="51"/>
       <c r="E15" s="51"/>
@@ -2104,57 +2116,57 @@
       </c>
     </row>
     <row r="16" spans="1:37" ht="18.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="89"/>
-      <c r="B16" s="80" t="s">
-        <v>10</v>
-      </c>
-      <c r="C16" s="81"/>
-      <c r="D16" s="80">
+      <c r="A16" s="116"/>
+      <c r="B16" s="107" t="s">
+        <v>24</v>
+      </c>
+      <c r="C16" s="108"/>
+      <c r="D16" s="107">
         <f>SUM(D5:G15)</f>
         <v>257</v>
       </c>
-      <c r="E16" s="81"/>
-      <c r="F16" s="81"/>
-      <c r="G16" s="82"/>
-      <c r="H16" s="80">
+      <c r="E16" s="108"/>
+      <c r="F16" s="108"/>
+      <c r="G16" s="109"/>
+      <c r="H16" s="107">
         <f>SUM(H5:N15)</f>
         <v>81</v>
       </c>
-      <c r="I16" s="81"/>
-      <c r="J16" s="81"/>
-      <c r="K16" s="81"/>
-      <c r="L16" s="81"/>
-      <c r="M16" s="81"/>
-      <c r="N16" s="82"/>
-      <c r="O16" s="80">
+      <c r="I16" s="108"/>
+      <c r="J16" s="108"/>
+      <c r="K16" s="108"/>
+      <c r="L16" s="108"/>
+      <c r="M16" s="108"/>
+      <c r="N16" s="109"/>
+      <c r="O16" s="107">
         <f>SUM(O5:U15)</f>
         <v>273</v>
       </c>
-      <c r="P16" s="81"/>
-      <c r="Q16" s="81"/>
-      <c r="R16" s="81"/>
-      <c r="S16" s="81"/>
-      <c r="T16" s="81"/>
-      <c r="U16" s="82"/>
-      <c r="V16" s="80">
+      <c r="P16" s="108"/>
+      <c r="Q16" s="108"/>
+      <c r="R16" s="108"/>
+      <c r="S16" s="108"/>
+      <c r="T16" s="108"/>
+      <c r="U16" s="109"/>
+      <c r="V16" s="107">
         <f>SUM(V5:AB15)</f>
         <v>882</v>
       </c>
-      <c r="W16" s="81"/>
-      <c r="X16" s="81"/>
-      <c r="Y16" s="81"/>
-      <c r="Z16" s="81"/>
-      <c r="AA16" s="81"/>
-      <c r="AB16" s="82"/>
-      <c r="AC16" s="80">
+      <c r="W16" s="108"/>
+      <c r="X16" s="108"/>
+      <c r="Y16" s="108"/>
+      <c r="Z16" s="108"/>
+      <c r="AA16" s="108"/>
+      <c r="AB16" s="109"/>
+      <c r="AC16" s="107">
         <f>SUM(AC5:AH15)</f>
         <v>280</v>
       </c>
-      <c r="AD16" s="81"/>
-      <c r="AE16" s="81"/>
-      <c r="AF16" s="81"/>
-      <c r="AG16" s="81"/>
-      <c r="AH16" s="82"/>
+      <c r="AD16" s="108"/>
+      <c r="AE16" s="108"/>
+      <c r="AF16" s="108"/>
+      <c r="AG16" s="108"/>
+      <c r="AH16" s="109"/>
       <c r="AI16" s="53">
         <f t="shared" si="0"/>
         <v>57.193548387096776</v>
@@ -2169,158 +2181,146 @@
       </c>
     </row>
     <row r="17" spans="1:37" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="114" t="s">
+      <c r="A17" s="86" t="s">
+        <v>25</v>
+      </c>
+      <c r="B17" s="86"/>
+      <c r="C17" s="87"/>
+      <c r="D17" s="88">
+        <v>2113</v>
+      </c>
+      <c r="E17" s="89"/>
+      <c r="F17" s="89"/>
+      <c r="G17" s="89"/>
+      <c r="H17" s="89"/>
+      <c r="I17" s="89"/>
+      <c r="J17" s="89"/>
+      <c r="K17" s="89"/>
+      <c r="L17" s="89"/>
+      <c r="M17" s="89"/>
+      <c r="N17" s="89"/>
+      <c r="O17" s="89"/>
+      <c r="P17" s="89"/>
+      <c r="Q17" s="89"/>
+      <c r="R17" s="89"/>
+      <c r="S17" s="89"/>
+      <c r="T17" s="89"/>
+      <c r="U17" s="89"/>
+      <c r="V17" s="89"/>
+      <c r="W17" s="89"/>
+      <c r="X17" s="89"/>
+      <c r="Y17" s="89"/>
+      <c r="Z17" s="89"/>
+      <c r="AA17" s="89"/>
+      <c r="AB17" s="89"/>
+      <c r="AC17" s="89"/>
+      <c r="AD17" s="89"/>
+      <c r="AE17" s="89"/>
+      <c r="AF17" s="89"/>
+      <c r="AG17" s="89"/>
+      <c r="AH17" s="89"/>
+      <c r="AI17" s="90"/>
+      <c r="AJ17" s="91"/>
+      <c r="AK17" s="63"/>
+    </row>
+    <row r="18" spans="1:37" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="81" t="s">
         <v>26</v>
       </c>
-      <c r="B17" s="114"/>
-      <c r="C17" s="115"/>
-      <c r="D17" s="116">
-        <v>2113</v>
-      </c>
-      <c r="E17" s="117"/>
-      <c r="F17" s="117"/>
-      <c r="G17" s="117"/>
-      <c r="H17" s="117"/>
-      <c r="I17" s="117"/>
-      <c r="J17" s="117"/>
-      <c r="K17" s="117"/>
-      <c r="L17" s="117"/>
-      <c r="M17" s="117"/>
-      <c r="N17" s="117"/>
-      <c r="O17" s="117"/>
-      <c r="P17" s="117"/>
-      <c r="Q17" s="117"/>
-      <c r="R17" s="117"/>
-      <c r="S17" s="117"/>
-      <c r="T17" s="117"/>
-      <c r="U17" s="117"/>
-      <c r="V17" s="117"/>
-      <c r="W17" s="117"/>
-      <c r="X17" s="117"/>
-      <c r="Y17" s="117"/>
-      <c r="Z17" s="117"/>
-      <c r="AA17" s="117"/>
-      <c r="AB17" s="117"/>
-      <c r="AC17" s="117"/>
-      <c r="AD17" s="117"/>
-      <c r="AE17" s="117"/>
-      <c r="AF17" s="117"/>
-      <c r="AG17" s="117"/>
-      <c r="AH17" s="117"/>
-      <c r="AI17" s="118"/>
-      <c r="AJ17" s="119"/>
-      <c r="AK17" s="63"/>
-    </row>
-    <row r="18" spans="1:37" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="109" t="s">
-        <v>20</v>
-      </c>
-      <c r="B18" s="109"/>
-      <c r="C18" s="110"/>
-      <c r="D18" s="120">
+      <c r="B18" s="81"/>
+      <c r="C18" s="82"/>
+      <c r="D18" s="92">
         <f>((AJ3+AJ4+D17)-AJ16)-D17</f>
         <v>-418</v>
       </c>
-      <c r="E18" s="118"/>
-      <c r="F18" s="118"/>
-      <c r="G18" s="118"/>
-      <c r="H18" s="118"/>
-      <c r="I18" s="118"/>
-      <c r="J18" s="118"/>
-      <c r="K18" s="118"/>
-      <c r="L18" s="118"/>
-      <c r="M18" s="118"/>
-      <c r="N18" s="118"/>
-      <c r="O18" s="118"/>
-      <c r="P18" s="118"/>
-      <c r="Q18" s="118"/>
-      <c r="R18" s="118"/>
-      <c r="S18" s="118"/>
-      <c r="T18" s="118"/>
-      <c r="U18" s="118"/>
-      <c r="V18" s="118"/>
-      <c r="W18" s="118"/>
-      <c r="X18" s="118"/>
-      <c r="Y18" s="118"/>
-      <c r="Z18" s="118"/>
-      <c r="AA18" s="118"/>
-      <c r="AB18" s="118"/>
-      <c r="AC18" s="118"/>
-      <c r="AD18" s="118"/>
-      <c r="AE18" s="118"/>
-      <c r="AF18" s="118"/>
-      <c r="AG18" s="118"/>
-      <c r="AH18" s="118"/>
-      <c r="AI18" s="118"/>
-      <c r="AJ18" s="119"/>
+      <c r="E18" s="90"/>
+      <c r="F18" s="90"/>
+      <c r="G18" s="90"/>
+      <c r="H18" s="90"/>
+      <c r="I18" s="90"/>
+      <c r="J18" s="90"/>
+      <c r="K18" s="90"/>
+      <c r="L18" s="90"/>
+      <c r="M18" s="90"/>
+      <c r="N18" s="90"/>
+      <c r="O18" s="90"/>
+      <c r="P18" s="90"/>
+      <c r="Q18" s="90"/>
+      <c r="R18" s="90"/>
+      <c r="S18" s="90"/>
+      <c r="T18" s="90"/>
+      <c r="U18" s="90"/>
+      <c r="V18" s="90"/>
+      <c r="W18" s="90"/>
+      <c r="X18" s="90"/>
+      <c r="Y18" s="90"/>
+      <c r="Z18" s="90"/>
+      <c r="AA18" s="90"/>
+      <c r="AB18" s="90"/>
+      <c r="AC18" s="90"/>
+      <c r="AD18" s="90"/>
+      <c r="AE18" s="90"/>
+      <c r="AF18" s="90"/>
+      <c r="AG18" s="90"/>
+      <c r="AH18" s="90"/>
+      <c r="AI18" s="90"/>
+      <c r="AJ18" s="91"/>
       <c r="AK18" s="31">
         <f>((AJ3+AJ4-AJ16)/(AJ3+AJ4))*100</f>
         <v>-30.84870848708487</v>
       </c>
     </row>
     <row r="19" spans="1:37" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="108" t="s">
+      <c r="A19" s="80" t="s">
         <v>27</v>
       </c>
-      <c r="B19" s="109"/>
-      <c r="C19" s="110"/>
-      <c r="D19" s="111">
+      <c r="B19" s="81"/>
+      <c r="C19" s="82"/>
+      <c r="D19" s="83">
         <f>(AJ3+AJ4+D17)-AJ16</f>
         <v>1695</v>
       </c>
-      <c r="E19" s="112"/>
-      <c r="F19" s="112"/>
-      <c r="G19" s="112"/>
-      <c r="H19" s="112"/>
-      <c r="I19" s="112"/>
-      <c r="J19" s="112"/>
-      <c r="K19" s="112"/>
-      <c r="L19" s="112"/>
-      <c r="M19" s="112"/>
-      <c r="N19" s="112"/>
-      <c r="O19" s="112"/>
-      <c r="P19" s="112"/>
-      <c r="Q19" s="112"/>
-      <c r="R19" s="112"/>
-      <c r="S19" s="112"/>
-      <c r="T19" s="112"/>
-      <c r="U19" s="112"/>
-      <c r="V19" s="112"/>
-      <c r="W19" s="112"/>
-      <c r="X19" s="112"/>
-      <c r="Y19" s="112"/>
-      <c r="Z19" s="112"/>
-      <c r="AA19" s="112"/>
-      <c r="AB19" s="112"/>
-      <c r="AC19" s="112"/>
-      <c r="AD19" s="112"/>
-      <c r="AE19" s="112"/>
-      <c r="AF19" s="112"/>
-      <c r="AG19" s="112"/>
-      <c r="AH19" s="112"/>
-      <c r="AI19" s="112"/>
-      <c r="AJ19" s="113"/>
+      <c r="E19" s="84"/>
+      <c r="F19" s="84"/>
+      <c r="G19" s="84"/>
+      <c r="H19" s="84"/>
+      <c r="I19" s="84"/>
+      <c r="J19" s="84"/>
+      <c r="K19" s="84"/>
+      <c r="L19" s="84"/>
+      <c r="M19" s="84"/>
+      <c r="N19" s="84"/>
+      <c r="O19" s="84"/>
+      <c r="P19" s="84"/>
+      <c r="Q19" s="84"/>
+      <c r="R19" s="84"/>
+      <c r="S19" s="84"/>
+      <c r="T19" s="84"/>
+      <c r="U19" s="84"/>
+      <c r="V19" s="84"/>
+      <c r="W19" s="84"/>
+      <c r="X19" s="84"/>
+      <c r="Y19" s="84"/>
+      <c r="Z19" s="84"/>
+      <c r="AA19" s="84"/>
+      <c r="AB19" s="84"/>
+      <c r="AC19" s="84"/>
+      <c r="AD19" s="84"/>
+      <c r="AE19" s="84"/>
+      <c r="AF19" s="84"/>
+      <c r="AG19" s="84"/>
+      <c r="AH19" s="84"/>
+      <c r="AI19" s="84"/>
+      <c r="AJ19" s="85"/>
       <c r="AK19" s="54"/>
     </row>
     <row r="24" spans="1:37" x14ac:dyDescent="0.3">
       <c r="S24" s="1" t="s">
-        <v>29</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="D19:AJ19"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="D17:AJ17"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="D18:AJ18"/>
-    <mergeCell ref="AI1:AI2"/>
-    <mergeCell ref="AJ1:AJ2"/>
-    <mergeCell ref="AK1:AK2"/>
-    <mergeCell ref="A3:B4"/>
-    <mergeCell ref="AI3:AI4"/>
-    <mergeCell ref="AK3:AK4"/>
     <mergeCell ref="H16:N16"/>
     <mergeCell ref="O16:U16"/>
     <mergeCell ref="V16:AB16"/>
@@ -2331,6 +2331,18 @@
     <mergeCell ref="B12:B15"/>
     <mergeCell ref="B16:C16"/>
     <mergeCell ref="D16:G16"/>
+    <mergeCell ref="AI1:AI2"/>
+    <mergeCell ref="AJ1:AJ2"/>
+    <mergeCell ref="AK1:AK2"/>
+    <mergeCell ref="A3:B4"/>
+    <mergeCell ref="AI3:AI4"/>
+    <mergeCell ref="AK3:AK4"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="D19:AJ19"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="D17:AJ17"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="D18:AJ18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2346,123 +2358,123 @@
     <col min="2" max="2" width="6.140625" style="1" customWidth="1"/>
     <col min="3" max="3" width="19.28515625" style="1" customWidth="1"/>
     <col min="4" max="34" width="5.7109375" style="1" customWidth="1"/>
-    <col min="35" max="35" width="8.85546875" style="1" customWidth="1"/>
+    <col min="35" max="35" width="11.85546875" style="1" customWidth="1"/>
     <col min="36" max="36" width="10.140625" style="1" customWidth="1"/>
     <col min="37" max="37" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="83"/>
-      <c r="B1" s="83"/>
-      <c r="C1" s="84"/>
+      <c r="A1" s="110"/>
+      <c r="B1" s="110"/>
+      <c r="C1" s="111"/>
       <c r="D1" s="36" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E1" s="36" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="F1" s="36" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="G1" s="37" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="H1" s="55" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="I1" s="36" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="J1" s="37" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="K1" s="36" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="L1" s="36" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="M1" s="36" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="N1" s="37" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="O1" s="55" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="P1" s="36" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="Q1" s="37" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="R1" s="36" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="S1" s="36" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="T1" s="36" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="U1" s="37" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="V1" s="55" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="W1" s="36" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="X1" s="37" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="Y1" s="36" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="Z1" s="36" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="AA1" s="36" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="AB1" s="37" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="AC1" s="55" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="AD1" s="36" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="AE1" s="37" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="AF1" s="36" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="AG1" s="36" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="AH1" s="36" t="s">
-        <v>12</v>
-      </c>
-      <c r="AI1" s="94" t="s">
-        <v>23</v>
-      </c>
-      <c r="AJ1" s="96" t="s">
-        <v>18</v>
-      </c>
-      <c r="AK1" s="98" t="s">
-        <v>19</v>
+        <v>3</v>
+      </c>
+      <c r="AI1" s="93" t="s">
+        <v>28</v>
+      </c>
+      <c r="AJ1" s="95" t="s">
+        <v>29</v>
+      </c>
+      <c r="AK1" s="97" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="85"/>
-      <c r="B2" s="85"/>
-      <c r="C2" s="86"/>
+      <c r="A2" s="112"/>
+      <c r="B2" s="112"/>
+      <c r="C2" s="113"/>
       <c r="D2" s="11">
         <v>1</v>
       </c>
@@ -2556,17 +2568,17 @@
       <c r="AH2" s="12">
         <v>31</v>
       </c>
-      <c r="AI2" s="95"/>
-      <c r="AJ2" s="97"/>
-      <c r="AK2" s="99"/>
+      <c r="AI2" s="94"/>
+      <c r="AJ2" s="96"/>
+      <c r="AK2" s="98"/>
     </row>
     <row r="3" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="100" t="s">
+      <c r="A3" s="99" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="100"/>
+      <c r="C3" s="57" t="s">
         <v>0</v>
-      </c>
-      <c r="B3" s="101"/>
-      <c r="C3" s="57" t="s">
-        <v>1</v>
       </c>
       <c r="D3" s="14"/>
       <c r="E3" s="15"/>
@@ -2607,7 +2619,7 @@
       <c r="AF3" s="15"/>
       <c r="AG3" s="17"/>
       <c r="AH3" s="15"/>
-      <c r="AI3" s="104">
+      <c r="AI3" s="103">
         <f>(AJ3+AJ4)/31</f>
         <v>94.935483870967744</v>
       </c>
@@ -2615,15 +2627,15 @@
         <f>SUM(D3:AH3)</f>
         <v>2781</v>
       </c>
-      <c r="AK3" s="106">
+      <c r="AK3" s="105">
         <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="102"/>
-      <c r="B4" s="103"/>
+      <c r="A4" s="101"/>
+      <c r="B4" s="102"/>
       <c r="C4" s="58" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="D4" s="18"/>
       <c r="E4" s="18">
@@ -2674,22 +2686,22 @@
       <c r="AH4" s="18">
         <v>16</v>
       </c>
-      <c r="AI4" s="105"/>
+      <c r="AI4" s="104"/>
       <c r="AJ4" s="48">
         <f>SUM(D4:AH4)</f>
         <v>162</v>
       </c>
-      <c r="AK4" s="107"/>
+      <c r="AK4" s="106"/>
     </row>
     <row r="5" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="87" t="s">
-        <v>2</v>
-      </c>
-      <c r="B5" s="90" t="s">
-        <v>3</v>
+      <c r="A5" s="114" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="117" t="s">
+        <v>14</v>
       </c>
       <c r="C5" s="59" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="D5" s="21">
         <v>3</v>
@@ -2758,10 +2770,10 @@
       </c>
     </row>
     <row r="6" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="88"/>
-      <c r="B6" s="90"/>
+      <c r="A6" s="115"/>
+      <c r="B6" s="117"/>
       <c r="C6" s="60" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D6" s="4">
         <v>13</v>
@@ -2852,10 +2864,10 @@
       </c>
     </row>
     <row r="7" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="88"/>
-      <c r="B7" s="90"/>
+      <c r="A7" s="115"/>
+      <c r="B7" s="117"/>
       <c r="C7" s="60" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D7" s="25"/>
       <c r="E7" s="4"/>
@@ -2904,10 +2916,10 @@
       </c>
     </row>
     <row r="8" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="88"/>
-      <c r="B8" s="90"/>
+      <c r="A8" s="115"/>
+      <c r="B8" s="117"/>
       <c r="C8" s="61" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D8" s="38"/>
       <c r="E8" s="39"/>
@@ -2958,10 +2970,10 @@
       </c>
     </row>
     <row r="9" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="88"/>
-      <c r="B9" s="90"/>
+      <c r="A9" s="115"/>
+      <c r="B9" s="117"/>
       <c r="C9" s="59" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D9" s="21"/>
       <c r="E9" s="2"/>
@@ -3014,10 +3026,10 @@
       </c>
     </row>
     <row r="10" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="88"/>
-      <c r="B10" s="90"/>
+      <c r="A10" s="115"/>
+      <c r="B10" s="117"/>
       <c r="C10" s="60" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="4"/>
@@ -3064,10 +3076,10 @@
       </c>
     </row>
     <row r="11" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="88"/>
-      <c r="B11" s="90"/>
+      <c r="A11" s="115"/>
+      <c r="B11" s="117"/>
       <c r="C11" s="60" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="D11" s="21"/>
       <c r="E11" s="2"/>
@@ -3120,12 +3132,12 @@
       </c>
     </row>
     <row r="12" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="88"/>
-      <c r="B12" s="91" t="s">
-        <v>4</v>
+      <c r="A12" s="115"/>
+      <c r="B12" s="121" t="s">
+        <v>21</v>
       </c>
       <c r="C12" s="62" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D12" s="6"/>
       <c r="E12" s="6">
@@ -3190,10 +3202,10 @@
       </c>
     </row>
     <row r="13" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="88"/>
-      <c r="B13" s="92"/>
+      <c r="A13" s="115"/>
+      <c r="B13" s="122"/>
       <c r="C13" s="62" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D13" s="28"/>
       <c r="E13" s="8"/>
@@ -3244,10 +3256,10 @@
       </c>
     </row>
     <row r="14" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="88"/>
-      <c r="B14" s="92"/>
+      <c r="A14" s="115"/>
+      <c r="B14" s="122"/>
       <c r="C14" s="56" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D14" s="6"/>
       <c r="E14" s="6"/>
@@ -3296,10 +3308,10 @@
       </c>
     </row>
     <row r="15" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="88"/>
-      <c r="B15" s="93"/>
+      <c r="A15" s="115"/>
+      <c r="B15" s="123"/>
       <c r="C15" s="62" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="D15" s="51"/>
       <c r="E15" s="51">
@@ -3356,57 +3368,57 @@
       </c>
     </row>
     <row r="16" spans="1:37" ht="18.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="89"/>
-      <c r="B16" s="80" t="s">
-        <v>10</v>
-      </c>
-      <c r="C16" s="81"/>
-      <c r="D16" s="80">
+      <c r="A16" s="116"/>
+      <c r="B16" s="107" t="s">
+        <v>24</v>
+      </c>
+      <c r="C16" s="108"/>
+      <c r="D16" s="107">
         <f>SUM(D5:G15)+387</f>
         <v>658</v>
       </c>
-      <c r="E16" s="81"/>
-      <c r="F16" s="81"/>
-      <c r="G16" s="82"/>
-      <c r="H16" s="80">
+      <c r="E16" s="108"/>
+      <c r="F16" s="108"/>
+      <c r="G16" s="109"/>
+      <c r="H16" s="107">
         <f>SUM(H5:N15)</f>
         <v>474</v>
       </c>
-      <c r="I16" s="81"/>
-      <c r="J16" s="81"/>
-      <c r="K16" s="81"/>
-      <c r="L16" s="81"/>
-      <c r="M16" s="81"/>
-      <c r="N16" s="82"/>
-      <c r="O16" s="80">
+      <c r="I16" s="108"/>
+      <c r="J16" s="108"/>
+      <c r="K16" s="108"/>
+      <c r="L16" s="108"/>
+      <c r="M16" s="108"/>
+      <c r="N16" s="109"/>
+      <c r="O16" s="107">
         <f>SUM(O5:U15)</f>
         <v>587</v>
       </c>
-      <c r="P16" s="81"/>
-      <c r="Q16" s="81"/>
-      <c r="R16" s="81"/>
-      <c r="S16" s="81"/>
-      <c r="T16" s="81"/>
-      <c r="U16" s="82"/>
-      <c r="V16" s="80">
+      <c r="P16" s="108"/>
+      <c r="Q16" s="108"/>
+      <c r="R16" s="108"/>
+      <c r="S16" s="108"/>
+      <c r="T16" s="108"/>
+      <c r="U16" s="109"/>
+      <c r="V16" s="107">
         <f>SUM(V5:AB15)</f>
         <v>215</v>
       </c>
-      <c r="W16" s="81"/>
-      <c r="X16" s="81"/>
-      <c r="Y16" s="81"/>
-      <c r="Z16" s="81"/>
-      <c r="AA16" s="81"/>
-      <c r="AB16" s="82"/>
-      <c r="AC16" s="80">
+      <c r="W16" s="108"/>
+      <c r="X16" s="108"/>
+      <c r="Y16" s="108"/>
+      <c r="Z16" s="108"/>
+      <c r="AA16" s="108"/>
+      <c r="AB16" s="109"/>
+      <c r="AC16" s="107">
         <f>SUM(AC5:AH15)</f>
         <v>235</v>
       </c>
-      <c r="AD16" s="81"/>
-      <c r="AE16" s="81"/>
-      <c r="AF16" s="81"/>
-      <c r="AG16" s="81"/>
-      <c r="AH16" s="82"/>
+      <c r="AD16" s="108"/>
+      <c r="AE16" s="108"/>
+      <c r="AF16" s="108"/>
+      <c r="AG16" s="108"/>
+      <c r="AH16" s="109"/>
       <c r="AI16" s="53">
         <f t="shared" si="0"/>
         <v>57.483870967741936</v>
@@ -3421,146 +3433,153 @@
       </c>
     </row>
     <row r="17" spans="1:37" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="114" t="s">
+      <c r="A17" s="86" t="s">
+        <v>25</v>
+      </c>
+      <c r="B17" s="86"/>
+      <c r="C17" s="87"/>
+      <c r="D17" s="88">
+        <v>3058</v>
+      </c>
+      <c r="E17" s="89"/>
+      <c r="F17" s="89"/>
+      <c r="G17" s="89"/>
+      <c r="H17" s="89"/>
+      <c r="I17" s="89"/>
+      <c r="J17" s="89"/>
+      <c r="K17" s="89"/>
+      <c r="L17" s="89"/>
+      <c r="M17" s="89"/>
+      <c r="N17" s="89"/>
+      <c r="O17" s="89"/>
+      <c r="P17" s="89"/>
+      <c r="Q17" s="89"/>
+      <c r="R17" s="89"/>
+      <c r="S17" s="89"/>
+      <c r="T17" s="89"/>
+      <c r="U17" s="89"/>
+      <c r="V17" s="89"/>
+      <c r="W17" s="89"/>
+      <c r="X17" s="89"/>
+      <c r="Y17" s="89"/>
+      <c r="Z17" s="89"/>
+      <c r="AA17" s="89"/>
+      <c r="AB17" s="89"/>
+      <c r="AC17" s="89"/>
+      <c r="AD17" s="89"/>
+      <c r="AE17" s="89"/>
+      <c r="AF17" s="89"/>
+      <c r="AG17" s="89"/>
+      <c r="AH17" s="89"/>
+      <c r="AI17" s="90"/>
+      <c r="AJ17" s="91"/>
+      <c r="AK17" s="77"/>
+    </row>
+    <row r="18" spans="1:37" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="81" t="s">
         <v>26</v>
       </c>
-      <c r="B17" s="114"/>
-      <c r="C17" s="115"/>
-      <c r="D17" s="116">
-        <v>3058</v>
-      </c>
-      <c r="E17" s="117"/>
-      <c r="F17" s="117"/>
-      <c r="G17" s="117"/>
-      <c r="H17" s="117"/>
-      <c r="I17" s="117"/>
-      <c r="J17" s="117"/>
-      <c r="K17" s="117"/>
-      <c r="L17" s="117"/>
-      <c r="M17" s="117"/>
-      <c r="N17" s="117"/>
-      <c r="O17" s="117"/>
-      <c r="P17" s="117"/>
-      <c r="Q17" s="117"/>
-      <c r="R17" s="117"/>
-      <c r="S17" s="117"/>
-      <c r="T17" s="117"/>
-      <c r="U17" s="117"/>
-      <c r="V17" s="117"/>
-      <c r="W17" s="117"/>
-      <c r="X17" s="117"/>
-      <c r="Y17" s="117"/>
-      <c r="Z17" s="117"/>
-      <c r="AA17" s="117"/>
-      <c r="AB17" s="117"/>
-      <c r="AC17" s="117"/>
-      <c r="AD17" s="117"/>
-      <c r="AE17" s="117"/>
-      <c r="AF17" s="117"/>
-      <c r="AG17" s="117"/>
-      <c r="AH17" s="117"/>
-      <c r="AI17" s="118"/>
-      <c r="AJ17" s="119"/>
-      <c r="AK17" s="77"/>
-    </row>
-    <row r="18" spans="1:37" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="109" t="s">
-        <v>20</v>
-      </c>
-      <c r="B18" s="109"/>
-      <c r="C18" s="110"/>
-      <c r="D18" s="120">
+      <c r="B18" s="81"/>
+      <c r="C18" s="82"/>
+      <c r="D18" s="92">
         <f>(AJ3+AJ4)-AJ16</f>
         <v>1161</v>
       </c>
-      <c r="E18" s="118"/>
-      <c r="F18" s="118"/>
-      <c r="G18" s="118"/>
-      <c r="H18" s="118"/>
-      <c r="I18" s="118"/>
-      <c r="J18" s="118"/>
-      <c r="K18" s="118"/>
-      <c r="L18" s="118"/>
-      <c r="M18" s="118"/>
-      <c r="N18" s="118"/>
-      <c r="O18" s="118"/>
-      <c r="P18" s="118"/>
-      <c r="Q18" s="118"/>
-      <c r="R18" s="118"/>
-      <c r="S18" s="118"/>
-      <c r="T18" s="118"/>
-      <c r="U18" s="118"/>
-      <c r="V18" s="118"/>
-      <c r="W18" s="118"/>
-      <c r="X18" s="118"/>
-      <c r="Y18" s="118"/>
-      <c r="Z18" s="118"/>
-      <c r="AA18" s="118"/>
-      <c r="AB18" s="118"/>
-      <c r="AC18" s="118"/>
-      <c r="AD18" s="118"/>
-      <c r="AE18" s="118"/>
-      <c r="AF18" s="118"/>
-      <c r="AG18" s="118"/>
-      <c r="AH18" s="118"/>
-      <c r="AI18" s="118"/>
-      <c r="AJ18" s="119"/>
+      <c r="E18" s="90"/>
+      <c r="F18" s="90"/>
+      <c r="G18" s="90"/>
+      <c r="H18" s="90"/>
+      <c r="I18" s="90"/>
+      <c r="J18" s="90"/>
+      <c r="K18" s="90"/>
+      <c r="L18" s="90"/>
+      <c r="M18" s="90"/>
+      <c r="N18" s="90"/>
+      <c r="O18" s="90"/>
+      <c r="P18" s="90"/>
+      <c r="Q18" s="90"/>
+      <c r="R18" s="90"/>
+      <c r="S18" s="90"/>
+      <c r="T18" s="90"/>
+      <c r="U18" s="90"/>
+      <c r="V18" s="90"/>
+      <c r="W18" s="90"/>
+      <c r="X18" s="90"/>
+      <c r="Y18" s="90"/>
+      <c r="Z18" s="90"/>
+      <c r="AA18" s="90"/>
+      <c r="AB18" s="90"/>
+      <c r="AC18" s="90"/>
+      <c r="AD18" s="90"/>
+      <c r="AE18" s="90"/>
+      <c r="AF18" s="90"/>
+      <c r="AG18" s="90"/>
+      <c r="AH18" s="90"/>
+      <c r="AI18" s="90"/>
+      <c r="AJ18" s="91"/>
       <c r="AK18" s="31">
         <f>((AJ3+AJ4-AJ16)/(AJ3+AJ4))*100</f>
         <v>39.449541284403672</v>
       </c>
     </row>
     <row r="19" spans="1:37" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="108" t="s">
+      <c r="A19" s="80" t="s">
         <v>27</v>
       </c>
-      <c r="B19" s="109"/>
-      <c r="C19" s="110"/>
-      <c r="D19" s="111">
+      <c r="B19" s="81"/>
+      <c r="C19" s="82"/>
+      <c r="D19" s="83">
         <f>(AJ3+AJ4+D17)-AJ16</f>
         <v>4219</v>
       </c>
-      <c r="E19" s="112"/>
-      <c r="F19" s="112"/>
-      <c r="G19" s="112"/>
-      <c r="H19" s="112"/>
-      <c r="I19" s="112"/>
-      <c r="J19" s="112"/>
-      <c r="K19" s="112"/>
-      <c r="L19" s="112"/>
-      <c r="M19" s="112"/>
-      <c r="N19" s="112"/>
-      <c r="O19" s="112"/>
-      <c r="P19" s="112"/>
-      <c r="Q19" s="112"/>
-      <c r="R19" s="112"/>
-      <c r="S19" s="112"/>
-      <c r="T19" s="112"/>
-      <c r="U19" s="112"/>
-      <c r="V19" s="112"/>
-      <c r="W19" s="112"/>
-      <c r="X19" s="112"/>
-      <c r="Y19" s="112"/>
-      <c r="Z19" s="112"/>
-      <c r="AA19" s="112"/>
-      <c r="AB19" s="112"/>
-      <c r="AC19" s="112"/>
-      <c r="AD19" s="112"/>
-      <c r="AE19" s="112"/>
-      <c r="AF19" s="112"/>
-      <c r="AG19" s="112"/>
-      <c r="AH19" s="112"/>
-      <c r="AI19" s="112"/>
-      <c r="AJ19" s="113"/>
+      <c r="E19" s="84"/>
+      <c r="F19" s="84"/>
+      <c r="G19" s="84"/>
+      <c r="H19" s="84"/>
+      <c r="I19" s="84"/>
+      <c r="J19" s="84"/>
+      <c r="K19" s="84"/>
+      <c r="L19" s="84"/>
+      <c r="M19" s="84"/>
+      <c r="N19" s="84"/>
+      <c r="O19" s="84"/>
+      <c r="P19" s="84"/>
+      <c r="Q19" s="84"/>
+      <c r="R19" s="84"/>
+      <c r="S19" s="84"/>
+      <c r="T19" s="84"/>
+      <c r="U19" s="84"/>
+      <c r="V19" s="84"/>
+      <c r="W19" s="84"/>
+      <c r="X19" s="84"/>
+      <c r="Y19" s="84"/>
+      <c r="Z19" s="84"/>
+      <c r="AA19" s="84"/>
+      <c r="AB19" s="84"/>
+      <c r="AC19" s="84"/>
+      <c r="AD19" s="84"/>
+      <c r="AE19" s="84"/>
+      <c r="AF19" s="84"/>
+      <c r="AG19" s="84"/>
+      <c r="AH19" s="84"/>
+      <c r="AI19" s="84"/>
+      <c r="AJ19" s="85"/>
       <c r="AK19" s="54"/>
     </row>
     <row r="24" spans="1:37" x14ac:dyDescent="0.3">
       <c r="S24" s="1" t="s">
-        <v>29</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="A1:C2"/>
+    <mergeCell ref="AI1:AI2"/>
+    <mergeCell ref="AJ1:AJ2"/>
+    <mergeCell ref="AK1:AK2"/>
+    <mergeCell ref="A3:B4"/>
+    <mergeCell ref="AI3:AI4"/>
+    <mergeCell ref="AK3:AK4"/>
     <mergeCell ref="A19:C19"/>
     <mergeCell ref="D19:AJ19"/>
     <mergeCell ref="D16:G16"/>
@@ -3576,13 +3595,6 @@
     <mergeCell ref="B5:B11"/>
     <mergeCell ref="B12:B15"/>
     <mergeCell ref="B16:C16"/>
-    <mergeCell ref="A1:C2"/>
-    <mergeCell ref="AI1:AI2"/>
-    <mergeCell ref="AJ1:AJ2"/>
-    <mergeCell ref="AK1:AK2"/>
-    <mergeCell ref="A3:B4"/>
-    <mergeCell ref="AI3:AI4"/>
-    <mergeCell ref="AK3:AK4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -3598,121 +3610,121 @@
     <col min="2" max="2" width="6.140625" style="1" customWidth="1"/>
     <col min="3" max="3" width="19.28515625" style="1" customWidth="1"/>
     <col min="4" max="34" width="5.7109375" style="1" customWidth="1"/>
-    <col min="35" max="35" width="8.85546875" style="1" customWidth="1"/>
+    <col min="35" max="35" width="12" style="1" customWidth="1"/>
     <col min="36" max="36" width="10.140625" style="1" customWidth="1"/>
     <col min="37" max="37" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="83"/>
-      <c r="B1" s="83"/>
-      <c r="C1" s="84"/>
+      <c r="A1" s="110"/>
+      <c r="B1" s="110"/>
+      <c r="C1" s="111"/>
       <c r="D1" s="37" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="E1" s="55" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="F1" s="36" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="G1" s="37" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="H1" s="36" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="I1" s="36" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="J1" s="36" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="K1" s="37" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="L1" s="55" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="M1" s="36" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="N1" s="37" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="O1" s="36" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="P1" s="36" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="Q1" s="36" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="R1" s="37" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="S1" s="55" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="T1" s="36" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="U1" s="37" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="V1" s="36" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="W1" s="36" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="X1" s="36" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="Y1" s="37" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="Z1" s="55" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="AA1" s="36" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="AB1" s="37" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="AC1" s="36" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="AD1" s="36" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="AE1" s="36" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="AF1" s="37" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="AG1" s="55" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="AH1" s="36"/>
-      <c r="AI1" s="94" t="s">
-        <v>23</v>
-      </c>
-      <c r="AJ1" s="96" t="s">
-        <v>18</v>
-      </c>
-      <c r="AK1" s="98" t="s">
-        <v>19</v>
+      <c r="AI1" s="93" t="s">
+        <v>28</v>
+      </c>
+      <c r="AJ1" s="95" t="s">
+        <v>29</v>
+      </c>
+      <c r="AK1" s="97" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="85"/>
-      <c r="B2" s="85"/>
-      <c r="C2" s="86"/>
+      <c r="A2" s="112"/>
+      <c r="B2" s="112"/>
+      <c r="C2" s="113"/>
       <c r="D2" s="11">
         <v>1</v>
       </c>
@@ -3806,17 +3818,17 @@
       <c r="AH2" s="12">
         <v>31</v>
       </c>
-      <c r="AI2" s="95"/>
-      <c r="AJ2" s="97"/>
-      <c r="AK2" s="99"/>
+      <c r="AI2" s="94"/>
+      <c r="AJ2" s="96"/>
+      <c r="AK2" s="98"/>
     </row>
     <row r="3" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="100" t="s">
+      <c r="A3" s="99" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="100"/>
+      <c r="C3" s="57" t="s">
         <v>0</v>
-      </c>
-      <c r="B3" s="101"/>
-      <c r="C3" s="57" t="s">
-        <v>1</v>
       </c>
       <c r="D3" s="14"/>
       <c r="E3" s="15"/>
@@ -3859,7 +3871,7 @@
         <v>507</v>
       </c>
       <c r="AH3" s="15"/>
-      <c r="AI3" s="104">
+      <c r="AI3" s="103">
         <f>(AJ3+AJ4)/31</f>
         <v>111.09677419354838</v>
       </c>
@@ -3867,15 +3879,15 @@
         <f>SUM(D3:AH3)</f>
         <v>2978</v>
       </c>
-      <c r="AK3" s="106">
+      <c r="AK3" s="105">
         <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="102"/>
-      <c r="B4" s="103"/>
+      <c r="A4" s="101"/>
+      <c r="B4" s="102"/>
       <c r="C4" s="58" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="D4" s="18">
         <v>22</v>
@@ -3918,22 +3930,22 @@
       </c>
       <c r="AG4" s="19"/>
       <c r="AH4" s="18"/>
-      <c r="AI4" s="105"/>
+      <c r="AI4" s="104"/>
       <c r="AJ4" s="48">
         <f>SUM(D4:AH4)</f>
         <v>466</v>
       </c>
-      <c r="AK4" s="107"/>
+      <c r="AK4" s="106"/>
     </row>
     <row r="5" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="87" t="s">
-        <v>2</v>
-      </c>
-      <c r="B5" s="90" t="s">
-        <v>3</v>
+      <c r="A5" s="114" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="117" t="s">
+        <v>14</v>
       </c>
       <c r="C5" s="59" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="D5" s="21"/>
       <c r="E5" s="2">
@@ -4004,10 +4016,10 @@
       </c>
     </row>
     <row r="6" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="88"/>
-      <c r="B6" s="90"/>
+      <c r="A6" s="115"/>
+      <c r="B6" s="117"/>
       <c r="C6" s="60" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D6" s="4">
         <v>25</v>
@@ -4090,10 +4102,10 @@
       </c>
     </row>
     <row r="7" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="88"/>
-      <c r="B7" s="90"/>
+      <c r="A7" s="115"/>
+      <c r="B7" s="117"/>
       <c r="C7" s="60" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D7" s="25"/>
       <c r="E7" s="4"/>
@@ -4142,10 +4154,10 @@
       </c>
     </row>
     <row r="8" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="88"/>
-      <c r="B8" s="90"/>
+      <c r="A8" s="115"/>
+      <c r="B8" s="117"/>
       <c r="C8" s="61" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D8" s="38"/>
       <c r="E8" s="39"/>
@@ -4198,10 +4210,10 @@
       </c>
     </row>
     <row r="9" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="88"/>
-      <c r="B9" s="90"/>
+      <c r="A9" s="115"/>
+      <c r="B9" s="117"/>
       <c r="C9" s="59" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D9" s="21"/>
       <c r="E9" s="2"/>
@@ -4250,10 +4262,10 @@
       </c>
     </row>
     <row r="10" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="88"/>
-      <c r="B10" s="90"/>
+      <c r="A10" s="115"/>
+      <c r="B10" s="117"/>
       <c r="C10" s="60" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="4"/>
@@ -4300,10 +4312,10 @@
       </c>
     </row>
     <row r="11" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="88"/>
-      <c r="B11" s="90"/>
+      <c r="A11" s="115"/>
+      <c r="B11" s="117"/>
       <c r="C11" s="60" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="D11" s="21"/>
       <c r="E11" s="2"/>
@@ -4356,12 +4368,12 @@
       </c>
     </row>
     <row r="12" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="88"/>
-      <c r="B12" s="91" t="s">
-        <v>4</v>
+      <c r="A12" s="115"/>
+      <c r="B12" s="121" t="s">
+        <v>21</v>
       </c>
       <c r="C12" s="62" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D12" s="6"/>
       <c r="E12" s="6"/>
@@ -4422,10 +4434,10 @@
       </c>
     </row>
     <row r="13" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="88"/>
-      <c r="B13" s="92"/>
+      <c r="A13" s="115"/>
+      <c r="B13" s="122"/>
       <c r="C13" s="62" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D13" s="28"/>
       <c r="E13" s="8"/>
@@ -4478,10 +4490,10 @@
       </c>
     </row>
     <row r="14" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="88"/>
-      <c r="B14" s="92"/>
+      <c r="A14" s="115"/>
+      <c r="B14" s="122"/>
       <c r="C14" s="56" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D14" s="6"/>
       <c r="E14" s="6"/>
@@ -4532,10 +4544,10 @@
       </c>
     </row>
     <row r="15" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="88"/>
-      <c r="B15" s="93"/>
+      <c r="A15" s="115"/>
+      <c r="B15" s="123"/>
       <c r="C15" s="62" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="D15" s="51"/>
       <c r="E15" s="51"/>
@@ -4586,52 +4598,52 @@
       </c>
     </row>
     <row r="16" spans="1:37" ht="18.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="89"/>
-      <c r="B16" s="80" t="s">
-        <v>10</v>
-      </c>
-      <c r="C16" s="81"/>
+      <c r="A16" s="116"/>
+      <c r="B16" s="107" t="s">
+        <v>24</v>
+      </c>
+      <c r="C16" s="108"/>
       <c r="D16" s="67"/>
-      <c r="E16" s="80">
+      <c r="E16" s="107">
         <f>SUM(E5:K15)</f>
         <v>256</v>
       </c>
-      <c r="F16" s="81"/>
-      <c r="G16" s="81"/>
-      <c r="H16" s="81"/>
-      <c r="I16" s="81"/>
-      <c r="J16" s="81"/>
-      <c r="K16" s="82"/>
-      <c r="L16" s="80">
+      <c r="F16" s="108"/>
+      <c r="G16" s="108"/>
+      <c r="H16" s="108"/>
+      <c r="I16" s="108"/>
+      <c r="J16" s="108"/>
+      <c r="K16" s="109"/>
+      <c r="L16" s="107">
         <f>SUM(L5:R15)</f>
         <v>260</v>
       </c>
-      <c r="M16" s="81"/>
-      <c r="N16" s="81"/>
-      <c r="O16" s="81"/>
-      <c r="P16" s="81"/>
-      <c r="Q16" s="81"/>
-      <c r="R16" s="82"/>
-      <c r="S16" s="80">
+      <c r="M16" s="108"/>
+      <c r="N16" s="108"/>
+      <c r="O16" s="108"/>
+      <c r="P16" s="108"/>
+      <c r="Q16" s="108"/>
+      <c r="R16" s="109"/>
+      <c r="S16" s="107">
         <f>SUM(S5:Y15)</f>
         <v>751</v>
       </c>
-      <c r="T16" s="81"/>
-      <c r="U16" s="81"/>
-      <c r="V16" s="81"/>
-      <c r="W16" s="81"/>
-      <c r="X16" s="81"/>
-      <c r="Y16" s="82"/>
-      <c r="Z16" s="80">
+      <c r="T16" s="108"/>
+      <c r="U16" s="108"/>
+      <c r="V16" s="108"/>
+      <c r="W16" s="108"/>
+      <c r="X16" s="108"/>
+      <c r="Y16" s="109"/>
+      <c r="Z16" s="107">
         <f>SUM(Z5:AF15)</f>
         <v>640</v>
       </c>
-      <c r="AA16" s="81"/>
-      <c r="AB16" s="81"/>
-      <c r="AC16" s="81"/>
-      <c r="AD16" s="81"/>
-      <c r="AE16" s="81"/>
-      <c r="AF16" s="81"/>
+      <c r="AA16" s="108"/>
+      <c r="AB16" s="108"/>
+      <c r="AC16" s="108"/>
+      <c r="AD16" s="108"/>
+      <c r="AE16" s="108"/>
+      <c r="AF16" s="108"/>
       <c r="AG16" s="67"/>
       <c r="AH16" s="66"/>
       <c r="AI16" s="53">
@@ -4648,146 +4660,153 @@
       </c>
     </row>
     <row r="17" spans="1:37" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="114" t="s">
+      <c r="A17" s="86" t="s">
+        <v>25</v>
+      </c>
+      <c r="B17" s="86"/>
+      <c r="C17" s="87"/>
+      <c r="D17" s="88">
+        <v>4219</v>
+      </c>
+      <c r="E17" s="89"/>
+      <c r="F17" s="89"/>
+      <c r="G17" s="89"/>
+      <c r="H17" s="89"/>
+      <c r="I17" s="89"/>
+      <c r="J17" s="89"/>
+      <c r="K17" s="89"/>
+      <c r="L17" s="89"/>
+      <c r="M17" s="89"/>
+      <c r="N17" s="89"/>
+      <c r="O17" s="89"/>
+      <c r="P17" s="89"/>
+      <c r="Q17" s="89"/>
+      <c r="R17" s="89"/>
+      <c r="S17" s="89"/>
+      <c r="T17" s="89"/>
+      <c r="U17" s="89"/>
+      <c r="V17" s="89"/>
+      <c r="W17" s="89"/>
+      <c r="X17" s="89"/>
+      <c r="Y17" s="89"/>
+      <c r="Z17" s="89"/>
+      <c r="AA17" s="89"/>
+      <c r="AB17" s="89"/>
+      <c r="AC17" s="89"/>
+      <c r="AD17" s="89"/>
+      <c r="AE17" s="89"/>
+      <c r="AF17" s="89"/>
+      <c r="AG17" s="89"/>
+      <c r="AH17" s="89"/>
+      <c r="AI17" s="90"/>
+      <c r="AJ17" s="91"/>
+      <c r="AK17" s="78"/>
+    </row>
+    <row r="18" spans="1:37" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="81" t="s">
         <v>26</v>
       </c>
-      <c r="B17" s="114"/>
-      <c r="C17" s="115"/>
-      <c r="D17" s="116">
-        <v>4219</v>
-      </c>
-      <c r="E17" s="117"/>
-      <c r="F17" s="117"/>
-      <c r="G17" s="117"/>
-      <c r="H17" s="117"/>
-      <c r="I17" s="117"/>
-      <c r="J17" s="117"/>
-      <c r="K17" s="117"/>
-      <c r="L17" s="117"/>
-      <c r="M17" s="117"/>
-      <c r="N17" s="117"/>
-      <c r="O17" s="117"/>
-      <c r="P17" s="117"/>
-      <c r="Q17" s="117"/>
-      <c r="R17" s="117"/>
-      <c r="S17" s="117"/>
-      <c r="T17" s="117"/>
-      <c r="U17" s="117"/>
-      <c r="V17" s="117"/>
-      <c r="W17" s="117"/>
-      <c r="X17" s="117"/>
-      <c r="Y17" s="117"/>
-      <c r="Z17" s="117"/>
-      <c r="AA17" s="117"/>
-      <c r="AB17" s="117"/>
-      <c r="AC17" s="117"/>
-      <c r="AD17" s="117"/>
-      <c r="AE17" s="117"/>
-      <c r="AF17" s="117"/>
-      <c r="AG17" s="117"/>
-      <c r="AH17" s="117"/>
-      <c r="AI17" s="118"/>
-      <c r="AJ17" s="119"/>
-      <c r="AK17" s="78"/>
-    </row>
-    <row r="18" spans="1:37" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="109" t="s">
-        <v>20</v>
-      </c>
-      <c r="B18" s="109"/>
-      <c r="C18" s="110"/>
-      <c r="D18" s="120">
+      <c r="B18" s="81"/>
+      <c r="C18" s="82"/>
+      <c r="D18" s="92">
         <f>(AJ3+AJ4)-AJ16</f>
         <v>1505</v>
       </c>
-      <c r="E18" s="118"/>
-      <c r="F18" s="118"/>
-      <c r="G18" s="118"/>
-      <c r="H18" s="118"/>
-      <c r="I18" s="118"/>
-      <c r="J18" s="118"/>
-      <c r="K18" s="118"/>
-      <c r="L18" s="118"/>
-      <c r="M18" s="118"/>
-      <c r="N18" s="118"/>
-      <c r="O18" s="118"/>
-      <c r="P18" s="118"/>
-      <c r="Q18" s="118"/>
-      <c r="R18" s="118"/>
-      <c r="S18" s="118"/>
-      <c r="T18" s="118"/>
-      <c r="U18" s="118"/>
-      <c r="V18" s="118"/>
-      <c r="W18" s="118"/>
-      <c r="X18" s="118"/>
-      <c r="Y18" s="118"/>
-      <c r="Z18" s="118"/>
-      <c r="AA18" s="118"/>
-      <c r="AB18" s="118"/>
-      <c r="AC18" s="118"/>
-      <c r="AD18" s="118"/>
-      <c r="AE18" s="118"/>
-      <c r="AF18" s="118"/>
-      <c r="AG18" s="118"/>
-      <c r="AH18" s="118"/>
-      <c r="AI18" s="118"/>
-      <c r="AJ18" s="119"/>
+      <c r="E18" s="90"/>
+      <c r="F18" s="90"/>
+      <c r="G18" s="90"/>
+      <c r="H18" s="90"/>
+      <c r="I18" s="90"/>
+      <c r="J18" s="90"/>
+      <c r="K18" s="90"/>
+      <c r="L18" s="90"/>
+      <c r="M18" s="90"/>
+      <c r="N18" s="90"/>
+      <c r="O18" s="90"/>
+      <c r="P18" s="90"/>
+      <c r="Q18" s="90"/>
+      <c r="R18" s="90"/>
+      <c r="S18" s="90"/>
+      <c r="T18" s="90"/>
+      <c r="U18" s="90"/>
+      <c r="V18" s="90"/>
+      <c r="W18" s="90"/>
+      <c r="X18" s="90"/>
+      <c r="Y18" s="90"/>
+      <c r="Z18" s="90"/>
+      <c r="AA18" s="90"/>
+      <c r="AB18" s="90"/>
+      <c r="AC18" s="90"/>
+      <c r="AD18" s="90"/>
+      <c r="AE18" s="90"/>
+      <c r="AF18" s="90"/>
+      <c r="AG18" s="90"/>
+      <c r="AH18" s="90"/>
+      <c r="AI18" s="90"/>
+      <c r="AJ18" s="91"/>
       <c r="AK18" s="31">
         <f>((AJ3+AJ4-AJ16)/(AJ3+AJ4))*100</f>
         <v>43.699186991869922</v>
       </c>
     </row>
     <row r="19" spans="1:37" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="108" t="s">
+      <c r="A19" s="80" t="s">
         <v>27</v>
       </c>
-      <c r="B19" s="109"/>
-      <c r="C19" s="110"/>
-      <c r="D19" s="111">
+      <c r="B19" s="81"/>
+      <c r="C19" s="82"/>
+      <c r="D19" s="83">
         <f>(AJ3+AJ4+D17)-AJ16</f>
         <v>5724</v>
       </c>
-      <c r="E19" s="112"/>
-      <c r="F19" s="112"/>
-      <c r="G19" s="112"/>
-      <c r="H19" s="112"/>
-      <c r="I19" s="112"/>
-      <c r="J19" s="112"/>
-      <c r="K19" s="112"/>
-      <c r="L19" s="112"/>
-      <c r="M19" s="112"/>
-      <c r="N19" s="112"/>
-      <c r="O19" s="112"/>
-      <c r="P19" s="112"/>
-      <c r="Q19" s="112"/>
-      <c r="R19" s="112"/>
-      <c r="S19" s="112"/>
-      <c r="T19" s="112"/>
-      <c r="U19" s="112"/>
-      <c r="V19" s="112"/>
-      <c r="W19" s="112"/>
-      <c r="X19" s="112"/>
-      <c r="Y19" s="112"/>
-      <c r="Z19" s="112"/>
-      <c r="AA19" s="112"/>
-      <c r="AB19" s="112"/>
-      <c r="AC19" s="112"/>
-      <c r="AD19" s="112"/>
-      <c r="AE19" s="112"/>
-      <c r="AF19" s="112"/>
-      <c r="AG19" s="112"/>
-      <c r="AH19" s="112"/>
-      <c r="AI19" s="112"/>
-      <c r="AJ19" s="113"/>
+      <c r="E19" s="84"/>
+      <c r="F19" s="84"/>
+      <c r="G19" s="84"/>
+      <c r="H19" s="84"/>
+      <c r="I19" s="84"/>
+      <c r="J19" s="84"/>
+      <c r="K19" s="84"/>
+      <c r="L19" s="84"/>
+      <c r="M19" s="84"/>
+      <c r="N19" s="84"/>
+      <c r="O19" s="84"/>
+      <c r="P19" s="84"/>
+      <c r="Q19" s="84"/>
+      <c r="R19" s="84"/>
+      <c r="S19" s="84"/>
+      <c r="T19" s="84"/>
+      <c r="U19" s="84"/>
+      <c r="V19" s="84"/>
+      <c r="W19" s="84"/>
+      <c r="X19" s="84"/>
+      <c r="Y19" s="84"/>
+      <c r="Z19" s="84"/>
+      <c r="AA19" s="84"/>
+      <c r="AB19" s="84"/>
+      <c r="AC19" s="84"/>
+      <c r="AD19" s="84"/>
+      <c r="AE19" s="84"/>
+      <c r="AF19" s="84"/>
+      <c r="AG19" s="84"/>
+      <c r="AH19" s="84"/>
+      <c r="AI19" s="84"/>
+      <c r="AJ19" s="85"/>
       <c r="AK19" s="54"/>
     </row>
     <row r="24" spans="1:37" x14ac:dyDescent="0.3">
       <c r="S24" s="1" t="s">
-        <v>29</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="A1:C2"/>
+    <mergeCell ref="AI1:AI2"/>
+    <mergeCell ref="AJ1:AJ2"/>
+    <mergeCell ref="AK1:AK2"/>
+    <mergeCell ref="A3:B4"/>
+    <mergeCell ref="AI3:AI4"/>
+    <mergeCell ref="AK3:AK4"/>
     <mergeCell ref="A19:C19"/>
     <mergeCell ref="D19:AJ19"/>
     <mergeCell ref="E16:K16"/>
@@ -4802,13 +4821,6 @@
     <mergeCell ref="B5:B11"/>
     <mergeCell ref="B12:B15"/>
     <mergeCell ref="B16:C16"/>
-    <mergeCell ref="A1:C2"/>
-    <mergeCell ref="AI1:AI2"/>
-    <mergeCell ref="AJ1:AJ2"/>
-    <mergeCell ref="AK1:AK2"/>
-    <mergeCell ref="A3:B4"/>
-    <mergeCell ref="AI3:AI4"/>
-    <mergeCell ref="AK3:AK4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -4824,123 +4836,123 @@
     <col min="2" max="2" width="6.140625" style="1" customWidth="1"/>
     <col min="3" max="3" width="19.28515625" style="1" customWidth="1"/>
     <col min="4" max="34" width="5.7109375" style="1" customWidth="1"/>
-    <col min="35" max="35" width="8.85546875" style="1" customWidth="1"/>
+    <col min="35" max="35" width="12.140625" style="1" customWidth="1"/>
     <col min="36" max="36" width="10.140625" style="1" customWidth="1"/>
     <col min="37" max="37" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="83"/>
-      <c r="B1" s="83"/>
-      <c r="C1" s="84"/>
+      <c r="A1" s="110"/>
+      <c r="B1" s="110"/>
+      <c r="C1" s="111"/>
       <c r="D1" s="36" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E1" s="37" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="F1" s="36" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="G1" s="36" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="H1" s="36" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="I1" s="37" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="J1" s="55" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="K1" s="36" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="L1" s="37" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="M1" s="36" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="N1" s="36" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="O1" s="36" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="P1" s="37" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="Q1" s="55" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="R1" s="36" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="S1" s="37" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="T1" s="36" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="U1" s="36" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="V1" s="36" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="W1" s="37" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="X1" s="55" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="Y1" s="36" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="Z1" s="37" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="AA1" s="36" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="AB1" s="36" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="AC1" s="36" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="AD1" s="37" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="AE1" s="55" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="AF1" s="36" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="AG1" s="37" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="AH1" s="36" t="s">
-        <v>14</v>
-      </c>
-      <c r="AI1" s="94" t="s">
-        <v>23</v>
-      </c>
-      <c r="AJ1" s="96" t="s">
-        <v>18</v>
-      </c>
-      <c r="AK1" s="98" t="s">
-        <v>19</v>
+        <v>5</v>
+      </c>
+      <c r="AI1" s="93" t="s">
+        <v>28</v>
+      </c>
+      <c r="AJ1" s="95" t="s">
+        <v>29</v>
+      </c>
+      <c r="AK1" s="97" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="85"/>
-      <c r="B2" s="85"/>
-      <c r="C2" s="86"/>
+      <c r="A2" s="112"/>
+      <c r="B2" s="112"/>
+      <c r="C2" s="113"/>
       <c r="D2" s="11">
         <v>1</v>
       </c>
@@ -5034,17 +5046,17 @@
       <c r="AH2" s="12">
         <v>31</v>
       </c>
-      <c r="AI2" s="95"/>
-      <c r="AJ2" s="97"/>
-      <c r="AK2" s="99"/>
+      <c r="AI2" s="94"/>
+      <c r="AJ2" s="96"/>
+      <c r="AK2" s="98"/>
     </row>
     <row r="3" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="100" t="s">
+      <c r="A3" s="99" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="100"/>
+      <c r="C3" s="57" t="s">
         <v>0</v>
-      </c>
-      <c r="B3" s="101"/>
-      <c r="C3" s="57" t="s">
-        <v>1</v>
       </c>
       <c r="D3" s="14"/>
       <c r="E3" s="15"/>
@@ -5085,7 +5097,7 @@
       <c r="AF3" s="15"/>
       <c r="AG3" s="17"/>
       <c r="AH3" s="15"/>
-      <c r="AI3" s="104">
+      <c r="AI3" s="103">
         <f>(AJ3+AJ4)/31</f>
         <v>120.12903225806451</v>
       </c>
@@ -5093,15 +5105,15 @@
         <f>SUM(D3:AH3)</f>
         <v>3468</v>
       </c>
-      <c r="AK3" s="106">
+      <c r="AK3" s="105">
         <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="102"/>
-      <c r="B4" s="103"/>
+      <c r="A4" s="101"/>
+      <c r="B4" s="102"/>
       <c r="C4" s="58" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="D4" s="18"/>
       <c r="E4" s="18"/>
@@ -5142,22 +5154,22 @@
       <c r="AH4" s="18">
         <v>81</v>
       </c>
-      <c r="AI4" s="105"/>
+      <c r="AI4" s="104"/>
       <c r="AJ4" s="48">
         <f>SUM(D4:AH4)</f>
         <v>256</v>
       </c>
-      <c r="AK4" s="107"/>
+      <c r="AK4" s="106"/>
     </row>
     <row r="5" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="87" t="s">
-        <v>2</v>
-      </c>
-      <c r="B5" s="90" t="s">
-        <v>3</v>
+      <c r="A5" s="114" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="117" t="s">
+        <v>14</v>
       </c>
       <c r="C5" s="59" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="D5" s="21">
         <v>23</v>
@@ -5234,10 +5246,10 @@
       </c>
     </row>
     <row r="6" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="88"/>
-      <c r="B6" s="90"/>
+      <c r="A6" s="115"/>
+      <c r="B6" s="117"/>
       <c r="C6" s="60" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D6" s="4">
         <v>21</v>
@@ -5320,10 +5332,10 @@
       </c>
     </row>
     <row r="7" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="88"/>
-      <c r="B7" s="90"/>
+      <c r="A7" s="115"/>
+      <c r="B7" s="117"/>
       <c r="C7" s="60" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D7" s="25"/>
       <c r="E7" s="4"/>
@@ -5370,10 +5382,10 @@
       </c>
     </row>
     <row r="8" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="88"/>
-      <c r="B8" s="90"/>
+      <c r="A8" s="115"/>
+      <c r="B8" s="117"/>
       <c r="C8" s="61" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D8" s="38"/>
       <c r="E8" s="39"/>
@@ -5426,10 +5438,10 @@
       </c>
     </row>
     <row r="9" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="88"/>
-      <c r="B9" s="90"/>
+      <c r="A9" s="115"/>
+      <c r="B9" s="117"/>
       <c r="C9" s="59" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D9" s="21">
         <v>85</v>
@@ -5486,10 +5498,10 @@
       </c>
     </row>
     <row r="10" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="88"/>
-      <c r="B10" s="90"/>
+      <c r="A10" s="115"/>
+      <c r="B10" s="117"/>
       <c r="C10" s="60" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="4"/>
@@ -5536,10 +5548,10 @@
       </c>
     </row>
     <row r="11" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="88"/>
-      <c r="B11" s="90"/>
+      <c r="A11" s="115"/>
+      <c r="B11" s="117"/>
       <c r="C11" s="60" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="D11" s="21">
         <v>1226</v>
@@ -5596,12 +5608,12 @@
       </c>
     </row>
     <row r="12" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="88"/>
-      <c r="B12" s="91" t="s">
-        <v>4</v>
+      <c r="A12" s="115"/>
+      <c r="B12" s="121" t="s">
+        <v>21</v>
       </c>
       <c r="C12" s="62" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D12" s="6">
         <v>15</v>
@@ -5674,10 +5686,10 @@
       </c>
     </row>
     <row r="13" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="88"/>
-      <c r="B13" s="92"/>
+      <c r="A13" s="115"/>
+      <c r="B13" s="122"/>
       <c r="C13" s="62" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D13" s="28"/>
       <c r="E13" s="8"/>
@@ -5726,10 +5738,10 @@
       </c>
     </row>
     <row r="14" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="88"/>
-      <c r="B14" s="92"/>
+      <c r="A14" s="115"/>
+      <c r="B14" s="122"/>
       <c r="C14" s="56" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D14" s="6"/>
       <c r="E14" s="6"/>
@@ -5782,10 +5794,10 @@
       </c>
     </row>
     <row r="15" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="88"/>
-      <c r="B15" s="93"/>
+      <c r="A15" s="115"/>
+      <c r="B15" s="123"/>
       <c r="C15" s="62" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="D15" s="51"/>
       <c r="E15" s="51"/>
@@ -5840,57 +5852,57 @@
       </c>
     </row>
     <row r="16" spans="1:37" ht="18.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="89"/>
-      <c r="B16" s="80" t="s">
-        <v>10</v>
-      </c>
-      <c r="C16" s="81"/>
-      <c r="D16" s="80">
+      <c r="A16" s="116"/>
+      <c r="B16" s="107" t="s">
+        <v>24</v>
+      </c>
+      <c r="C16" s="108"/>
+      <c r="D16" s="107">
         <f>SUM(D5:I15)</f>
         <v>1938</v>
       </c>
-      <c r="E16" s="81"/>
-      <c r="F16" s="81"/>
-      <c r="G16" s="81"/>
-      <c r="H16" s="81"/>
-      <c r="I16" s="82"/>
-      <c r="J16" s="80">
+      <c r="E16" s="108"/>
+      <c r="F16" s="108"/>
+      <c r="G16" s="108"/>
+      <c r="H16" s="108"/>
+      <c r="I16" s="109"/>
+      <c r="J16" s="107">
         <f>SUM(J5:P15)</f>
         <v>696</v>
       </c>
-      <c r="K16" s="81"/>
-      <c r="L16" s="81"/>
-      <c r="M16" s="81"/>
-      <c r="N16" s="81"/>
-      <c r="O16" s="81"/>
-      <c r="P16" s="82"/>
-      <c r="Q16" s="80">
+      <c r="K16" s="108"/>
+      <c r="L16" s="108"/>
+      <c r="M16" s="108"/>
+      <c r="N16" s="108"/>
+      <c r="O16" s="108"/>
+      <c r="P16" s="109"/>
+      <c r="Q16" s="107">
         <f>SUM(Q5:W15)</f>
         <v>280</v>
       </c>
-      <c r="R16" s="81"/>
-      <c r="S16" s="81"/>
-      <c r="T16" s="81"/>
-      <c r="U16" s="81"/>
-      <c r="V16" s="81"/>
-      <c r="W16" s="82"/>
-      <c r="X16" s="80">
+      <c r="R16" s="108"/>
+      <c r="S16" s="108"/>
+      <c r="T16" s="108"/>
+      <c r="U16" s="108"/>
+      <c r="V16" s="108"/>
+      <c r="W16" s="109"/>
+      <c r="X16" s="107">
         <f>SUM(X5:AD15)</f>
         <v>470</v>
       </c>
-      <c r="Y16" s="81"/>
-      <c r="Z16" s="81"/>
-      <c r="AA16" s="81"/>
-      <c r="AB16" s="81"/>
-      <c r="AC16" s="81"/>
-      <c r="AD16" s="82"/>
-      <c r="AE16" s="80">
+      <c r="Y16" s="108"/>
+      <c r="Z16" s="108"/>
+      <c r="AA16" s="108"/>
+      <c r="AB16" s="108"/>
+      <c r="AC16" s="108"/>
+      <c r="AD16" s="109"/>
+      <c r="AE16" s="107">
         <f>SUM(AE5:AH15)</f>
         <v>216</v>
       </c>
-      <c r="AF16" s="81"/>
-      <c r="AG16" s="81"/>
-      <c r="AH16" s="82"/>
+      <c r="AF16" s="108"/>
+      <c r="AG16" s="108"/>
+      <c r="AH16" s="109"/>
       <c r="AI16" s="53">
         <f>AJ16/31</f>
         <v>116.12903225806451</v>
@@ -5905,146 +5917,153 @@
       </c>
     </row>
     <row r="17" spans="1:37" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="114" t="s">
+      <c r="A17" s="86" t="s">
+        <v>25</v>
+      </c>
+      <c r="B17" s="86"/>
+      <c r="C17" s="87"/>
+      <c r="D17" s="88">
+        <v>5724</v>
+      </c>
+      <c r="E17" s="89"/>
+      <c r="F17" s="89"/>
+      <c r="G17" s="89"/>
+      <c r="H17" s="89"/>
+      <c r="I17" s="89"/>
+      <c r="J17" s="89"/>
+      <c r="K17" s="89"/>
+      <c r="L17" s="89"/>
+      <c r="M17" s="89"/>
+      <c r="N17" s="89"/>
+      <c r="O17" s="89"/>
+      <c r="P17" s="89"/>
+      <c r="Q17" s="89"/>
+      <c r="R17" s="89"/>
+      <c r="S17" s="89"/>
+      <c r="T17" s="89"/>
+      <c r="U17" s="89"/>
+      <c r="V17" s="89"/>
+      <c r="W17" s="89"/>
+      <c r="X17" s="89"/>
+      <c r="Y17" s="89"/>
+      <c r="Z17" s="89"/>
+      <c r="AA17" s="89"/>
+      <c r="AB17" s="89"/>
+      <c r="AC17" s="89"/>
+      <c r="AD17" s="89"/>
+      <c r="AE17" s="89"/>
+      <c r="AF17" s="89"/>
+      <c r="AG17" s="89"/>
+      <c r="AH17" s="89"/>
+      <c r="AI17" s="90"/>
+      <c r="AJ17" s="91"/>
+      <c r="AK17" s="79"/>
+    </row>
+    <row r="18" spans="1:37" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="81" t="s">
         <v>26</v>
       </c>
-      <c r="B17" s="114"/>
-      <c r="C17" s="115"/>
-      <c r="D17" s="116">
-        <v>5724</v>
-      </c>
-      <c r="E17" s="117"/>
-      <c r="F17" s="117"/>
-      <c r="G17" s="117"/>
-      <c r="H17" s="117"/>
-      <c r="I17" s="117"/>
-      <c r="J17" s="117"/>
-      <c r="K17" s="117"/>
-      <c r="L17" s="117"/>
-      <c r="M17" s="117"/>
-      <c r="N17" s="117"/>
-      <c r="O17" s="117"/>
-      <c r="P17" s="117"/>
-      <c r="Q17" s="117"/>
-      <c r="R17" s="117"/>
-      <c r="S17" s="117"/>
-      <c r="T17" s="117"/>
-      <c r="U17" s="117"/>
-      <c r="V17" s="117"/>
-      <c r="W17" s="117"/>
-      <c r="X17" s="117"/>
-      <c r="Y17" s="117"/>
-      <c r="Z17" s="117"/>
-      <c r="AA17" s="117"/>
-      <c r="AB17" s="117"/>
-      <c r="AC17" s="117"/>
-      <c r="AD17" s="117"/>
-      <c r="AE17" s="117"/>
-      <c r="AF17" s="117"/>
-      <c r="AG17" s="117"/>
-      <c r="AH17" s="117"/>
-      <c r="AI17" s="118"/>
-      <c r="AJ17" s="119"/>
-      <c r="AK17" s="79"/>
-    </row>
-    <row r="18" spans="1:37" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="109" t="s">
-        <v>20</v>
-      </c>
-      <c r="B18" s="109"/>
-      <c r="C18" s="110"/>
-      <c r="D18" s="120">
+      <c r="B18" s="81"/>
+      <c r="C18" s="82"/>
+      <c r="D18" s="92">
         <f>(AJ3+AJ4)-AJ16</f>
         <v>124</v>
       </c>
-      <c r="E18" s="118"/>
-      <c r="F18" s="118"/>
-      <c r="G18" s="118"/>
-      <c r="H18" s="118"/>
-      <c r="I18" s="118"/>
-      <c r="J18" s="118"/>
-      <c r="K18" s="118"/>
-      <c r="L18" s="118"/>
-      <c r="M18" s="118"/>
-      <c r="N18" s="118"/>
-      <c r="O18" s="118"/>
-      <c r="P18" s="118"/>
-      <c r="Q18" s="118"/>
-      <c r="R18" s="118"/>
-      <c r="S18" s="118"/>
-      <c r="T18" s="118"/>
-      <c r="U18" s="118"/>
-      <c r="V18" s="118"/>
-      <c r="W18" s="118"/>
-      <c r="X18" s="118"/>
-      <c r="Y18" s="118"/>
-      <c r="Z18" s="118"/>
-      <c r="AA18" s="118"/>
-      <c r="AB18" s="118"/>
-      <c r="AC18" s="118"/>
-      <c r="AD18" s="118"/>
-      <c r="AE18" s="118"/>
-      <c r="AF18" s="118"/>
-      <c r="AG18" s="118"/>
-      <c r="AH18" s="118"/>
-      <c r="AI18" s="118"/>
-      <c r="AJ18" s="119"/>
+      <c r="E18" s="90"/>
+      <c r="F18" s="90"/>
+      <c r="G18" s="90"/>
+      <c r="H18" s="90"/>
+      <c r="I18" s="90"/>
+      <c r="J18" s="90"/>
+      <c r="K18" s="90"/>
+      <c r="L18" s="90"/>
+      <c r="M18" s="90"/>
+      <c r="N18" s="90"/>
+      <c r="O18" s="90"/>
+      <c r="P18" s="90"/>
+      <c r="Q18" s="90"/>
+      <c r="R18" s="90"/>
+      <c r="S18" s="90"/>
+      <c r="T18" s="90"/>
+      <c r="U18" s="90"/>
+      <c r="V18" s="90"/>
+      <c r="W18" s="90"/>
+      <c r="X18" s="90"/>
+      <c r="Y18" s="90"/>
+      <c r="Z18" s="90"/>
+      <c r="AA18" s="90"/>
+      <c r="AB18" s="90"/>
+      <c r="AC18" s="90"/>
+      <c r="AD18" s="90"/>
+      <c r="AE18" s="90"/>
+      <c r="AF18" s="90"/>
+      <c r="AG18" s="90"/>
+      <c r="AH18" s="90"/>
+      <c r="AI18" s="90"/>
+      <c r="AJ18" s="91"/>
       <c r="AK18" s="31">
         <f>((AJ3+AJ4-AJ16)/(AJ3+AJ4))*100</f>
         <v>3.3297529538131041</v>
       </c>
     </row>
     <row r="19" spans="1:37" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="108" t="s">
+      <c r="A19" s="80" t="s">
         <v>27</v>
       </c>
-      <c r="B19" s="109"/>
-      <c r="C19" s="110"/>
-      <c r="D19" s="111">
+      <c r="B19" s="81"/>
+      <c r="C19" s="82"/>
+      <c r="D19" s="83">
         <f>(AJ3+AJ4+D17)-AJ16</f>
         <v>5848</v>
       </c>
-      <c r="E19" s="112"/>
-      <c r="F19" s="112"/>
-      <c r="G19" s="112"/>
-      <c r="H19" s="112"/>
-      <c r="I19" s="112"/>
-      <c r="J19" s="112"/>
-      <c r="K19" s="112"/>
-      <c r="L19" s="112"/>
-      <c r="M19" s="112"/>
-      <c r="N19" s="112"/>
-      <c r="O19" s="112"/>
-      <c r="P19" s="112"/>
-      <c r="Q19" s="112"/>
-      <c r="R19" s="112"/>
-      <c r="S19" s="112"/>
-      <c r="T19" s="112"/>
-      <c r="U19" s="112"/>
-      <c r="V19" s="112"/>
-      <c r="W19" s="112"/>
-      <c r="X19" s="112"/>
-      <c r="Y19" s="112"/>
-      <c r="Z19" s="112"/>
-      <c r="AA19" s="112"/>
-      <c r="AB19" s="112"/>
-      <c r="AC19" s="112"/>
-      <c r="AD19" s="112"/>
-      <c r="AE19" s="112"/>
-      <c r="AF19" s="112"/>
-      <c r="AG19" s="112"/>
-      <c r="AH19" s="112"/>
-      <c r="AI19" s="112"/>
-      <c r="AJ19" s="113"/>
+      <c r="E19" s="84"/>
+      <c r="F19" s="84"/>
+      <c r="G19" s="84"/>
+      <c r="H19" s="84"/>
+      <c r="I19" s="84"/>
+      <c r="J19" s="84"/>
+      <c r="K19" s="84"/>
+      <c r="L19" s="84"/>
+      <c r="M19" s="84"/>
+      <c r="N19" s="84"/>
+      <c r="O19" s="84"/>
+      <c r="P19" s="84"/>
+      <c r="Q19" s="84"/>
+      <c r="R19" s="84"/>
+      <c r="S19" s="84"/>
+      <c r="T19" s="84"/>
+      <c r="U19" s="84"/>
+      <c r="V19" s="84"/>
+      <c r="W19" s="84"/>
+      <c r="X19" s="84"/>
+      <c r="Y19" s="84"/>
+      <c r="Z19" s="84"/>
+      <c r="AA19" s="84"/>
+      <c r="AB19" s="84"/>
+      <c r="AC19" s="84"/>
+      <c r="AD19" s="84"/>
+      <c r="AE19" s="84"/>
+      <c r="AF19" s="84"/>
+      <c r="AG19" s="84"/>
+      <c r="AH19" s="84"/>
+      <c r="AI19" s="84"/>
+      <c r="AJ19" s="85"/>
       <c r="AK19" s="54"/>
     </row>
     <row r="24" spans="1:37" x14ac:dyDescent="0.3">
       <c r="S24" s="1" t="s">
-        <v>29</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="A1:C2"/>
+    <mergeCell ref="AI1:AI2"/>
+    <mergeCell ref="AJ1:AJ2"/>
+    <mergeCell ref="AK1:AK2"/>
+    <mergeCell ref="A3:B4"/>
+    <mergeCell ref="AI3:AI4"/>
+    <mergeCell ref="AK3:AK4"/>
     <mergeCell ref="A19:C19"/>
     <mergeCell ref="D19:AJ19"/>
     <mergeCell ref="D16:I16"/>
@@ -6060,13 +6079,6 @@
     <mergeCell ref="B5:B11"/>
     <mergeCell ref="B12:B15"/>
     <mergeCell ref="B16:C16"/>
-    <mergeCell ref="A1:C2"/>
-    <mergeCell ref="AI1:AI2"/>
-    <mergeCell ref="AJ1:AJ2"/>
-    <mergeCell ref="AK1:AK2"/>
-    <mergeCell ref="A3:B4"/>
-    <mergeCell ref="AI3:AI4"/>
-    <mergeCell ref="AK3:AK4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -6082,123 +6094,123 @@
     <col min="2" max="2" width="6.140625" style="1" customWidth="1"/>
     <col min="3" max="3" width="19.28515625" style="1" customWidth="1"/>
     <col min="4" max="34" width="5.7109375" style="1" customWidth="1"/>
-    <col min="35" max="35" width="8.85546875" style="1" customWidth="1"/>
+    <col min="35" max="35" width="11.5703125" style="1" customWidth="1"/>
     <col min="36" max="36" width="10.140625" style="1" customWidth="1"/>
     <col min="37" max="37" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="83"/>
-      <c r="B1" s="83"/>
-      <c r="C1" s="84"/>
+      <c r="A1" s="110"/>
+      <c r="B1" s="110"/>
+      <c r="C1" s="111"/>
       <c r="D1" s="37" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="E1" s="55" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="F1" s="36" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="G1" s="37" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="H1" s="36" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="I1" s="36" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="J1" s="36" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="K1" s="37" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="L1" s="55" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="M1" s="36" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="N1" s="37" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="O1" s="36" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="P1" s="36" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="Q1" s="36" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="R1" s="37" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="S1" s="55" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="T1" s="36" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="U1" s="37" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="V1" s="36" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="W1" s="36" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="X1" s="36" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="Y1" s="37" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="Z1" s="55" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="AA1" s="36" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="AB1" s="37" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="AC1" s="36" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="AD1" s="36" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="AE1" s="36" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="AF1" s="37" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="AG1" s="55" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="AH1" s="36" t="s">
-        <v>16</v>
-      </c>
-      <c r="AI1" s="94" t="s">
-        <v>23</v>
-      </c>
-      <c r="AJ1" s="96" t="s">
-        <v>18</v>
-      </c>
-      <c r="AK1" s="98" t="s">
-        <v>19</v>
+        <v>7</v>
+      </c>
+      <c r="AI1" s="93" t="s">
+        <v>28</v>
+      </c>
+      <c r="AJ1" s="95" t="s">
+        <v>29</v>
+      </c>
+      <c r="AK1" s="97" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="85"/>
-      <c r="B2" s="85"/>
-      <c r="C2" s="86"/>
+      <c r="A2" s="112"/>
+      <c r="B2" s="112"/>
+      <c r="C2" s="113"/>
       <c r="D2" s="11">
         <v>1</v>
       </c>
@@ -6292,17 +6304,17 @@
       <c r="AH2" s="12">
         <v>31</v>
       </c>
-      <c r="AI2" s="95"/>
-      <c r="AJ2" s="97"/>
-      <c r="AK2" s="99"/>
+      <c r="AI2" s="94"/>
+      <c r="AJ2" s="96"/>
+      <c r="AK2" s="98"/>
     </row>
     <row r="3" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="100" t="s">
+      <c r="A3" s="99" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="100"/>
+      <c r="C3" s="57" t="s">
         <v>0</v>
-      </c>
-      <c r="B3" s="101"/>
-      <c r="C3" s="57" t="s">
-        <v>1</v>
       </c>
       <c r="D3" s="14"/>
       <c r="E3" s="15"/>
@@ -6339,7 +6351,7 @@
       <c r="AF3" s="15"/>
       <c r="AG3" s="17"/>
       <c r="AH3" s="15"/>
-      <c r="AI3" s="104">
+      <c r="AI3" s="103">
         <f>(AJ3+AJ4)/31</f>
         <v>69.677419354838705</v>
       </c>
@@ -6347,15 +6359,15 @@
         <f>SUM(D3:AH3)</f>
         <v>1469</v>
       </c>
-      <c r="AK3" s="106">
+      <c r="AK3" s="105">
         <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="102"/>
-      <c r="B4" s="103"/>
+      <c r="A4" s="101"/>
+      <c r="B4" s="102"/>
       <c r="C4" s="58" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="D4" s="18">
         <v>50</v>
@@ -6428,22 +6440,22 @@
       <c r="AF4" s="18"/>
       <c r="AG4" s="19"/>
       <c r="AH4" s="18"/>
-      <c r="AI4" s="105"/>
+      <c r="AI4" s="104"/>
       <c r="AJ4" s="48">
         <f>SUM(D4:AH4)</f>
         <v>691</v>
       </c>
-      <c r="AK4" s="107"/>
+      <c r="AK4" s="106"/>
     </row>
     <row r="5" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="87" t="s">
-        <v>2</v>
-      </c>
-      <c r="B5" s="90" t="s">
-        <v>3</v>
+      <c r="A5" s="114" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="117" t="s">
+        <v>14</v>
       </c>
       <c r="C5" s="59" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="D5" s="21"/>
       <c r="E5" s="2">
@@ -6494,10 +6506,10 @@
       </c>
     </row>
     <row r="6" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="88"/>
-      <c r="B6" s="90"/>
+      <c r="A6" s="115"/>
+      <c r="B6" s="117"/>
       <c r="C6" s="60" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="4"/>
@@ -6546,10 +6558,10 @@
       </c>
     </row>
     <row r="7" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="88"/>
-      <c r="B7" s="90"/>
+      <c r="A7" s="115"/>
+      <c r="B7" s="117"/>
       <c r="C7" s="60" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D7" s="25"/>
       <c r="E7" s="4"/>
@@ -6596,10 +6608,10 @@
       </c>
     </row>
     <row r="8" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="88"/>
-      <c r="B8" s="90"/>
+      <c r="A8" s="115"/>
+      <c r="B8" s="117"/>
       <c r="C8" s="61" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D8" s="38"/>
       <c r="E8" s="39"/>
@@ -6648,10 +6660,10 @@
       </c>
     </row>
     <row r="9" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="88"/>
-      <c r="B9" s="90"/>
+      <c r="A9" s="115"/>
+      <c r="B9" s="117"/>
       <c r="C9" s="59" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D9" s="21"/>
       <c r="E9" s="2"/>
@@ -6698,10 +6710,10 @@
       </c>
     </row>
     <row r="10" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="88"/>
-      <c r="B10" s="90"/>
+      <c r="A10" s="115"/>
+      <c r="B10" s="117"/>
       <c r="C10" s="60" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="4"/>
@@ -6748,10 +6760,10 @@
       </c>
     </row>
     <row r="11" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="88"/>
-      <c r="B11" s="90"/>
+      <c r="A11" s="115"/>
+      <c r="B11" s="117"/>
       <c r="C11" s="60" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="D11" s="21"/>
       <c r="E11" s="2"/>
@@ -6812,12 +6824,12 @@
       </c>
     </row>
     <row r="12" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="88"/>
-      <c r="B12" s="91" t="s">
-        <v>4</v>
+      <c r="A12" s="115"/>
+      <c r="B12" s="118" t="s">
+        <v>21</v>
       </c>
       <c r="C12" s="62" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D12" s="6"/>
       <c r="E12" s="6"/>
@@ -6872,10 +6884,10 @@
       </c>
     </row>
     <row r="13" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="88"/>
-      <c r="B13" s="92"/>
+      <c r="A13" s="115"/>
+      <c r="B13" s="119"/>
       <c r="C13" s="62" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D13" s="28"/>
       <c r="E13" s="8"/>
@@ -6922,10 +6934,10 @@
       </c>
     </row>
     <row r="14" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="88"/>
-      <c r="B14" s="92"/>
+      <c r="A14" s="115"/>
+      <c r="B14" s="119"/>
       <c r="C14" s="56" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D14" s="6"/>
       <c r="E14" s="6"/>
@@ -6974,10 +6986,10 @@
       </c>
     </row>
     <row r="15" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="88"/>
-      <c r="B15" s="93"/>
+      <c r="A15" s="115"/>
+      <c r="B15" s="120"/>
       <c r="C15" s="62" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="D15" s="51">
         <v>40</v>
@@ -7048,52 +7060,52 @@
       </c>
     </row>
     <row r="16" spans="1:37" ht="18.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="89"/>
-      <c r="B16" s="80" t="s">
-        <v>10</v>
-      </c>
-      <c r="C16" s="81"/>
+      <c r="A16" s="116"/>
+      <c r="B16" s="107" t="s">
+        <v>24</v>
+      </c>
+      <c r="C16" s="108"/>
       <c r="D16" s="67"/>
-      <c r="E16" s="80">
+      <c r="E16" s="107">
         <f>SUM(E5:K15)</f>
         <v>323</v>
       </c>
-      <c r="F16" s="81"/>
-      <c r="G16" s="81"/>
-      <c r="H16" s="81"/>
-      <c r="I16" s="81"/>
-      <c r="J16" s="81"/>
-      <c r="K16" s="82"/>
-      <c r="L16" s="80">
+      <c r="F16" s="108"/>
+      <c r="G16" s="108"/>
+      <c r="H16" s="108"/>
+      <c r="I16" s="108"/>
+      <c r="J16" s="108"/>
+      <c r="K16" s="109"/>
+      <c r="L16" s="107">
         <f>SUM(L5:R15)</f>
         <v>299</v>
       </c>
-      <c r="M16" s="81"/>
-      <c r="N16" s="81"/>
-      <c r="O16" s="81"/>
-      <c r="P16" s="81"/>
-      <c r="Q16" s="81"/>
-      <c r="R16" s="82"/>
-      <c r="S16" s="80">
+      <c r="M16" s="108"/>
+      <c r="N16" s="108"/>
+      <c r="O16" s="108"/>
+      <c r="P16" s="108"/>
+      <c r="Q16" s="108"/>
+      <c r="R16" s="109"/>
+      <c r="S16" s="107">
         <f>SUM(S5:Y15)</f>
         <v>497</v>
       </c>
-      <c r="T16" s="81"/>
-      <c r="U16" s="81"/>
-      <c r="V16" s="81"/>
-      <c r="W16" s="81"/>
-      <c r="X16" s="81"/>
-      <c r="Y16" s="82"/>
-      <c r="Z16" s="80">
+      <c r="T16" s="108"/>
+      <c r="U16" s="108"/>
+      <c r="V16" s="108"/>
+      <c r="W16" s="108"/>
+      <c r="X16" s="108"/>
+      <c r="Y16" s="109"/>
+      <c r="Z16" s="107">
         <f>SUM(Z5:AF15)</f>
         <v>77</v>
       </c>
-      <c r="AA16" s="81"/>
-      <c r="AB16" s="81"/>
-      <c r="AC16" s="81"/>
-      <c r="AD16" s="81"/>
-      <c r="AE16" s="81"/>
-      <c r="AF16" s="82"/>
+      <c r="AA16" s="108"/>
+      <c r="AB16" s="108"/>
+      <c r="AC16" s="108"/>
+      <c r="AD16" s="108"/>
+      <c r="AE16" s="108"/>
+      <c r="AF16" s="109"/>
       <c r="AG16" s="65"/>
       <c r="AH16" s="66"/>
       <c r="AI16" s="53">
@@ -7110,146 +7122,157 @@
       </c>
     </row>
     <row r="17" spans="1:37" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="114" t="s">
+      <c r="A17" s="86" t="s">
+        <v>25</v>
+      </c>
+      <c r="B17" s="86"/>
+      <c r="C17" s="87"/>
+      <c r="D17" s="88">
+        <v>1695</v>
+      </c>
+      <c r="E17" s="89"/>
+      <c r="F17" s="89"/>
+      <c r="G17" s="89"/>
+      <c r="H17" s="89"/>
+      <c r="I17" s="89"/>
+      <c r="J17" s="89"/>
+      <c r="K17" s="89"/>
+      <c r="L17" s="89"/>
+      <c r="M17" s="89"/>
+      <c r="N17" s="89"/>
+      <c r="O17" s="89"/>
+      <c r="P17" s="89"/>
+      <c r="Q17" s="89"/>
+      <c r="R17" s="89"/>
+      <c r="S17" s="89"/>
+      <c r="T17" s="89"/>
+      <c r="U17" s="89"/>
+      <c r="V17" s="89"/>
+      <c r="W17" s="89"/>
+      <c r="X17" s="89"/>
+      <c r="Y17" s="89"/>
+      <c r="Z17" s="89"/>
+      <c r="AA17" s="89"/>
+      <c r="AB17" s="89"/>
+      <c r="AC17" s="89"/>
+      <c r="AD17" s="89"/>
+      <c r="AE17" s="89"/>
+      <c r="AF17" s="89"/>
+      <c r="AG17" s="89"/>
+      <c r="AH17" s="89"/>
+      <c r="AI17" s="90"/>
+      <c r="AJ17" s="91"/>
+      <c r="AK17" s="64"/>
+    </row>
+    <row r="18" spans="1:37" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="81" t="s">
         <v>26</v>
       </c>
-      <c r="B17" s="114"/>
-      <c r="C17" s="115"/>
-      <c r="D17" s="116">
-        <v>1695</v>
-      </c>
-      <c r="E17" s="117"/>
-      <c r="F17" s="117"/>
-      <c r="G17" s="117"/>
-      <c r="H17" s="117"/>
-      <c r="I17" s="117"/>
-      <c r="J17" s="117"/>
-      <c r="K17" s="117"/>
-      <c r="L17" s="117"/>
-      <c r="M17" s="117"/>
-      <c r="N17" s="117"/>
-      <c r="O17" s="117"/>
-      <c r="P17" s="117"/>
-      <c r="Q17" s="117"/>
-      <c r="R17" s="117"/>
-      <c r="S17" s="117"/>
-      <c r="T17" s="117"/>
-      <c r="U17" s="117"/>
-      <c r="V17" s="117"/>
-      <c r="W17" s="117"/>
-      <c r="X17" s="117"/>
-      <c r="Y17" s="117"/>
-      <c r="Z17" s="117"/>
-      <c r="AA17" s="117"/>
-      <c r="AB17" s="117"/>
-      <c r="AC17" s="117"/>
-      <c r="AD17" s="117"/>
-      <c r="AE17" s="117"/>
-      <c r="AF17" s="117"/>
-      <c r="AG17" s="117"/>
-      <c r="AH17" s="117"/>
-      <c r="AI17" s="118"/>
-      <c r="AJ17" s="119"/>
-      <c r="AK17" s="64"/>
-    </row>
-    <row r="18" spans="1:37" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="109" t="s">
-        <v>20</v>
-      </c>
-      <c r="B18" s="109"/>
-      <c r="C18" s="110"/>
-      <c r="D18" s="120">
+      <c r="B18" s="81"/>
+      <c r="C18" s="82"/>
+      <c r="D18" s="92">
         <f>((AJ3+AJ4+D17)-AJ16)-D17</f>
         <v>924</v>
       </c>
-      <c r="E18" s="118"/>
-      <c r="F18" s="118"/>
-      <c r="G18" s="118"/>
-      <c r="H18" s="118"/>
-      <c r="I18" s="118"/>
-      <c r="J18" s="118"/>
-      <c r="K18" s="118"/>
-      <c r="L18" s="118"/>
-      <c r="M18" s="118"/>
-      <c r="N18" s="118"/>
-      <c r="O18" s="118"/>
-      <c r="P18" s="118"/>
-      <c r="Q18" s="118"/>
-      <c r="R18" s="118"/>
-      <c r="S18" s="118"/>
-      <c r="T18" s="118"/>
-      <c r="U18" s="118"/>
-      <c r="V18" s="118"/>
-      <c r="W18" s="118"/>
-      <c r="X18" s="118"/>
-      <c r="Y18" s="118"/>
-      <c r="Z18" s="118"/>
-      <c r="AA18" s="118"/>
-      <c r="AB18" s="118"/>
-      <c r="AC18" s="118"/>
-      <c r="AD18" s="118"/>
-      <c r="AE18" s="118"/>
-      <c r="AF18" s="118"/>
-      <c r="AG18" s="118"/>
-      <c r="AH18" s="118"/>
-      <c r="AI18" s="118"/>
-      <c r="AJ18" s="119"/>
+      <c r="E18" s="90"/>
+      <c r="F18" s="90"/>
+      <c r="G18" s="90"/>
+      <c r="H18" s="90"/>
+      <c r="I18" s="90"/>
+      <c r="J18" s="90"/>
+      <c r="K18" s="90"/>
+      <c r="L18" s="90"/>
+      <c r="M18" s="90"/>
+      <c r="N18" s="90"/>
+      <c r="O18" s="90"/>
+      <c r="P18" s="90"/>
+      <c r="Q18" s="90"/>
+      <c r="R18" s="90"/>
+      <c r="S18" s="90"/>
+      <c r="T18" s="90"/>
+      <c r="U18" s="90"/>
+      <c r="V18" s="90"/>
+      <c r="W18" s="90"/>
+      <c r="X18" s="90"/>
+      <c r="Y18" s="90"/>
+      <c r="Z18" s="90"/>
+      <c r="AA18" s="90"/>
+      <c r="AB18" s="90"/>
+      <c r="AC18" s="90"/>
+      <c r="AD18" s="90"/>
+      <c r="AE18" s="90"/>
+      <c r="AF18" s="90"/>
+      <c r="AG18" s="90"/>
+      <c r="AH18" s="90"/>
+      <c r="AI18" s="90"/>
+      <c r="AJ18" s="91"/>
       <c r="AK18" s="31">
         <f>((AJ3+AJ4-AJ16)/(AJ3+AJ4))*100</f>
         <v>42.777777777777779</v>
       </c>
     </row>
     <row r="19" spans="1:37" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="108" t="s">
+      <c r="A19" s="80" t="s">
         <v>27</v>
       </c>
-      <c r="B19" s="109"/>
-      <c r="C19" s="110"/>
-      <c r="D19" s="111">
+      <c r="B19" s="81"/>
+      <c r="C19" s="82"/>
+      <c r="D19" s="83">
         <f>(AJ3+AJ4+D17)-AJ16</f>
         <v>2619</v>
       </c>
-      <c r="E19" s="112"/>
-      <c r="F19" s="112"/>
-      <c r="G19" s="112"/>
-      <c r="H19" s="112"/>
-      <c r="I19" s="112"/>
-      <c r="J19" s="112"/>
-      <c r="K19" s="112"/>
-      <c r="L19" s="112"/>
-      <c r="M19" s="112"/>
-      <c r="N19" s="112"/>
-      <c r="O19" s="112"/>
-      <c r="P19" s="112"/>
-      <c r="Q19" s="112"/>
-      <c r="R19" s="112"/>
-      <c r="S19" s="112"/>
-      <c r="T19" s="112"/>
-      <c r="U19" s="112"/>
-      <c r="V19" s="112"/>
-      <c r="W19" s="112"/>
-      <c r="X19" s="112"/>
-      <c r="Y19" s="112"/>
-      <c r="Z19" s="112"/>
-      <c r="AA19" s="112"/>
-      <c r="AB19" s="112"/>
-      <c r="AC19" s="112"/>
-      <c r="AD19" s="112"/>
-      <c r="AE19" s="112"/>
-      <c r="AF19" s="112"/>
-      <c r="AG19" s="112"/>
-      <c r="AH19" s="112"/>
-      <c r="AI19" s="112"/>
-      <c r="AJ19" s="113"/>
+      <c r="E19" s="84"/>
+      <c r="F19" s="84"/>
+      <c r="G19" s="84"/>
+      <c r="H19" s="84"/>
+      <c r="I19" s="84"/>
+      <c r="J19" s="84"/>
+      <c r="K19" s="84"/>
+      <c r="L19" s="84"/>
+      <c r="M19" s="84"/>
+      <c r="N19" s="84"/>
+      <c r="O19" s="84"/>
+      <c r="P19" s="84"/>
+      <c r="Q19" s="84"/>
+      <c r="R19" s="84"/>
+      <c r="S19" s="84"/>
+      <c r="T19" s="84"/>
+      <c r="U19" s="84"/>
+      <c r="V19" s="84"/>
+      <c r="W19" s="84"/>
+      <c r="X19" s="84"/>
+      <c r="Y19" s="84"/>
+      <c r="Z19" s="84"/>
+      <c r="AA19" s="84"/>
+      <c r="AB19" s="84"/>
+      <c r="AC19" s="84"/>
+      <c r="AD19" s="84"/>
+      <c r="AE19" s="84"/>
+      <c r="AF19" s="84"/>
+      <c r="AG19" s="84"/>
+      <c r="AH19" s="84"/>
+      <c r="AI19" s="84"/>
+      <c r="AJ19" s="85"/>
       <c r="AK19" s="54"/>
     </row>
     <row r="24" spans="1:37" x14ac:dyDescent="0.3">
       <c r="S24" s="1" t="s">
-        <v>29</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="D19:AJ19"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="D17:AJ17"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="D18:AJ18"/>
+    <mergeCell ref="AJ1:AJ2"/>
+    <mergeCell ref="AK1:AK2"/>
+    <mergeCell ref="A3:B4"/>
+    <mergeCell ref="AI3:AI4"/>
+    <mergeCell ref="AK3:AK4"/>
     <mergeCell ref="L16:R16"/>
     <mergeCell ref="S16:Y16"/>
     <mergeCell ref="Z16:AF16"/>
@@ -7260,17 +7283,6 @@
     <mergeCell ref="B12:B15"/>
     <mergeCell ref="B16:C16"/>
     <mergeCell ref="E16:K16"/>
-    <mergeCell ref="AJ1:AJ2"/>
-    <mergeCell ref="AK1:AK2"/>
-    <mergeCell ref="A3:B4"/>
-    <mergeCell ref="AI3:AI4"/>
-    <mergeCell ref="AK3:AK4"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="D19:AJ19"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="D17:AJ17"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="D18:AJ18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -7286,123 +7298,123 @@
     <col min="2" max="2" width="6.140625" style="1" customWidth="1"/>
     <col min="3" max="3" width="19.28515625" style="1" customWidth="1"/>
     <col min="4" max="34" width="5.7109375" style="1" customWidth="1"/>
-    <col min="35" max="35" width="8.85546875" style="1" customWidth="1"/>
+    <col min="35" max="35" width="11.42578125" style="1" customWidth="1"/>
     <col min="36" max="36" width="10.140625" style="1" customWidth="1"/>
     <col min="37" max="37" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="83"/>
-      <c r="B1" s="83"/>
-      <c r="C1" s="84"/>
+      <c r="A1" s="110"/>
+      <c r="B1" s="110"/>
+      <c r="C1" s="111"/>
       <c r="D1" s="37" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="E1" s="55" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="F1" s="36" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="G1" s="37" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="H1" s="36" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="I1" s="36" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="J1" s="36" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="K1" s="37" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="L1" s="55" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="M1" s="36" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="N1" s="37" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="O1" s="36" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="P1" s="36" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="Q1" s="36" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="R1" s="37" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="S1" s="55" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="T1" s="36" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="U1" s="37" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="V1" s="36" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="W1" s="36" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="X1" s="36" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="Y1" s="37" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="Z1" s="55" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="AA1" s="36" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="AB1" s="37" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="AC1" s="36" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="AD1" s="36" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="AE1" s="36" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="AF1" s="37" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="AG1" s="55" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="AH1" s="36" t="s">
-        <v>16</v>
-      </c>
-      <c r="AI1" s="94" t="s">
-        <v>23</v>
-      </c>
-      <c r="AJ1" s="96" t="s">
-        <v>18</v>
-      </c>
-      <c r="AK1" s="98" t="s">
-        <v>19</v>
+        <v>7</v>
+      </c>
+      <c r="AI1" s="93" t="s">
+        <v>28</v>
+      </c>
+      <c r="AJ1" s="95" t="s">
+        <v>29</v>
+      </c>
+      <c r="AK1" s="97" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="85"/>
-      <c r="B2" s="85"/>
-      <c r="C2" s="86"/>
+      <c r="A2" s="112"/>
+      <c r="B2" s="112"/>
+      <c r="C2" s="113"/>
       <c r="D2" s="11">
         <v>1</v>
       </c>
@@ -7496,17 +7508,17 @@
       <c r="AH2" s="12">
         <v>31</v>
       </c>
-      <c r="AI2" s="95"/>
-      <c r="AJ2" s="97"/>
-      <c r="AK2" s="99"/>
+      <c r="AI2" s="94"/>
+      <c r="AJ2" s="96"/>
+      <c r="AK2" s="98"/>
     </row>
     <row r="3" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="100" t="s">
+      <c r="A3" s="99" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="100"/>
+      <c r="C3" s="57" t="s">
         <v>0</v>
-      </c>
-      <c r="B3" s="101"/>
-      <c r="C3" s="57" t="s">
-        <v>1</v>
       </c>
       <c r="D3" s="14"/>
       <c r="E3" s="15"/>
@@ -7543,7 +7555,7 @@
       <c r="AF3" s="15"/>
       <c r="AG3" s="17"/>
       <c r="AH3" s="15"/>
-      <c r="AI3" s="104">
+      <c r="AI3" s="103">
         <f>(AJ3+AJ4)/31</f>
         <v>65.645161290322577</v>
       </c>
@@ -7551,15 +7563,15 @@
         <f>SUM(D3:AH3)</f>
         <v>1801</v>
       </c>
-      <c r="AK3" s="106">
+      <c r="AK3" s="105">
         <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="102"/>
-      <c r="B4" s="103"/>
+      <c r="A4" s="101"/>
+      <c r="B4" s="102"/>
       <c r="C4" s="58" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="D4" s="18"/>
       <c r="E4" s="18"/>
@@ -7624,22 +7636,22 @@
       <c r="AF4" s="18"/>
       <c r="AG4" s="19"/>
       <c r="AH4" s="18"/>
-      <c r="AI4" s="105"/>
+      <c r="AI4" s="104"/>
       <c r="AJ4" s="48">
         <f>SUM(D4:AH4)</f>
         <v>234</v>
       </c>
-      <c r="AK4" s="107"/>
+      <c r="AK4" s="106"/>
     </row>
     <row r="5" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="87" t="s">
-        <v>2</v>
-      </c>
-      <c r="B5" s="90" t="s">
-        <v>3</v>
+      <c r="A5" s="114" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="117" t="s">
+        <v>14</v>
       </c>
       <c r="C5" s="59" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="D5" s="21"/>
       <c r="E5" s="2">
@@ -7712,10 +7724,10 @@
       </c>
     </row>
     <row r="6" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="88"/>
-      <c r="B6" s="90"/>
+      <c r="A6" s="115"/>
+      <c r="B6" s="117"/>
       <c r="C6" s="60" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="4">
@@ -7786,10 +7798,10 @@
       </c>
     </row>
     <row r="7" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="88"/>
-      <c r="B7" s="90"/>
+      <c r="A7" s="115"/>
+      <c r="B7" s="117"/>
       <c r="C7" s="60" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D7" s="25"/>
       <c r="E7" s="4"/>
@@ -7836,10 +7848,10 @@
       </c>
     </row>
     <row r="8" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="88"/>
-      <c r="B8" s="90"/>
+      <c r="A8" s="115"/>
+      <c r="B8" s="117"/>
       <c r="C8" s="61" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D8" s="38"/>
       <c r="E8" s="39"/>
@@ -7894,10 +7906,10 @@
       </c>
     </row>
     <row r="9" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="88"/>
-      <c r="B9" s="90"/>
+      <c r="A9" s="115"/>
+      <c r="B9" s="117"/>
       <c r="C9" s="59" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D9" s="21"/>
       <c r="E9" s="2"/>
@@ -7944,10 +7956,10 @@
       </c>
     </row>
     <row r="10" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="88"/>
-      <c r="B10" s="90"/>
+      <c r="A10" s="115"/>
+      <c r="B10" s="117"/>
       <c r="C10" s="60" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="4"/>
@@ -7994,10 +8006,10 @@
       </c>
     </row>
     <row r="11" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="88"/>
-      <c r="B11" s="90"/>
+      <c r="A11" s="115"/>
+      <c r="B11" s="117"/>
       <c r="C11" s="60" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="D11" s="21"/>
       <c r="E11" s="2"/>
@@ -8058,12 +8070,12 @@
       </c>
     </row>
     <row r="12" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="88"/>
-      <c r="B12" s="91" t="s">
-        <v>4</v>
+      <c r="A12" s="115"/>
+      <c r="B12" s="118" t="s">
+        <v>21</v>
       </c>
       <c r="C12" s="62" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D12" s="6"/>
       <c r="E12" s="6"/>
@@ -8130,10 +8142,10 @@
       </c>
     </row>
     <row r="13" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="88"/>
-      <c r="B13" s="92"/>
+      <c r="A13" s="115"/>
+      <c r="B13" s="119"/>
       <c r="C13" s="62" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D13" s="28"/>
       <c r="E13" s="8"/>
@@ -8182,10 +8194,10 @@
       </c>
     </row>
     <row r="14" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="88"/>
-      <c r="B14" s="92"/>
+      <c r="A14" s="115"/>
+      <c r="B14" s="119"/>
       <c r="C14" s="56" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D14" s="6"/>
       <c r="E14" s="6"/>
@@ -8234,10 +8246,10 @@
       </c>
     </row>
     <row r="15" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="88"/>
-      <c r="B15" s="93"/>
+      <c r="A15" s="115"/>
+      <c r="B15" s="120"/>
       <c r="C15" s="62" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="D15" s="51"/>
       <c r="E15" s="51"/>
@@ -8302,57 +8314,57 @@
       </c>
     </row>
     <row r="16" spans="1:37" ht="18.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="89"/>
-      <c r="B16" s="80" t="s">
-        <v>10</v>
-      </c>
-      <c r="C16" s="81"/>
+      <c r="A16" s="116"/>
+      <c r="B16" s="107" t="s">
+        <v>24</v>
+      </c>
+      <c r="C16" s="108"/>
       <c r="D16" s="68"/>
-      <c r="E16" s="80">
+      <c r="E16" s="107">
         <f>SUM(E5:K15)</f>
         <v>240</v>
       </c>
-      <c r="F16" s="81"/>
-      <c r="G16" s="81"/>
-      <c r="H16" s="81"/>
-      <c r="I16" s="81"/>
-      <c r="J16" s="81"/>
-      <c r="K16" s="82"/>
-      <c r="L16" s="80">
+      <c r="F16" s="108"/>
+      <c r="G16" s="108"/>
+      <c r="H16" s="108"/>
+      <c r="I16" s="108"/>
+      <c r="J16" s="108"/>
+      <c r="K16" s="109"/>
+      <c r="L16" s="107">
         <f>SUM(L5:R15)</f>
         <v>371</v>
       </c>
-      <c r="M16" s="81"/>
-      <c r="N16" s="81"/>
-      <c r="O16" s="81"/>
-      <c r="P16" s="81"/>
-      <c r="Q16" s="81"/>
-      <c r="R16" s="82"/>
-      <c r="S16" s="80">
+      <c r="M16" s="108"/>
+      <c r="N16" s="108"/>
+      <c r="O16" s="108"/>
+      <c r="P16" s="108"/>
+      <c r="Q16" s="108"/>
+      <c r="R16" s="109"/>
+      <c r="S16" s="107">
         <f>SUM(S5:Y15)</f>
         <v>354</v>
       </c>
-      <c r="T16" s="81"/>
-      <c r="U16" s="81"/>
-      <c r="V16" s="81"/>
-      <c r="W16" s="81"/>
-      <c r="X16" s="81"/>
-      <c r="Y16" s="82"/>
-      <c r="Z16" s="80">
+      <c r="T16" s="108"/>
+      <c r="U16" s="108"/>
+      <c r="V16" s="108"/>
+      <c r="W16" s="108"/>
+      <c r="X16" s="108"/>
+      <c r="Y16" s="109"/>
+      <c r="Z16" s="107">
         <f>SUM(Z5:AF15)</f>
         <v>337</v>
       </c>
-      <c r="AA16" s="81"/>
-      <c r="AB16" s="81"/>
-      <c r="AC16" s="81"/>
-      <c r="AD16" s="81"/>
-      <c r="AE16" s="81"/>
-      <c r="AF16" s="82"/>
-      <c r="AG16" s="80">
+      <c r="AA16" s="108"/>
+      <c r="AB16" s="108"/>
+      <c r="AC16" s="108"/>
+      <c r="AD16" s="108"/>
+      <c r="AE16" s="108"/>
+      <c r="AF16" s="109"/>
+      <c r="AG16" s="107">
         <f>SUM(AG5:AH15)</f>
         <v>64</v>
       </c>
-      <c r="AH16" s="82"/>
+      <c r="AH16" s="109"/>
       <c r="AI16" s="53">
         <f t="shared" si="0"/>
         <v>44.064516129032256</v>
@@ -8367,153 +8379,146 @@
       </c>
     </row>
     <row r="17" spans="1:37" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="114" t="s">
+      <c r="A17" s="86" t="s">
+        <v>25</v>
+      </c>
+      <c r="B17" s="86"/>
+      <c r="C17" s="87"/>
+      <c r="D17" s="88">
+        <v>2619</v>
+      </c>
+      <c r="E17" s="89"/>
+      <c r="F17" s="89"/>
+      <c r="G17" s="89"/>
+      <c r="H17" s="89"/>
+      <c r="I17" s="89"/>
+      <c r="J17" s="89"/>
+      <c r="K17" s="89"/>
+      <c r="L17" s="89"/>
+      <c r="M17" s="89"/>
+      <c r="N17" s="89"/>
+      <c r="O17" s="89"/>
+      <c r="P17" s="89"/>
+      <c r="Q17" s="89"/>
+      <c r="R17" s="89"/>
+      <c r="S17" s="89"/>
+      <c r="T17" s="89"/>
+      <c r="U17" s="89"/>
+      <c r="V17" s="89"/>
+      <c r="W17" s="89"/>
+      <c r="X17" s="89"/>
+      <c r="Y17" s="89"/>
+      <c r="Z17" s="89"/>
+      <c r="AA17" s="89"/>
+      <c r="AB17" s="89"/>
+      <c r="AC17" s="89"/>
+      <c r="AD17" s="89"/>
+      <c r="AE17" s="89"/>
+      <c r="AF17" s="89"/>
+      <c r="AG17" s="89"/>
+      <c r="AH17" s="89"/>
+      <c r="AI17" s="90"/>
+      <c r="AJ17" s="91"/>
+      <c r="AK17" s="69"/>
+    </row>
+    <row r="18" spans="1:37" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="81" t="s">
         <v>26</v>
       </c>
-      <c r="B17" s="114"/>
-      <c r="C17" s="115"/>
-      <c r="D17" s="116">
-        <v>2619</v>
-      </c>
-      <c r="E17" s="117"/>
-      <c r="F17" s="117"/>
-      <c r="G17" s="117"/>
-      <c r="H17" s="117"/>
-      <c r="I17" s="117"/>
-      <c r="J17" s="117"/>
-      <c r="K17" s="117"/>
-      <c r="L17" s="117"/>
-      <c r="M17" s="117"/>
-      <c r="N17" s="117"/>
-      <c r="O17" s="117"/>
-      <c r="P17" s="117"/>
-      <c r="Q17" s="117"/>
-      <c r="R17" s="117"/>
-      <c r="S17" s="117"/>
-      <c r="T17" s="117"/>
-      <c r="U17" s="117"/>
-      <c r="V17" s="117"/>
-      <c r="W17" s="117"/>
-      <c r="X17" s="117"/>
-      <c r="Y17" s="117"/>
-      <c r="Z17" s="117"/>
-      <c r="AA17" s="117"/>
-      <c r="AB17" s="117"/>
-      <c r="AC17" s="117"/>
-      <c r="AD17" s="117"/>
-      <c r="AE17" s="117"/>
-      <c r="AF17" s="117"/>
-      <c r="AG17" s="117"/>
-      <c r="AH17" s="117"/>
-      <c r="AI17" s="118"/>
-      <c r="AJ17" s="119"/>
-      <c r="AK17" s="69"/>
-    </row>
-    <row r="18" spans="1:37" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="109" t="s">
-        <v>20</v>
-      </c>
-      <c r="B18" s="109"/>
-      <c r="C18" s="110"/>
-      <c r="D18" s="120">
+      <c r="B18" s="81"/>
+      <c r="C18" s="82"/>
+      <c r="D18" s="92">
         <f>((AJ3+AJ4+D17)-AJ16)-D17</f>
         <v>669</v>
       </c>
-      <c r="E18" s="118"/>
-      <c r="F18" s="118"/>
-      <c r="G18" s="118"/>
-      <c r="H18" s="118"/>
-      <c r="I18" s="118"/>
-      <c r="J18" s="118"/>
-      <c r="K18" s="118"/>
-      <c r="L18" s="118"/>
-      <c r="M18" s="118"/>
-      <c r="N18" s="118"/>
-      <c r="O18" s="118"/>
-      <c r="P18" s="118"/>
-      <c r="Q18" s="118"/>
-      <c r="R18" s="118"/>
-      <c r="S18" s="118"/>
-      <c r="T18" s="118"/>
-      <c r="U18" s="118"/>
-      <c r="V18" s="118"/>
-      <c r="W18" s="118"/>
-      <c r="X18" s="118"/>
-      <c r="Y18" s="118"/>
-      <c r="Z18" s="118"/>
-      <c r="AA18" s="118"/>
-      <c r="AB18" s="118"/>
-      <c r="AC18" s="118"/>
-      <c r="AD18" s="118"/>
-      <c r="AE18" s="118"/>
-      <c r="AF18" s="118"/>
-      <c r="AG18" s="118"/>
-      <c r="AH18" s="118"/>
-      <c r="AI18" s="118"/>
-      <c r="AJ18" s="119"/>
+      <c r="E18" s="90"/>
+      <c r="F18" s="90"/>
+      <c r="G18" s="90"/>
+      <c r="H18" s="90"/>
+      <c r="I18" s="90"/>
+      <c r="J18" s="90"/>
+      <c r="K18" s="90"/>
+      <c r="L18" s="90"/>
+      <c r="M18" s="90"/>
+      <c r="N18" s="90"/>
+      <c r="O18" s="90"/>
+      <c r="P18" s="90"/>
+      <c r="Q18" s="90"/>
+      <c r="R18" s="90"/>
+      <c r="S18" s="90"/>
+      <c r="T18" s="90"/>
+      <c r="U18" s="90"/>
+      <c r="V18" s="90"/>
+      <c r="W18" s="90"/>
+      <c r="X18" s="90"/>
+      <c r="Y18" s="90"/>
+      <c r="Z18" s="90"/>
+      <c r="AA18" s="90"/>
+      <c r="AB18" s="90"/>
+      <c r="AC18" s="90"/>
+      <c r="AD18" s="90"/>
+      <c r="AE18" s="90"/>
+      <c r="AF18" s="90"/>
+      <c r="AG18" s="90"/>
+      <c r="AH18" s="90"/>
+      <c r="AI18" s="90"/>
+      <c r="AJ18" s="91"/>
       <c r="AK18" s="31">
         <f>((AJ3+AJ4-AJ16)/(AJ3+AJ4))*100</f>
         <v>32.874692874692876</v>
       </c>
     </row>
     <row r="19" spans="1:37" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="108" t="s">
+      <c r="A19" s="80" t="s">
         <v>27</v>
       </c>
-      <c r="B19" s="109"/>
-      <c r="C19" s="110"/>
-      <c r="D19" s="111">
+      <c r="B19" s="81"/>
+      <c r="C19" s="82"/>
+      <c r="D19" s="83">
         <f>(AJ3+AJ4+D17)-AJ16</f>
         <v>3288</v>
       </c>
-      <c r="E19" s="112"/>
-      <c r="F19" s="112"/>
-      <c r="G19" s="112"/>
-      <c r="H19" s="112"/>
-      <c r="I19" s="112"/>
-      <c r="J19" s="112"/>
-      <c r="K19" s="112"/>
-      <c r="L19" s="112"/>
-      <c r="M19" s="112"/>
-      <c r="N19" s="112"/>
-      <c r="O19" s="112"/>
-      <c r="P19" s="112"/>
-      <c r="Q19" s="112"/>
-      <c r="R19" s="112"/>
-      <c r="S19" s="112"/>
-      <c r="T19" s="112"/>
-      <c r="U19" s="112"/>
-      <c r="V19" s="112"/>
-      <c r="W19" s="112"/>
-      <c r="X19" s="112"/>
-      <c r="Y19" s="112"/>
-      <c r="Z19" s="112"/>
-      <c r="AA19" s="112"/>
-      <c r="AB19" s="112"/>
-      <c r="AC19" s="112"/>
-      <c r="AD19" s="112"/>
-      <c r="AE19" s="112"/>
-      <c r="AF19" s="112"/>
-      <c r="AG19" s="112"/>
-      <c r="AH19" s="112"/>
-      <c r="AI19" s="112"/>
-      <c r="AJ19" s="113"/>
+      <c r="E19" s="84"/>
+      <c r="F19" s="84"/>
+      <c r="G19" s="84"/>
+      <c r="H19" s="84"/>
+      <c r="I19" s="84"/>
+      <c r="J19" s="84"/>
+      <c r="K19" s="84"/>
+      <c r="L19" s="84"/>
+      <c r="M19" s="84"/>
+      <c r="N19" s="84"/>
+      <c r="O19" s="84"/>
+      <c r="P19" s="84"/>
+      <c r="Q19" s="84"/>
+      <c r="R19" s="84"/>
+      <c r="S19" s="84"/>
+      <c r="T19" s="84"/>
+      <c r="U19" s="84"/>
+      <c r="V19" s="84"/>
+      <c r="W19" s="84"/>
+      <c r="X19" s="84"/>
+      <c r="Y19" s="84"/>
+      <c r="Z19" s="84"/>
+      <c r="AA19" s="84"/>
+      <c r="AB19" s="84"/>
+      <c r="AC19" s="84"/>
+      <c r="AD19" s="84"/>
+      <c r="AE19" s="84"/>
+      <c r="AF19" s="84"/>
+      <c r="AG19" s="84"/>
+      <c r="AH19" s="84"/>
+      <c r="AI19" s="84"/>
+      <c r="AJ19" s="85"/>
       <c r="AK19" s="54"/>
     </row>
     <row r="24" spans="1:37" x14ac:dyDescent="0.3">
       <c r="S24" s="1" t="s">
-        <v>29</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="A1:C2"/>
-    <mergeCell ref="AI1:AI2"/>
-    <mergeCell ref="AJ1:AJ2"/>
-    <mergeCell ref="AK1:AK2"/>
-    <mergeCell ref="A3:B4"/>
-    <mergeCell ref="AI3:AI4"/>
-    <mergeCell ref="AK3:AK4"/>
     <mergeCell ref="A19:C19"/>
     <mergeCell ref="D19:AJ19"/>
     <mergeCell ref="S16:Y16"/>
@@ -8529,6 +8534,13 @@
     <mergeCell ref="E16:K16"/>
     <mergeCell ref="L16:R16"/>
     <mergeCell ref="AG16:AH16"/>
+    <mergeCell ref="A1:C2"/>
+    <mergeCell ref="AI1:AI2"/>
+    <mergeCell ref="AJ1:AJ2"/>
+    <mergeCell ref="AK1:AK2"/>
+    <mergeCell ref="A3:B4"/>
+    <mergeCell ref="AI3:AI4"/>
+    <mergeCell ref="AK3:AK4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -8544,121 +8556,121 @@
     <col min="2" max="2" width="6.140625" style="1" customWidth="1"/>
     <col min="3" max="3" width="19.28515625" style="1" customWidth="1"/>
     <col min="4" max="34" width="5.7109375" style="1" customWidth="1"/>
-    <col min="35" max="35" width="8.85546875" style="1" customWidth="1"/>
+    <col min="35" max="35" width="11.140625" style="1" customWidth="1"/>
     <col min="36" max="36" width="10.140625" style="1" customWidth="1"/>
     <col min="37" max="37" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="83"/>
-      <c r="B1" s="83"/>
-      <c r="C1" s="84"/>
+      <c r="A1" s="110"/>
+      <c r="B1" s="110"/>
+      <c r="C1" s="111"/>
       <c r="D1" s="37" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E1" s="36" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="F1" s="36" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G1" s="36" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="H1" s="37" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="I1" s="55" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="J1" s="36" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="K1" s="37" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="L1" s="36" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="M1" s="36" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="N1" s="36" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="O1" s="37" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="P1" s="55" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="Q1" s="36" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="R1" s="37" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="S1" s="36" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="T1" s="36" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="U1" s="36" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="V1" s="37" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="W1" s="55" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="X1" s="36" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="Y1" s="37" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="Z1" s="36" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="AA1" s="36" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="AB1" s="36" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="AC1" s="37" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="AD1" s="55" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="AE1" s="36" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="AF1" s="37" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="AG1" s="36" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="AH1" s="36"/>
-      <c r="AI1" s="94" t="s">
-        <v>23</v>
-      </c>
-      <c r="AJ1" s="96" t="s">
-        <v>18</v>
-      </c>
-      <c r="AK1" s="98" t="s">
-        <v>19</v>
+      <c r="AI1" s="93" t="s">
+        <v>28</v>
+      </c>
+      <c r="AJ1" s="95" t="s">
+        <v>29</v>
+      </c>
+      <c r="AK1" s="97" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="85"/>
-      <c r="B2" s="85"/>
-      <c r="C2" s="86"/>
+      <c r="A2" s="112"/>
+      <c r="B2" s="112"/>
+      <c r="C2" s="113"/>
       <c r="D2" s="11">
         <v>1</v>
       </c>
@@ -8752,17 +8764,17 @@
       <c r="AH2" s="12">
         <v>31</v>
       </c>
-      <c r="AI2" s="95"/>
-      <c r="AJ2" s="97"/>
-      <c r="AK2" s="99"/>
+      <c r="AI2" s="94"/>
+      <c r="AJ2" s="96"/>
+      <c r="AK2" s="98"/>
     </row>
     <row r="3" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="100" t="s">
+      <c r="A3" s="99" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="100"/>
+      <c r="C3" s="57" t="s">
         <v>0</v>
-      </c>
-      <c r="B3" s="101"/>
-      <c r="C3" s="57" t="s">
-        <v>1</v>
       </c>
       <c r="D3" s="14"/>
       <c r="E3" s="15"/>
@@ -8803,7 +8815,7 @@
       </c>
       <c r="AG3" s="17"/>
       <c r="AH3" s="15"/>
-      <c r="AI3" s="104">
+      <c r="AI3" s="103">
         <f>(AJ3+AJ4)/31</f>
         <v>123.58064516129032</v>
       </c>
@@ -8811,15 +8823,15 @@
         <f>SUM(D3:AH3)</f>
         <v>2949</v>
       </c>
-      <c r="AK3" s="106">
+      <c r="AK3" s="105">
         <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="102"/>
-      <c r="B4" s="103"/>
+      <c r="A4" s="101"/>
+      <c r="B4" s="102"/>
       <c r="C4" s="58" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="D4" s="18"/>
       <c r="E4" s="18"/>
@@ -8876,22 +8888,22 @@
         <v>142</v>
       </c>
       <c r="AH4" s="18"/>
-      <c r="AI4" s="105"/>
+      <c r="AI4" s="104"/>
       <c r="AJ4" s="48">
         <f>SUM(D4:AH4)</f>
         <v>882</v>
       </c>
-      <c r="AK4" s="107"/>
+      <c r="AK4" s="106"/>
     </row>
     <row r="5" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="87" t="s">
-        <v>2</v>
-      </c>
-      <c r="B5" s="90" t="s">
-        <v>3</v>
+      <c r="A5" s="114" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="117" t="s">
+        <v>14</v>
       </c>
       <c r="C5" s="59" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="D5" s="21">
         <v>24</v>
@@ -8958,10 +8970,10 @@
       </c>
     </row>
     <row r="6" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="88"/>
-      <c r="B6" s="90"/>
+      <c r="A6" s="115"/>
+      <c r="B6" s="117"/>
       <c r="C6" s="60" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D6" s="4">
         <v>9</v>
@@ -9034,10 +9046,10 @@
       </c>
     </row>
     <row r="7" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="88"/>
-      <c r="B7" s="90"/>
+      <c r="A7" s="115"/>
+      <c r="B7" s="117"/>
       <c r="C7" s="60" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D7" s="25"/>
       <c r="E7" s="4"/>
@@ -9084,10 +9096,10 @@
       </c>
     </row>
     <row r="8" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="88"/>
-      <c r="B8" s="90"/>
+      <c r="A8" s="115"/>
+      <c r="B8" s="117"/>
       <c r="C8" s="61" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D8" s="38"/>
       <c r="E8" s="39"/>
@@ -9134,10 +9146,10 @@
       </c>
     </row>
     <row r="9" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="88"/>
-      <c r="B9" s="90"/>
+      <c r="A9" s="115"/>
+      <c r="B9" s="117"/>
       <c r="C9" s="59" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D9" s="21"/>
       <c r="E9" s="2"/>
@@ -9188,10 +9200,10 @@
       </c>
     </row>
     <row r="10" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="88"/>
-      <c r="B10" s="90"/>
+      <c r="A10" s="115"/>
+      <c r="B10" s="117"/>
       <c r="C10" s="60" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="4"/>
@@ -9238,10 +9250,10 @@
       </c>
     </row>
     <row r="11" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="88"/>
-      <c r="B11" s="90"/>
+      <c r="A11" s="115"/>
+      <c r="B11" s="117"/>
       <c r="C11" s="60" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="D11" s="21"/>
       <c r="E11" s="2"/>
@@ -9298,12 +9310,12 @@
       </c>
     </row>
     <row r="12" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="88"/>
-      <c r="B12" s="91" t="s">
-        <v>4</v>
+      <c r="A12" s="115"/>
+      <c r="B12" s="118" t="s">
+        <v>21</v>
       </c>
       <c r="C12" s="62" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D12" s="6"/>
       <c r="E12" s="6"/>
@@ -9354,10 +9366,10 @@
       </c>
     </row>
     <row r="13" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="88"/>
-      <c r="B13" s="92"/>
+      <c r="A13" s="115"/>
+      <c r="B13" s="119"/>
       <c r="C13" s="62" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D13" s="28"/>
       <c r="E13" s="8"/>
@@ -9404,10 +9416,10 @@
       </c>
     </row>
     <row r="14" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="88"/>
-      <c r="B14" s="92"/>
+      <c r="A14" s="115"/>
+      <c r="B14" s="119"/>
       <c r="C14" s="56" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D14" s="6"/>
       <c r="E14" s="6"/>
@@ -9454,10 +9466,10 @@
       </c>
     </row>
     <row r="15" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="88"/>
-      <c r="B15" s="93"/>
+      <c r="A15" s="115"/>
+      <c r="B15" s="120"/>
       <c r="C15" s="62" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="D15" s="51"/>
       <c r="E15" s="51"/>
@@ -9528,56 +9540,56 @@
       </c>
     </row>
     <row r="16" spans="1:37" ht="18.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="89"/>
-      <c r="B16" s="80" t="s">
-        <v>10</v>
-      </c>
-      <c r="C16" s="81"/>
-      <c r="D16" s="80">
+      <c r="A16" s="116"/>
+      <c r="B16" s="107" t="s">
+        <v>24</v>
+      </c>
+      <c r="C16" s="108"/>
+      <c r="D16" s="107">
         <f>SUM(D5:H15)+64</f>
         <v>343</v>
       </c>
-      <c r="E16" s="81"/>
-      <c r="F16" s="81"/>
-      <c r="G16" s="81"/>
-      <c r="H16" s="82"/>
-      <c r="I16" s="80">
+      <c r="E16" s="108"/>
+      <c r="F16" s="108"/>
+      <c r="G16" s="108"/>
+      <c r="H16" s="109"/>
+      <c r="I16" s="107">
         <f>SUM(I5:O15)</f>
         <v>388</v>
       </c>
-      <c r="J16" s="81"/>
-      <c r="K16" s="81"/>
-      <c r="L16" s="81"/>
-      <c r="M16" s="81"/>
-      <c r="N16" s="81"/>
-      <c r="O16" s="82"/>
-      <c r="P16" s="80">
+      <c r="J16" s="108"/>
+      <c r="K16" s="108"/>
+      <c r="L16" s="108"/>
+      <c r="M16" s="108"/>
+      <c r="N16" s="108"/>
+      <c r="O16" s="109"/>
+      <c r="P16" s="107">
         <f>SUM(P5:V15)</f>
         <v>999</v>
       </c>
-      <c r="Q16" s="81"/>
-      <c r="R16" s="81"/>
-      <c r="S16" s="81"/>
-      <c r="T16" s="81"/>
-      <c r="U16" s="81"/>
-      <c r="V16" s="82"/>
-      <c r="W16" s="80">
+      <c r="Q16" s="108"/>
+      <c r="R16" s="108"/>
+      <c r="S16" s="108"/>
+      <c r="T16" s="108"/>
+      <c r="U16" s="108"/>
+      <c r="V16" s="109"/>
+      <c r="W16" s="107">
         <f>SUM(W5:AC15)</f>
         <v>389</v>
       </c>
-      <c r="X16" s="81"/>
-      <c r="Y16" s="81"/>
-      <c r="Z16" s="81"/>
-      <c r="AA16" s="81"/>
-      <c r="AB16" s="81"/>
-      <c r="AC16" s="82"/>
-      <c r="AD16" s="80">
+      <c r="X16" s="108"/>
+      <c r="Y16" s="108"/>
+      <c r="Z16" s="108"/>
+      <c r="AA16" s="108"/>
+      <c r="AB16" s="108"/>
+      <c r="AC16" s="109"/>
+      <c r="AD16" s="107">
         <f>SUM(AD5:AG15)</f>
         <v>890</v>
       </c>
-      <c r="AE16" s="81"/>
-      <c r="AF16" s="81"/>
-      <c r="AG16" s="82"/>
+      <c r="AE16" s="108"/>
+      <c r="AF16" s="108"/>
+      <c r="AG16" s="109"/>
       <c r="AH16" s="66"/>
       <c r="AI16" s="53">
         <f t="shared" si="0"/>
@@ -9593,153 +9605,146 @@
       </c>
     </row>
     <row r="17" spans="1:37" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="114" t="s">
+      <c r="A17" s="86" t="s">
+        <v>25</v>
+      </c>
+      <c r="B17" s="86"/>
+      <c r="C17" s="87"/>
+      <c r="D17" s="88">
+        <v>3288</v>
+      </c>
+      <c r="E17" s="89"/>
+      <c r="F17" s="89"/>
+      <c r="G17" s="89"/>
+      <c r="H17" s="89"/>
+      <c r="I17" s="89"/>
+      <c r="J17" s="89"/>
+      <c r="K17" s="89"/>
+      <c r="L17" s="89"/>
+      <c r="M17" s="89"/>
+      <c r="N17" s="89"/>
+      <c r="O17" s="89"/>
+      <c r="P17" s="89"/>
+      <c r="Q17" s="89"/>
+      <c r="R17" s="89"/>
+      <c r="S17" s="89"/>
+      <c r="T17" s="89"/>
+      <c r="U17" s="89"/>
+      <c r="V17" s="89"/>
+      <c r="W17" s="89"/>
+      <c r="X17" s="89"/>
+      <c r="Y17" s="89"/>
+      <c r="Z17" s="89"/>
+      <c r="AA17" s="89"/>
+      <c r="AB17" s="89"/>
+      <c r="AC17" s="89"/>
+      <c r="AD17" s="89"/>
+      <c r="AE17" s="89"/>
+      <c r="AF17" s="89"/>
+      <c r="AG17" s="89"/>
+      <c r="AH17" s="89"/>
+      <c r="AI17" s="90"/>
+      <c r="AJ17" s="91"/>
+      <c r="AK17" s="70"/>
+    </row>
+    <row r="18" spans="1:37" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="81" t="s">
         <v>26</v>
       </c>
-      <c r="B17" s="114"/>
-      <c r="C17" s="115"/>
-      <c r="D17" s="116">
-        <v>3288</v>
-      </c>
-      <c r="E17" s="117"/>
-      <c r="F17" s="117"/>
-      <c r="G17" s="117"/>
-      <c r="H17" s="117"/>
-      <c r="I17" s="117"/>
-      <c r="J17" s="117"/>
-      <c r="K17" s="117"/>
-      <c r="L17" s="117"/>
-      <c r="M17" s="117"/>
-      <c r="N17" s="117"/>
-      <c r="O17" s="117"/>
-      <c r="P17" s="117"/>
-      <c r="Q17" s="117"/>
-      <c r="R17" s="117"/>
-      <c r="S17" s="117"/>
-      <c r="T17" s="117"/>
-      <c r="U17" s="117"/>
-      <c r="V17" s="117"/>
-      <c r="W17" s="117"/>
-      <c r="X17" s="117"/>
-      <c r="Y17" s="117"/>
-      <c r="Z17" s="117"/>
-      <c r="AA17" s="117"/>
-      <c r="AB17" s="117"/>
-      <c r="AC17" s="117"/>
-      <c r="AD17" s="117"/>
-      <c r="AE17" s="117"/>
-      <c r="AF17" s="117"/>
-      <c r="AG17" s="117"/>
-      <c r="AH17" s="117"/>
-      <c r="AI17" s="118"/>
-      <c r="AJ17" s="119"/>
-      <c r="AK17" s="70"/>
-    </row>
-    <row r="18" spans="1:37" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="109" t="s">
-        <v>20</v>
-      </c>
-      <c r="B18" s="109"/>
-      <c r="C18" s="110"/>
-      <c r="D18" s="120">
+      <c r="B18" s="81"/>
+      <c r="C18" s="82"/>
+      <c r="D18" s="92">
         <f>((AJ3+AJ4+D17)-AJ16)-D17</f>
         <v>886</v>
       </c>
-      <c r="E18" s="118"/>
-      <c r="F18" s="118"/>
-      <c r="G18" s="118"/>
-      <c r="H18" s="118"/>
-      <c r="I18" s="118"/>
-      <c r="J18" s="118"/>
-      <c r="K18" s="118"/>
-      <c r="L18" s="118"/>
-      <c r="M18" s="118"/>
-      <c r="N18" s="118"/>
-      <c r="O18" s="118"/>
-      <c r="P18" s="118"/>
-      <c r="Q18" s="118"/>
-      <c r="R18" s="118"/>
-      <c r="S18" s="118"/>
-      <c r="T18" s="118"/>
-      <c r="U18" s="118"/>
-      <c r="V18" s="118"/>
-      <c r="W18" s="118"/>
-      <c r="X18" s="118"/>
-      <c r="Y18" s="118"/>
-      <c r="Z18" s="118"/>
-      <c r="AA18" s="118"/>
-      <c r="AB18" s="118"/>
-      <c r="AC18" s="118"/>
-      <c r="AD18" s="118"/>
-      <c r="AE18" s="118"/>
-      <c r="AF18" s="118"/>
-      <c r="AG18" s="118"/>
-      <c r="AH18" s="118"/>
-      <c r="AI18" s="118"/>
-      <c r="AJ18" s="119"/>
+      <c r="E18" s="90"/>
+      <c r="F18" s="90"/>
+      <c r="G18" s="90"/>
+      <c r="H18" s="90"/>
+      <c r="I18" s="90"/>
+      <c r="J18" s="90"/>
+      <c r="K18" s="90"/>
+      <c r="L18" s="90"/>
+      <c r="M18" s="90"/>
+      <c r="N18" s="90"/>
+      <c r="O18" s="90"/>
+      <c r="P18" s="90"/>
+      <c r="Q18" s="90"/>
+      <c r="R18" s="90"/>
+      <c r="S18" s="90"/>
+      <c r="T18" s="90"/>
+      <c r="U18" s="90"/>
+      <c r="V18" s="90"/>
+      <c r="W18" s="90"/>
+      <c r="X18" s="90"/>
+      <c r="Y18" s="90"/>
+      <c r="Z18" s="90"/>
+      <c r="AA18" s="90"/>
+      <c r="AB18" s="90"/>
+      <c r="AC18" s="90"/>
+      <c r="AD18" s="90"/>
+      <c r="AE18" s="90"/>
+      <c r="AF18" s="90"/>
+      <c r="AG18" s="90"/>
+      <c r="AH18" s="90"/>
+      <c r="AI18" s="90"/>
+      <c r="AJ18" s="91"/>
       <c r="AK18" s="31">
         <f>((AJ3+AJ4-AJ16)/(AJ3+AJ4))*100</f>
         <v>23.12712085617332</v>
       </c>
     </row>
     <row r="19" spans="1:37" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="108" t="s">
+      <c r="A19" s="80" t="s">
         <v>27</v>
       </c>
-      <c r="B19" s="109"/>
-      <c r="C19" s="110"/>
-      <c r="D19" s="111">
+      <c r="B19" s="81"/>
+      <c r="C19" s="82"/>
+      <c r="D19" s="83">
         <f>(AJ3+AJ4+D17)-AJ16</f>
         <v>4174</v>
       </c>
-      <c r="E19" s="112"/>
-      <c r="F19" s="112"/>
-      <c r="G19" s="112"/>
-      <c r="H19" s="112"/>
-      <c r="I19" s="112"/>
-      <c r="J19" s="112"/>
-      <c r="K19" s="112"/>
-      <c r="L19" s="112"/>
-      <c r="M19" s="112"/>
-      <c r="N19" s="112"/>
-      <c r="O19" s="112"/>
-      <c r="P19" s="112"/>
-      <c r="Q19" s="112"/>
-      <c r="R19" s="112"/>
-      <c r="S19" s="112"/>
-      <c r="T19" s="112"/>
-      <c r="U19" s="112"/>
-      <c r="V19" s="112"/>
-      <c r="W19" s="112"/>
-      <c r="X19" s="112"/>
-      <c r="Y19" s="112"/>
-      <c r="Z19" s="112"/>
-      <c r="AA19" s="112"/>
-      <c r="AB19" s="112"/>
-      <c r="AC19" s="112"/>
-      <c r="AD19" s="112"/>
-      <c r="AE19" s="112"/>
-      <c r="AF19" s="112"/>
-      <c r="AG19" s="112"/>
-      <c r="AH19" s="112"/>
-      <c r="AI19" s="112"/>
-      <c r="AJ19" s="113"/>
+      <c r="E19" s="84"/>
+      <c r="F19" s="84"/>
+      <c r="G19" s="84"/>
+      <c r="H19" s="84"/>
+      <c r="I19" s="84"/>
+      <c r="J19" s="84"/>
+      <c r="K19" s="84"/>
+      <c r="L19" s="84"/>
+      <c r="M19" s="84"/>
+      <c r="N19" s="84"/>
+      <c r="O19" s="84"/>
+      <c r="P19" s="84"/>
+      <c r="Q19" s="84"/>
+      <c r="R19" s="84"/>
+      <c r="S19" s="84"/>
+      <c r="T19" s="84"/>
+      <c r="U19" s="84"/>
+      <c r="V19" s="84"/>
+      <c r="W19" s="84"/>
+      <c r="X19" s="84"/>
+      <c r="Y19" s="84"/>
+      <c r="Z19" s="84"/>
+      <c r="AA19" s="84"/>
+      <c r="AB19" s="84"/>
+      <c r="AC19" s="84"/>
+      <c r="AD19" s="84"/>
+      <c r="AE19" s="84"/>
+      <c r="AF19" s="84"/>
+      <c r="AG19" s="84"/>
+      <c r="AH19" s="84"/>
+      <c r="AI19" s="84"/>
+      <c r="AJ19" s="85"/>
       <c r="AK19" s="54"/>
     </row>
     <row r="24" spans="1:37" x14ac:dyDescent="0.3">
       <c r="S24" s="1" t="s">
-        <v>29</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="A1:C2"/>
-    <mergeCell ref="AI1:AI2"/>
-    <mergeCell ref="AJ1:AJ2"/>
-    <mergeCell ref="AK1:AK2"/>
-    <mergeCell ref="A3:B4"/>
-    <mergeCell ref="AI3:AI4"/>
-    <mergeCell ref="AK3:AK4"/>
     <mergeCell ref="A19:C19"/>
     <mergeCell ref="D19:AJ19"/>
     <mergeCell ref="D16:H16"/>
@@ -9755,6 +9760,13 @@
     <mergeCell ref="B5:B11"/>
     <mergeCell ref="B12:B15"/>
     <mergeCell ref="B16:C16"/>
+    <mergeCell ref="A1:C2"/>
+    <mergeCell ref="AI1:AI2"/>
+    <mergeCell ref="AJ1:AJ2"/>
+    <mergeCell ref="AK1:AK2"/>
+    <mergeCell ref="A3:B4"/>
+    <mergeCell ref="AI3:AI4"/>
+    <mergeCell ref="AK3:AK4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -9770,123 +9782,123 @@
     <col min="2" max="2" width="6.140625" style="1" customWidth="1"/>
     <col min="3" max="3" width="19.28515625" style="1" customWidth="1"/>
     <col min="4" max="34" width="5.7109375" style="1" customWidth="1"/>
-    <col min="35" max="35" width="8.85546875" style="1" customWidth="1"/>
+    <col min="35" max="35" width="11.7109375" style="1" customWidth="1"/>
     <col min="36" max="36" width="10.140625" style="1" customWidth="1"/>
     <col min="37" max="37" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="83"/>
-      <c r="B1" s="83"/>
-      <c r="C1" s="84"/>
+      <c r="A1" s="110"/>
+      <c r="B1" s="110"/>
+      <c r="C1" s="111"/>
       <c r="D1" s="36" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="E1" s="36" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="F1" s="37" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="G1" s="55" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="H1" s="36" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="I1" s="37" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="J1" s="36" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="K1" s="36" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="L1" s="36" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="M1" s="37" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="N1" s="55" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="O1" s="36" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="P1" s="37" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="Q1" s="36" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="R1" s="36" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="S1" s="36" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="T1" s="37" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="U1" s="55" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="V1" s="36" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="W1" s="37" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="X1" s="36" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="Y1" s="36" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="Z1" s="36" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="AA1" s="37" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="AB1" s="55" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="AC1" s="36" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="AD1" s="37" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="AE1" s="36" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="AF1" s="36" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="AG1" s="36" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="AH1" s="37" t="s">
-        <v>11</v>
-      </c>
-      <c r="AI1" s="94" t="s">
-        <v>23</v>
-      </c>
-      <c r="AJ1" s="96" t="s">
-        <v>18</v>
-      </c>
-      <c r="AK1" s="98" t="s">
-        <v>19</v>
+        <v>30</v>
+      </c>
+      <c r="AI1" s="93" t="s">
+        <v>28</v>
+      </c>
+      <c r="AJ1" s="95" t="s">
+        <v>29</v>
+      </c>
+      <c r="AK1" s="97" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="85"/>
-      <c r="B2" s="85"/>
-      <c r="C2" s="86"/>
+      <c r="A2" s="112"/>
+      <c r="B2" s="112"/>
+      <c r="C2" s="113"/>
       <c r="D2" s="11">
         <v>1</v>
       </c>
@@ -9980,17 +9992,17 @@
       <c r="AH2" s="12">
         <v>31</v>
       </c>
-      <c r="AI2" s="95"/>
-      <c r="AJ2" s="97"/>
-      <c r="AK2" s="99"/>
+      <c r="AI2" s="94"/>
+      <c r="AJ2" s="96"/>
+      <c r="AK2" s="98"/>
     </row>
     <row r="3" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="100" t="s">
+      <c r="A3" s="99" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="100"/>
+      <c r="C3" s="57" t="s">
         <v>0</v>
-      </c>
-      <c r="B3" s="101"/>
-      <c r="C3" s="57" t="s">
-        <v>1</v>
       </c>
       <c r="D3" s="14"/>
       <c r="E3" s="15"/>
@@ -10029,7 +10041,7 @@
       <c r="AF3" s="15"/>
       <c r="AG3" s="17"/>
       <c r="AH3" s="15"/>
-      <c r="AI3" s="104">
+      <c r="AI3" s="103">
         <f>(AJ3+AJ4)/31</f>
         <v>65.354838709677423</v>
       </c>
@@ -10037,15 +10049,15 @@
         <f>SUM(D3:AH3)</f>
         <v>1894</v>
       </c>
-      <c r="AK3" s="106">
+      <c r="AK3" s="105">
         <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="102"/>
-      <c r="B4" s="103"/>
+      <c r="A4" s="101"/>
+      <c r="B4" s="102"/>
       <c r="C4" s="58" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="D4" s="18"/>
       <c r="E4" s="18"/>
@@ -10098,22 +10110,22 @@
       <c r="AF4" s="18"/>
       <c r="AG4" s="19"/>
       <c r="AH4" s="18"/>
-      <c r="AI4" s="105"/>
+      <c r="AI4" s="104"/>
       <c r="AJ4" s="48">
         <f>SUM(D4:AH4)</f>
         <v>132</v>
       </c>
-      <c r="AK4" s="107"/>
+      <c r="AK4" s="106"/>
     </row>
     <row r="5" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="87" t="s">
-        <v>2</v>
-      </c>
-      <c r="B5" s="90" t="s">
-        <v>3</v>
+      <c r="A5" s="114" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="117" t="s">
+        <v>14</v>
       </c>
       <c r="C5" s="59" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="D5" s="21">
         <v>4</v>
@@ -10182,10 +10194,10 @@
       </c>
     </row>
     <row r="6" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="88"/>
-      <c r="B6" s="90"/>
+      <c r="A6" s="115"/>
+      <c r="B6" s="117"/>
       <c r="C6" s="60" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="4"/>
@@ -10258,10 +10270,10 @@
       </c>
     </row>
     <row r="7" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="88"/>
-      <c r="B7" s="90"/>
+      <c r="A7" s="115"/>
+      <c r="B7" s="117"/>
       <c r="C7" s="60" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D7" s="25"/>
       <c r="E7" s="4"/>
@@ -10308,10 +10320,10 @@
       </c>
     </row>
     <row r="8" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="88"/>
-      <c r="B8" s="90"/>
+      <c r="A8" s="115"/>
+      <c r="B8" s="117"/>
       <c r="C8" s="61" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D8" s="38"/>
       <c r="E8" s="39"/>
@@ -10364,10 +10376,10 @@
       </c>
     </row>
     <row r="9" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="88"/>
-      <c r="B9" s="90"/>
+      <c r="A9" s="115"/>
+      <c r="B9" s="117"/>
       <c r="C9" s="59" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D9" s="21"/>
       <c r="E9" s="2"/>
@@ -10416,10 +10428,10 @@
       </c>
     </row>
     <row r="10" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="88"/>
-      <c r="B10" s="90"/>
+      <c r="A10" s="115"/>
+      <c r="B10" s="117"/>
       <c r="C10" s="60" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="4"/>
@@ -10468,10 +10480,10 @@
       </c>
     </row>
     <row r="11" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="88"/>
-      <c r="B11" s="90"/>
+      <c r="A11" s="115"/>
+      <c r="B11" s="117"/>
       <c r="C11" s="60" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="D11" s="21"/>
       <c r="E11" s="2"/>
@@ -10528,12 +10540,12 @@
       </c>
     </row>
     <row r="12" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="88"/>
-      <c r="B12" s="91" t="s">
-        <v>4</v>
+      <c r="A12" s="115"/>
+      <c r="B12" s="121" t="s">
+        <v>21</v>
       </c>
       <c r="C12" s="62" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D12" s="6"/>
       <c r="E12" s="6"/>
@@ -10584,10 +10596,10 @@
       </c>
     </row>
     <row r="13" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="88"/>
-      <c r="B13" s="92"/>
+      <c r="A13" s="115"/>
+      <c r="B13" s="122"/>
       <c r="C13" s="62" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D13" s="28"/>
       <c r="E13" s="8"/>
@@ -10634,10 +10646,10 @@
       </c>
     </row>
     <row r="14" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="88"/>
-      <c r="B14" s="92"/>
+      <c r="A14" s="115"/>
+      <c r="B14" s="122"/>
       <c r="C14" s="56" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D14" s="6"/>
       <c r="E14" s="6"/>
@@ -10690,10 +10702,10 @@
       </c>
     </row>
     <row r="15" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="88"/>
-      <c r="B15" s="93"/>
+      <c r="A15" s="115"/>
+      <c r="B15" s="123"/>
       <c r="C15" s="62" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="D15" s="51">
         <v>20</v>
@@ -10760,57 +10772,57 @@
       </c>
     </row>
     <row r="16" spans="1:37" ht="18.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="89"/>
-      <c r="B16" s="80" t="s">
-        <v>10</v>
-      </c>
-      <c r="C16" s="81"/>
-      <c r="D16" s="80">
+      <c r="A16" s="116"/>
+      <c r="B16" s="107" t="s">
+        <v>24</v>
+      </c>
+      <c r="C16" s="108"/>
+      <c r="D16" s="107">
         <f>SUM(D5:F15)+890</f>
         <v>994</v>
       </c>
-      <c r="E16" s="81"/>
-      <c r="F16" s="82"/>
-      <c r="G16" s="80">
+      <c r="E16" s="108"/>
+      <c r="F16" s="109"/>
+      <c r="G16" s="107">
         <f>SUM(G5:M15)</f>
         <v>845</v>
       </c>
-      <c r="H16" s="81"/>
-      <c r="I16" s="81"/>
-      <c r="J16" s="81"/>
-      <c r="K16" s="81"/>
-      <c r="L16" s="81"/>
-      <c r="M16" s="82"/>
-      <c r="N16" s="80">
+      <c r="H16" s="108"/>
+      <c r="I16" s="108"/>
+      <c r="J16" s="108"/>
+      <c r="K16" s="108"/>
+      <c r="L16" s="108"/>
+      <c r="M16" s="109"/>
+      <c r="N16" s="107">
         <f>SUM(N5:T15)</f>
         <v>364</v>
       </c>
-      <c r="O16" s="81"/>
-      <c r="P16" s="81"/>
-      <c r="Q16" s="81"/>
-      <c r="R16" s="81"/>
-      <c r="S16" s="81"/>
-      <c r="T16" s="82"/>
-      <c r="U16" s="80">
+      <c r="O16" s="108"/>
+      <c r="P16" s="108"/>
+      <c r="Q16" s="108"/>
+      <c r="R16" s="108"/>
+      <c r="S16" s="108"/>
+      <c r="T16" s="109"/>
+      <c r="U16" s="107">
         <f>SUM(U5:AA15)</f>
         <v>648</v>
       </c>
-      <c r="V16" s="81"/>
-      <c r="W16" s="81"/>
-      <c r="X16" s="81"/>
-      <c r="Y16" s="81"/>
-      <c r="Z16" s="81"/>
-      <c r="AA16" s="82"/>
-      <c r="AB16" s="80">
+      <c r="V16" s="108"/>
+      <c r="W16" s="108"/>
+      <c r="X16" s="108"/>
+      <c r="Y16" s="108"/>
+      <c r="Z16" s="108"/>
+      <c r="AA16" s="109"/>
+      <c r="AB16" s="107">
         <f>SUM(AB5:AH15)</f>
         <v>144</v>
       </c>
-      <c r="AC16" s="81"/>
-      <c r="AD16" s="81"/>
-      <c r="AE16" s="81"/>
-      <c r="AF16" s="81"/>
-      <c r="AG16" s="81"/>
-      <c r="AH16" s="82"/>
+      <c r="AC16" s="108"/>
+      <c r="AD16" s="108"/>
+      <c r="AE16" s="108"/>
+      <c r="AF16" s="108"/>
+      <c r="AG16" s="108"/>
+      <c r="AH16" s="109"/>
       <c r="AI16" s="53">
         <f t="shared" si="0"/>
         <v>67.903225806451616</v>
@@ -10825,146 +10837,153 @@
       </c>
     </row>
     <row r="17" spans="1:37" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="114" t="s">
+      <c r="A17" s="86" t="s">
+        <v>25</v>
+      </c>
+      <c r="B17" s="86"/>
+      <c r="C17" s="87"/>
+      <c r="D17" s="88">
+        <v>4174</v>
+      </c>
+      <c r="E17" s="89"/>
+      <c r="F17" s="89"/>
+      <c r="G17" s="89"/>
+      <c r="H17" s="89"/>
+      <c r="I17" s="89"/>
+      <c r="J17" s="89"/>
+      <c r="K17" s="89"/>
+      <c r="L17" s="89"/>
+      <c r="M17" s="89"/>
+      <c r="N17" s="89"/>
+      <c r="O17" s="89"/>
+      <c r="P17" s="89"/>
+      <c r="Q17" s="89"/>
+      <c r="R17" s="89"/>
+      <c r="S17" s="89"/>
+      <c r="T17" s="89"/>
+      <c r="U17" s="89"/>
+      <c r="V17" s="89"/>
+      <c r="W17" s="89"/>
+      <c r="X17" s="89"/>
+      <c r="Y17" s="89"/>
+      <c r="Z17" s="89"/>
+      <c r="AA17" s="89"/>
+      <c r="AB17" s="89"/>
+      <c r="AC17" s="89"/>
+      <c r="AD17" s="89"/>
+      <c r="AE17" s="89"/>
+      <c r="AF17" s="89"/>
+      <c r="AG17" s="89"/>
+      <c r="AH17" s="89"/>
+      <c r="AI17" s="90"/>
+      <c r="AJ17" s="91"/>
+      <c r="AK17" s="71"/>
+    </row>
+    <row r="18" spans="1:37" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="81" t="s">
         <v>26</v>
       </c>
-      <c r="B17" s="114"/>
-      <c r="C17" s="115"/>
-      <c r="D17" s="116">
-        <v>4174</v>
-      </c>
-      <c r="E17" s="117"/>
-      <c r="F17" s="117"/>
-      <c r="G17" s="117"/>
-      <c r="H17" s="117"/>
-      <c r="I17" s="117"/>
-      <c r="J17" s="117"/>
-      <c r="K17" s="117"/>
-      <c r="L17" s="117"/>
-      <c r="M17" s="117"/>
-      <c r="N17" s="117"/>
-      <c r="O17" s="117"/>
-      <c r="P17" s="117"/>
-      <c r="Q17" s="117"/>
-      <c r="R17" s="117"/>
-      <c r="S17" s="117"/>
-      <c r="T17" s="117"/>
-      <c r="U17" s="117"/>
-      <c r="V17" s="117"/>
-      <c r="W17" s="117"/>
-      <c r="X17" s="117"/>
-      <c r="Y17" s="117"/>
-      <c r="Z17" s="117"/>
-      <c r="AA17" s="117"/>
-      <c r="AB17" s="117"/>
-      <c r="AC17" s="117"/>
-      <c r="AD17" s="117"/>
-      <c r="AE17" s="117"/>
-      <c r="AF17" s="117"/>
-      <c r="AG17" s="117"/>
-      <c r="AH17" s="117"/>
-      <c r="AI17" s="118"/>
-      <c r="AJ17" s="119"/>
-      <c r="AK17" s="71"/>
-    </row>
-    <row r="18" spans="1:37" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="109" t="s">
-        <v>20</v>
-      </c>
-      <c r="B18" s="109"/>
-      <c r="C18" s="110"/>
-      <c r="D18" s="120">
+      <c r="B18" s="81"/>
+      <c r="C18" s="82"/>
+      <c r="D18" s="92">
         <f>((AJ3+AJ4+D17)-AJ16)-D17</f>
         <v>-79</v>
       </c>
-      <c r="E18" s="118"/>
-      <c r="F18" s="118"/>
-      <c r="G18" s="118"/>
-      <c r="H18" s="118"/>
-      <c r="I18" s="118"/>
-      <c r="J18" s="118"/>
-      <c r="K18" s="118"/>
-      <c r="L18" s="118"/>
-      <c r="M18" s="118"/>
-      <c r="N18" s="118"/>
-      <c r="O18" s="118"/>
-      <c r="P18" s="118"/>
-      <c r="Q18" s="118"/>
-      <c r="R18" s="118"/>
-      <c r="S18" s="118"/>
-      <c r="T18" s="118"/>
-      <c r="U18" s="118"/>
-      <c r="V18" s="118"/>
-      <c r="W18" s="118"/>
-      <c r="X18" s="118"/>
-      <c r="Y18" s="118"/>
-      <c r="Z18" s="118"/>
-      <c r="AA18" s="118"/>
-      <c r="AB18" s="118"/>
-      <c r="AC18" s="118"/>
-      <c r="AD18" s="118"/>
-      <c r="AE18" s="118"/>
-      <c r="AF18" s="118"/>
-      <c r="AG18" s="118"/>
-      <c r="AH18" s="118"/>
-      <c r="AI18" s="118"/>
-      <c r="AJ18" s="119"/>
+      <c r="E18" s="90"/>
+      <c r="F18" s="90"/>
+      <c r="G18" s="90"/>
+      <c r="H18" s="90"/>
+      <c r="I18" s="90"/>
+      <c r="J18" s="90"/>
+      <c r="K18" s="90"/>
+      <c r="L18" s="90"/>
+      <c r="M18" s="90"/>
+      <c r="N18" s="90"/>
+      <c r="O18" s="90"/>
+      <c r="P18" s="90"/>
+      <c r="Q18" s="90"/>
+      <c r="R18" s="90"/>
+      <c r="S18" s="90"/>
+      <c r="T18" s="90"/>
+      <c r="U18" s="90"/>
+      <c r="V18" s="90"/>
+      <c r="W18" s="90"/>
+      <c r="X18" s="90"/>
+      <c r="Y18" s="90"/>
+      <c r="Z18" s="90"/>
+      <c r="AA18" s="90"/>
+      <c r="AB18" s="90"/>
+      <c r="AC18" s="90"/>
+      <c r="AD18" s="90"/>
+      <c r="AE18" s="90"/>
+      <c r="AF18" s="90"/>
+      <c r="AG18" s="90"/>
+      <c r="AH18" s="90"/>
+      <c r="AI18" s="90"/>
+      <c r="AJ18" s="91"/>
       <c r="AK18" s="31">
         <f>((AJ3+AJ4-AJ16)/(AJ3+AJ4))*100</f>
         <v>-3.8993089832181638</v>
       </c>
     </row>
     <row r="19" spans="1:37" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="108" t="s">
+      <c r="A19" s="80" t="s">
         <v>27</v>
       </c>
-      <c r="B19" s="109"/>
-      <c r="C19" s="110"/>
-      <c r="D19" s="111">
+      <c r="B19" s="81"/>
+      <c r="C19" s="82"/>
+      <c r="D19" s="83">
         <f>(AJ3+AJ4+D17)-AJ16</f>
         <v>4095</v>
       </c>
-      <c r="E19" s="112"/>
-      <c r="F19" s="112"/>
-      <c r="G19" s="112"/>
-      <c r="H19" s="112"/>
-      <c r="I19" s="112"/>
-      <c r="J19" s="112"/>
-      <c r="K19" s="112"/>
-      <c r="L19" s="112"/>
-      <c r="M19" s="112"/>
-      <c r="N19" s="112"/>
-      <c r="O19" s="112"/>
-      <c r="P19" s="112"/>
-      <c r="Q19" s="112"/>
-      <c r="R19" s="112"/>
-      <c r="S19" s="112"/>
-      <c r="T19" s="112"/>
-      <c r="U19" s="112"/>
-      <c r="V19" s="112"/>
-      <c r="W19" s="112"/>
-      <c r="X19" s="112"/>
-      <c r="Y19" s="112"/>
-      <c r="Z19" s="112"/>
-      <c r="AA19" s="112"/>
-      <c r="AB19" s="112"/>
-      <c r="AC19" s="112"/>
-      <c r="AD19" s="112"/>
-      <c r="AE19" s="112"/>
-      <c r="AF19" s="112"/>
-      <c r="AG19" s="112"/>
-      <c r="AH19" s="112"/>
-      <c r="AI19" s="112"/>
-      <c r="AJ19" s="113"/>
+      <c r="E19" s="84"/>
+      <c r="F19" s="84"/>
+      <c r="G19" s="84"/>
+      <c r="H19" s="84"/>
+      <c r="I19" s="84"/>
+      <c r="J19" s="84"/>
+      <c r="K19" s="84"/>
+      <c r="L19" s="84"/>
+      <c r="M19" s="84"/>
+      <c r="N19" s="84"/>
+      <c r="O19" s="84"/>
+      <c r="P19" s="84"/>
+      <c r="Q19" s="84"/>
+      <c r="R19" s="84"/>
+      <c r="S19" s="84"/>
+      <c r="T19" s="84"/>
+      <c r="U19" s="84"/>
+      <c r="V19" s="84"/>
+      <c r="W19" s="84"/>
+      <c r="X19" s="84"/>
+      <c r="Y19" s="84"/>
+      <c r="Z19" s="84"/>
+      <c r="AA19" s="84"/>
+      <c r="AB19" s="84"/>
+      <c r="AC19" s="84"/>
+      <c r="AD19" s="84"/>
+      <c r="AE19" s="84"/>
+      <c r="AF19" s="84"/>
+      <c r="AG19" s="84"/>
+      <c r="AH19" s="84"/>
+      <c r="AI19" s="84"/>
+      <c r="AJ19" s="85"/>
       <c r="AK19" s="54"/>
     </row>
     <row r="24" spans="1:37" x14ac:dyDescent="0.3">
       <c r="S24" s="1" t="s">
-        <v>29</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="A1:C2"/>
+    <mergeCell ref="AI1:AI2"/>
+    <mergeCell ref="AJ1:AJ2"/>
+    <mergeCell ref="AK1:AK2"/>
+    <mergeCell ref="A3:B4"/>
+    <mergeCell ref="AI3:AI4"/>
+    <mergeCell ref="AK3:AK4"/>
     <mergeCell ref="A19:C19"/>
     <mergeCell ref="D19:AJ19"/>
     <mergeCell ref="D16:F16"/>
@@ -10980,13 +10999,6 @@
     <mergeCell ref="B5:B11"/>
     <mergeCell ref="B12:B15"/>
     <mergeCell ref="B16:C16"/>
-    <mergeCell ref="A1:C2"/>
-    <mergeCell ref="AI1:AI2"/>
-    <mergeCell ref="AJ1:AJ2"/>
-    <mergeCell ref="AK1:AK2"/>
-    <mergeCell ref="A3:B4"/>
-    <mergeCell ref="AI3:AI4"/>
-    <mergeCell ref="AK3:AK4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -11002,121 +11014,121 @@
     <col min="2" max="2" width="6.140625" style="1" customWidth="1"/>
     <col min="3" max="3" width="19.28515625" style="1" customWidth="1"/>
     <col min="4" max="34" width="5.7109375" style="1" customWidth="1"/>
-    <col min="35" max="35" width="8.85546875" style="1" customWidth="1"/>
+    <col min="35" max="35" width="12.28515625" style="1" customWidth="1"/>
     <col min="36" max="36" width="10.140625" style="1" customWidth="1"/>
     <col min="37" max="37" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="83"/>
-      <c r="B1" s="83"/>
-      <c r="C1" s="84"/>
+      <c r="A1" s="110"/>
+      <c r="B1" s="110"/>
+      <c r="C1" s="111"/>
       <c r="D1" s="55" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E1" s="36" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="F1" s="37" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="G1" s="36" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="H1" s="36" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="I1" s="36" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="J1" s="37" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="K1" s="55" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="L1" s="36" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="M1" s="37" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="N1" s="36" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="O1" s="36" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="P1" s="36" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="Q1" s="37" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="R1" s="55" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="S1" s="36" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="T1" s="37" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="U1" s="36" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="V1" s="36" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="W1" s="36" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="X1" s="37" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="Y1" s="55" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="Z1" s="36" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="AA1" s="37" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="AB1" s="36" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="AC1" s="36" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="AD1" s="36" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="AE1" s="37" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="AF1" s="55" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="AG1" s="36" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="AH1" s="37"/>
-      <c r="AI1" s="94" t="s">
-        <v>23</v>
-      </c>
-      <c r="AJ1" s="96" t="s">
-        <v>18</v>
-      </c>
-      <c r="AK1" s="98" t="s">
-        <v>19</v>
+      <c r="AI1" s="93" t="s">
+        <v>28</v>
+      </c>
+      <c r="AJ1" s="95" t="s">
+        <v>29</v>
+      </c>
+      <c r="AK1" s="97" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="85"/>
-      <c r="B2" s="85"/>
-      <c r="C2" s="86"/>
+      <c r="A2" s="112"/>
+      <c r="B2" s="112"/>
+      <c r="C2" s="113"/>
       <c r="D2" s="11">
         <v>1</v>
       </c>
@@ -11210,17 +11222,17 @@
       <c r="AH2" s="12">
         <v>31</v>
       </c>
-      <c r="AI2" s="95"/>
-      <c r="AJ2" s="97"/>
-      <c r="AK2" s="99"/>
+      <c r="AI2" s="94"/>
+      <c r="AJ2" s="96"/>
+      <c r="AK2" s="98"/>
     </row>
     <row r="3" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="100" t="s">
+      <c r="A3" s="99" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="100"/>
+      <c r="C3" s="57" t="s">
         <v>0</v>
-      </c>
-      <c r="B3" s="101"/>
-      <c r="C3" s="57" t="s">
-        <v>1</v>
       </c>
       <c r="D3" s="14"/>
       <c r="E3" s="15"/>
@@ -11261,7 +11273,7 @@
       <c r="AF3" s="15"/>
       <c r="AG3" s="17"/>
       <c r="AH3" s="15"/>
-      <c r="AI3" s="104">
+      <c r="AI3" s="103">
         <f>(AJ3+AJ4)/31</f>
         <v>171.7741935483871</v>
       </c>
@@ -11269,15 +11281,15 @@
         <f>SUM(D3:AH3)</f>
         <v>5085</v>
       </c>
-      <c r="AK3" s="106">
+      <c r="AK3" s="105">
         <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="102"/>
-      <c r="B4" s="103"/>
+      <c r="A4" s="101"/>
+      <c r="B4" s="102"/>
       <c r="C4" s="58" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="D4" s="18"/>
       <c r="E4" s="18"/>
@@ -11320,22 +11332,22 @@
       <c r="AF4" s="18"/>
       <c r="AG4" s="19"/>
       <c r="AH4" s="18"/>
-      <c r="AI4" s="105"/>
+      <c r="AI4" s="104"/>
       <c r="AJ4" s="48">
         <f>SUM(D4:AH4)</f>
         <v>240</v>
       </c>
-      <c r="AK4" s="107"/>
+      <c r="AK4" s="106"/>
     </row>
     <row r="5" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="87" t="s">
-        <v>2</v>
-      </c>
-      <c r="B5" s="90" t="s">
-        <v>3</v>
+      <c r="A5" s="114" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="117" t="s">
+        <v>14</v>
       </c>
       <c r="C5" s="59" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="D5" s="21"/>
       <c r="E5" s="2">
@@ -11408,10 +11420,10 @@
       </c>
     </row>
     <row r="6" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="88"/>
-      <c r="B6" s="90"/>
+      <c r="A6" s="115"/>
+      <c r="B6" s="117"/>
       <c r="C6" s="60" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="4">
@@ -11502,10 +11514,10 @@
       </c>
     </row>
     <row r="7" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="88"/>
-      <c r="B7" s="90"/>
+      <c r="A7" s="115"/>
+      <c r="B7" s="117"/>
       <c r="C7" s="60" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D7" s="25"/>
       <c r="E7" s="4"/>
@@ -11560,10 +11572,10 @@
       </c>
     </row>
     <row r="8" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="88"/>
-      <c r="B8" s="90"/>
+      <c r="A8" s="115"/>
+      <c r="B8" s="117"/>
       <c r="C8" s="61" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D8" s="38"/>
       <c r="E8" s="39"/>
@@ -11620,10 +11632,10 @@
       </c>
     </row>
     <row r="9" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="88"/>
-      <c r="B9" s="90"/>
+      <c r="A9" s="115"/>
+      <c r="B9" s="117"/>
       <c r="C9" s="59" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D9" s="21"/>
       <c r="E9" s="2"/>
@@ -11674,10 +11686,10 @@
       </c>
     </row>
     <row r="10" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="88"/>
-      <c r="B10" s="90"/>
+      <c r="A10" s="115"/>
+      <c r="B10" s="117"/>
       <c r="C10" s="60" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="4"/>
@@ -11724,10 +11736,10 @@
       </c>
     </row>
     <row r="11" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="88"/>
-      <c r="B11" s="90"/>
+      <c r="A11" s="115"/>
+      <c r="B11" s="117"/>
       <c r="C11" s="60" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="D11" s="21"/>
       <c r="E11" s="2"/>
@@ -11778,12 +11790,12 @@
       </c>
     </row>
     <row r="12" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="88"/>
-      <c r="B12" s="91" t="s">
-        <v>4</v>
+      <c r="A12" s="115"/>
+      <c r="B12" s="121" t="s">
+        <v>21</v>
       </c>
       <c r="C12" s="62" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D12" s="6"/>
       <c r="E12" s="6"/>
@@ -11838,10 +11850,10 @@
       </c>
     </row>
     <row r="13" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="88"/>
-      <c r="B13" s="92"/>
+      <c r="A13" s="115"/>
+      <c r="B13" s="122"/>
       <c r="C13" s="62" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D13" s="28"/>
       <c r="E13" s="8"/>
@@ -11892,10 +11904,10 @@
       </c>
     </row>
     <row r="14" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="88"/>
-      <c r="B14" s="92"/>
+      <c r="A14" s="115"/>
+      <c r="B14" s="122"/>
       <c r="C14" s="56" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D14" s="6"/>
       <c r="E14" s="6"/>
@@ -11944,10 +11956,10 @@
       </c>
     </row>
     <row r="15" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="88"/>
-      <c r="B15" s="93"/>
+      <c r="A15" s="115"/>
+      <c r="B15" s="123"/>
       <c r="C15" s="62" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="D15" s="51"/>
       <c r="E15" s="51"/>
@@ -11996,56 +12008,56 @@
       </c>
     </row>
     <row r="16" spans="1:37" ht="18.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="89"/>
-      <c r="B16" s="80" t="s">
-        <v>10</v>
-      </c>
-      <c r="C16" s="81"/>
-      <c r="D16" s="80">
+      <c r="A16" s="116"/>
+      <c r="B16" s="107" t="s">
+        <v>24</v>
+      </c>
+      <c r="C16" s="108"/>
+      <c r="D16" s="107">
         <f>SUM(D5:J15)</f>
         <v>519</v>
       </c>
-      <c r="E16" s="81"/>
-      <c r="F16" s="81"/>
-      <c r="G16" s="81"/>
-      <c r="H16" s="81"/>
-      <c r="I16" s="81"/>
-      <c r="J16" s="82"/>
-      <c r="K16" s="80">
+      <c r="E16" s="108"/>
+      <c r="F16" s="108"/>
+      <c r="G16" s="108"/>
+      <c r="H16" s="108"/>
+      <c r="I16" s="108"/>
+      <c r="J16" s="109"/>
+      <c r="K16" s="107">
         <f>SUM(K5:Q15)</f>
         <v>629</v>
       </c>
-      <c r="L16" s="81"/>
-      <c r="M16" s="81"/>
-      <c r="N16" s="81"/>
-      <c r="O16" s="81"/>
-      <c r="P16" s="81"/>
-      <c r="Q16" s="82"/>
-      <c r="R16" s="80">
+      <c r="L16" s="108"/>
+      <c r="M16" s="108"/>
+      <c r="N16" s="108"/>
+      <c r="O16" s="108"/>
+      <c r="P16" s="108"/>
+      <c r="Q16" s="109"/>
+      <c r="R16" s="107">
         <f>SUM(R5:X15)</f>
         <v>653</v>
       </c>
-      <c r="S16" s="81"/>
-      <c r="T16" s="81"/>
-      <c r="U16" s="81"/>
-      <c r="V16" s="81"/>
-      <c r="W16" s="81"/>
-      <c r="X16" s="82"/>
-      <c r="Y16" s="80">
+      <c r="S16" s="108"/>
+      <c r="T16" s="108"/>
+      <c r="U16" s="108"/>
+      <c r="V16" s="108"/>
+      <c r="W16" s="108"/>
+      <c r="X16" s="109"/>
+      <c r="Y16" s="107">
         <f>SUM(Y5:AE15)</f>
         <v>201</v>
       </c>
-      <c r="Z16" s="81"/>
-      <c r="AA16" s="81"/>
-      <c r="AB16" s="81"/>
-      <c r="AC16" s="81"/>
-      <c r="AD16" s="81"/>
-      <c r="AE16" s="82"/>
-      <c r="AF16" s="80">
+      <c r="Z16" s="108"/>
+      <c r="AA16" s="108"/>
+      <c r="AB16" s="108"/>
+      <c r="AC16" s="108"/>
+      <c r="AD16" s="108"/>
+      <c r="AE16" s="109"/>
+      <c r="AF16" s="107">
         <f>SUM(AF5:AG15)</f>
         <v>469</v>
       </c>
-      <c r="AG16" s="82"/>
+      <c r="AG16" s="109"/>
       <c r="AH16" s="66"/>
       <c r="AI16" s="53">
         <f t="shared" si="0"/>
@@ -12061,153 +12073,146 @@
       </c>
     </row>
     <row r="17" spans="1:37" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="114" t="s">
+      <c r="A17" s="86" t="s">
+        <v>25</v>
+      </c>
+      <c r="B17" s="86"/>
+      <c r="C17" s="87"/>
+      <c r="D17" s="88">
+        <v>4095</v>
+      </c>
+      <c r="E17" s="89"/>
+      <c r="F17" s="89"/>
+      <c r="G17" s="89"/>
+      <c r="H17" s="89"/>
+      <c r="I17" s="89"/>
+      <c r="J17" s="89"/>
+      <c r="K17" s="89"/>
+      <c r="L17" s="89"/>
+      <c r="M17" s="89"/>
+      <c r="N17" s="89"/>
+      <c r="O17" s="89"/>
+      <c r="P17" s="89"/>
+      <c r="Q17" s="89"/>
+      <c r="R17" s="89"/>
+      <c r="S17" s="89"/>
+      <c r="T17" s="89"/>
+      <c r="U17" s="89"/>
+      <c r="V17" s="89"/>
+      <c r="W17" s="89"/>
+      <c r="X17" s="89"/>
+      <c r="Y17" s="89"/>
+      <c r="Z17" s="89"/>
+      <c r="AA17" s="89"/>
+      <c r="AB17" s="89"/>
+      <c r="AC17" s="89"/>
+      <c r="AD17" s="89"/>
+      <c r="AE17" s="89"/>
+      <c r="AF17" s="89"/>
+      <c r="AG17" s="89"/>
+      <c r="AH17" s="89"/>
+      <c r="AI17" s="90"/>
+      <c r="AJ17" s="91"/>
+      <c r="AK17" s="72"/>
+    </row>
+    <row r="18" spans="1:37" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="81" t="s">
         <v>26</v>
       </c>
-      <c r="B17" s="114"/>
-      <c r="C17" s="115"/>
-      <c r="D17" s="116">
-        <v>4095</v>
-      </c>
-      <c r="E17" s="117"/>
-      <c r="F17" s="117"/>
-      <c r="G17" s="117"/>
-      <c r="H17" s="117"/>
-      <c r="I17" s="117"/>
-      <c r="J17" s="117"/>
-      <c r="K17" s="117"/>
-      <c r="L17" s="117"/>
-      <c r="M17" s="117"/>
-      <c r="N17" s="117"/>
-      <c r="O17" s="117"/>
-      <c r="P17" s="117"/>
-      <c r="Q17" s="117"/>
-      <c r="R17" s="117"/>
-      <c r="S17" s="117"/>
-      <c r="T17" s="117"/>
-      <c r="U17" s="117"/>
-      <c r="V17" s="117"/>
-      <c r="W17" s="117"/>
-      <c r="X17" s="117"/>
-      <c r="Y17" s="117"/>
-      <c r="Z17" s="117"/>
-      <c r="AA17" s="117"/>
-      <c r="AB17" s="117"/>
-      <c r="AC17" s="117"/>
-      <c r="AD17" s="117"/>
-      <c r="AE17" s="117"/>
-      <c r="AF17" s="117"/>
-      <c r="AG17" s="117"/>
-      <c r="AH17" s="117"/>
-      <c r="AI17" s="118"/>
-      <c r="AJ17" s="119"/>
-      <c r="AK17" s="72"/>
-    </row>
-    <row r="18" spans="1:37" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="109" t="s">
-        <v>20</v>
-      </c>
-      <c r="B18" s="109"/>
-      <c r="C18" s="110"/>
-      <c r="D18" s="120">
+      <c r="B18" s="81"/>
+      <c r="C18" s="82"/>
+      <c r="D18" s="92">
         <f>((AJ3+AJ4+D17)-AJ16)-D17</f>
         <v>2854</v>
       </c>
-      <c r="E18" s="118"/>
-      <c r="F18" s="118"/>
-      <c r="G18" s="118"/>
-      <c r="H18" s="118"/>
-      <c r="I18" s="118"/>
-      <c r="J18" s="118"/>
-      <c r="K18" s="118"/>
-      <c r="L18" s="118"/>
-      <c r="M18" s="118"/>
-      <c r="N18" s="118"/>
-      <c r="O18" s="118"/>
-      <c r="P18" s="118"/>
-      <c r="Q18" s="118"/>
-      <c r="R18" s="118"/>
-      <c r="S18" s="118"/>
-      <c r="T18" s="118"/>
-      <c r="U18" s="118"/>
-      <c r="V18" s="118"/>
-      <c r="W18" s="118"/>
-      <c r="X18" s="118"/>
-      <c r="Y18" s="118"/>
-      <c r="Z18" s="118"/>
-      <c r="AA18" s="118"/>
-      <c r="AB18" s="118"/>
-      <c r="AC18" s="118"/>
-      <c r="AD18" s="118"/>
-      <c r="AE18" s="118"/>
-      <c r="AF18" s="118"/>
-      <c r="AG18" s="118"/>
-      <c r="AH18" s="118"/>
-      <c r="AI18" s="118"/>
-      <c r="AJ18" s="119"/>
+      <c r="E18" s="90"/>
+      <c r="F18" s="90"/>
+      <c r="G18" s="90"/>
+      <c r="H18" s="90"/>
+      <c r="I18" s="90"/>
+      <c r="J18" s="90"/>
+      <c r="K18" s="90"/>
+      <c r="L18" s="90"/>
+      <c r="M18" s="90"/>
+      <c r="N18" s="90"/>
+      <c r="O18" s="90"/>
+      <c r="P18" s="90"/>
+      <c r="Q18" s="90"/>
+      <c r="R18" s="90"/>
+      <c r="S18" s="90"/>
+      <c r="T18" s="90"/>
+      <c r="U18" s="90"/>
+      <c r="V18" s="90"/>
+      <c r="W18" s="90"/>
+      <c r="X18" s="90"/>
+      <c r="Y18" s="90"/>
+      <c r="Z18" s="90"/>
+      <c r="AA18" s="90"/>
+      <c r="AB18" s="90"/>
+      <c r="AC18" s="90"/>
+      <c r="AD18" s="90"/>
+      <c r="AE18" s="90"/>
+      <c r="AF18" s="90"/>
+      <c r="AG18" s="90"/>
+      <c r="AH18" s="90"/>
+      <c r="AI18" s="90"/>
+      <c r="AJ18" s="91"/>
       <c r="AK18" s="31">
         <f>((AJ3+AJ4-AJ16)/(AJ3+AJ4))*100</f>
         <v>53.596244131455393</v>
       </c>
     </row>
     <row r="19" spans="1:37" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="108" t="s">
+      <c r="A19" s="80" t="s">
         <v>27</v>
       </c>
-      <c r="B19" s="109"/>
-      <c r="C19" s="110"/>
-      <c r="D19" s="111">
+      <c r="B19" s="81"/>
+      <c r="C19" s="82"/>
+      <c r="D19" s="83">
         <f>(AJ3+AJ4+D17)-AJ16</f>
         <v>6949</v>
       </c>
-      <c r="E19" s="112"/>
-      <c r="F19" s="112"/>
-      <c r="G19" s="112"/>
-      <c r="H19" s="112"/>
-      <c r="I19" s="112"/>
-      <c r="J19" s="112"/>
-      <c r="K19" s="112"/>
-      <c r="L19" s="112"/>
-      <c r="M19" s="112"/>
-      <c r="N19" s="112"/>
-      <c r="O19" s="112"/>
-      <c r="P19" s="112"/>
-      <c r="Q19" s="112"/>
-      <c r="R19" s="112"/>
-      <c r="S19" s="112"/>
-      <c r="T19" s="112"/>
-      <c r="U19" s="112"/>
-      <c r="V19" s="112"/>
-      <c r="W19" s="112"/>
-      <c r="X19" s="112"/>
-      <c r="Y19" s="112"/>
-      <c r="Z19" s="112"/>
-      <c r="AA19" s="112"/>
-      <c r="AB19" s="112"/>
-      <c r="AC19" s="112"/>
-      <c r="AD19" s="112"/>
-      <c r="AE19" s="112"/>
-      <c r="AF19" s="112"/>
-      <c r="AG19" s="112"/>
-      <c r="AH19" s="112"/>
-      <c r="AI19" s="112"/>
-      <c r="AJ19" s="113"/>
+      <c r="E19" s="84"/>
+      <c r="F19" s="84"/>
+      <c r="G19" s="84"/>
+      <c r="H19" s="84"/>
+      <c r="I19" s="84"/>
+      <c r="J19" s="84"/>
+      <c r="K19" s="84"/>
+      <c r="L19" s="84"/>
+      <c r="M19" s="84"/>
+      <c r="N19" s="84"/>
+      <c r="O19" s="84"/>
+      <c r="P19" s="84"/>
+      <c r="Q19" s="84"/>
+      <c r="R19" s="84"/>
+      <c r="S19" s="84"/>
+      <c r="T19" s="84"/>
+      <c r="U19" s="84"/>
+      <c r="V19" s="84"/>
+      <c r="W19" s="84"/>
+      <c r="X19" s="84"/>
+      <c r="Y19" s="84"/>
+      <c r="Z19" s="84"/>
+      <c r="AA19" s="84"/>
+      <c r="AB19" s="84"/>
+      <c r="AC19" s="84"/>
+      <c r="AD19" s="84"/>
+      <c r="AE19" s="84"/>
+      <c r="AF19" s="84"/>
+      <c r="AG19" s="84"/>
+      <c r="AH19" s="84"/>
+      <c r="AI19" s="84"/>
+      <c r="AJ19" s="85"/>
       <c r="AK19" s="54"/>
     </row>
     <row r="24" spans="1:37" x14ac:dyDescent="0.3">
       <c r="S24" s="1" t="s">
-        <v>29</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="A1:C2"/>
-    <mergeCell ref="AI1:AI2"/>
-    <mergeCell ref="AJ1:AJ2"/>
-    <mergeCell ref="AK1:AK2"/>
-    <mergeCell ref="A3:B4"/>
-    <mergeCell ref="AI3:AI4"/>
-    <mergeCell ref="AK3:AK4"/>
     <mergeCell ref="A19:C19"/>
     <mergeCell ref="D19:AJ19"/>
     <mergeCell ref="D16:J16"/>
@@ -12223,6 +12228,13 @@
     <mergeCell ref="B5:B11"/>
     <mergeCell ref="B12:B15"/>
     <mergeCell ref="B16:C16"/>
+    <mergeCell ref="A1:C2"/>
+    <mergeCell ref="AI1:AI2"/>
+    <mergeCell ref="AJ1:AJ2"/>
+    <mergeCell ref="AK1:AK2"/>
+    <mergeCell ref="A3:B4"/>
+    <mergeCell ref="AI3:AI4"/>
+    <mergeCell ref="AK3:AK4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -12238,123 +12250,123 @@
     <col min="2" max="2" width="6.140625" style="1" customWidth="1"/>
     <col min="3" max="3" width="19.28515625" style="1" customWidth="1"/>
     <col min="4" max="34" width="5.7109375" style="1" customWidth="1"/>
-    <col min="35" max="35" width="8.85546875" style="1" customWidth="1"/>
+    <col min="35" max="35" width="11.85546875" style="1" customWidth="1"/>
     <col min="36" max="36" width="10.140625" style="1" customWidth="1"/>
     <col min="37" max="37" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="83"/>
-      <c r="B1" s="83"/>
-      <c r="C1" s="84"/>
+      <c r="A1" s="110"/>
+      <c r="B1" s="110"/>
+      <c r="C1" s="111"/>
       <c r="D1" s="37" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E1" s="36" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="F1" s="36" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G1" s="36" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="H1" s="37" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="I1" s="55" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="J1" s="36" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="K1" s="37" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="L1" s="36" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="M1" s="36" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="N1" s="36" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="O1" s="37" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="P1" s="55" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="Q1" s="36" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="R1" s="37" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="S1" s="36" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="T1" s="36" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="U1" s="36" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="V1" s="37" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="W1" s="55" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="X1" s="36" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="Y1" s="37" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="Z1" s="36" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="AA1" s="36" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="AB1" s="36" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="AC1" s="37" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="AD1" s="55" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="AE1" s="36" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="AF1" s="37" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="AG1" s="36" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="AH1" s="36" t="s">
-        <v>13</v>
-      </c>
-      <c r="AI1" s="94" t="s">
-        <v>23</v>
-      </c>
-      <c r="AJ1" s="96" t="s">
-        <v>18</v>
-      </c>
-      <c r="AK1" s="98" t="s">
-        <v>19</v>
+        <v>4</v>
+      </c>
+      <c r="AI1" s="93" t="s">
+        <v>28</v>
+      </c>
+      <c r="AJ1" s="95" t="s">
+        <v>29</v>
+      </c>
+      <c r="AK1" s="97" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="85"/>
-      <c r="B2" s="85"/>
-      <c r="C2" s="86"/>
+      <c r="A2" s="112"/>
+      <c r="B2" s="112"/>
+      <c r="C2" s="113"/>
       <c r="D2" s="11">
         <v>1</v>
       </c>
@@ -12448,17 +12460,17 @@
       <c r="AH2" s="12">
         <v>31</v>
       </c>
-      <c r="AI2" s="95"/>
-      <c r="AJ2" s="97"/>
-      <c r="AK2" s="99"/>
+      <c r="AI2" s="94"/>
+      <c r="AJ2" s="96"/>
+      <c r="AK2" s="98"/>
     </row>
     <row r="3" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="100" t="s">
+      <c r="A3" s="99" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="100"/>
+      <c r="C3" s="57" t="s">
         <v>0</v>
-      </c>
-      <c r="B3" s="101"/>
-      <c r="C3" s="57" t="s">
-        <v>1</v>
       </c>
       <c r="D3" s="14">
         <v>508</v>
@@ -12495,7 +12507,7 @@
       <c r="AF3" s="15"/>
       <c r="AG3" s="17"/>
       <c r="AH3" s="15"/>
-      <c r="AI3" s="104">
+      <c r="AI3" s="103">
         <f>(AJ3+AJ4)/31</f>
         <v>88.548387096774192</v>
       </c>
@@ -12503,15 +12515,15 @@
         <f>SUM(D3:AH3)</f>
         <v>1772</v>
       </c>
-      <c r="AK3" s="106">
+      <c r="AK3" s="105">
         <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="102"/>
-      <c r="B4" s="103"/>
+      <c r="A4" s="101"/>
+      <c r="B4" s="102"/>
       <c r="C4" s="58" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="D4" s="18"/>
       <c r="E4" s="18"/>
@@ -12558,22 +12570,22 @@
       <c r="AH4" s="18">
         <v>11</v>
       </c>
-      <c r="AI4" s="105"/>
+      <c r="AI4" s="104"/>
       <c r="AJ4" s="48">
         <f>SUM(D4:AH4)</f>
         <v>973</v>
       </c>
-      <c r="AK4" s="107"/>
+      <c r="AK4" s="106"/>
     </row>
     <row r="5" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="87" t="s">
-        <v>2</v>
-      </c>
-      <c r="B5" s="90" t="s">
-        <v>3</v>
+      <c r="A5" s="114" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="117" t="s">
+        <v>14</v>
       </c>
       <c r="C5" s="59" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="D5" s="21">
         <v>4</v>
@@ -12654,10 +12666,10 @@
       </c>
     </row>
     <row r="6" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="88"/>
-      <c r="B6" s="90"/>
+      <c r="A6" s="115"/>
+      <c r="B6" s="117"/>
       <c r="C6" s="60" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D6" s="4">
         <v>35</v>
@@ -12738,10 +12750,10 @@
       </c>
     </row>
     <row r="7" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="88"/>
-      <c r="B7" s="90"/>
+      <c r="A7" s="115"/>
+      <c r="B7" s="117"/>
       <c r="C7" s="60" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D7" s="25">
         <v>76</v>
@@ -12796,10 +12808,10 @@
       </c>
     </row>
     <row r="8" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="88"/>
-      <c r="B8" s="90"/>
+      <c r="A8" s="115"/>
+      <c r="B8" s="117"/>
       <c r="C8" s="61" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D8" s="38"/>
       <c r="E8" s="39">
@@ -12852,10 +12864,10 @@
       </c>
     </row>
     <row r="9" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="88"/>
-      <c r="B9" s="90"/>
+      <c r="A9" s="115"/>
+      <c r="B9" s="117"/>
       <c r="C9" s="59" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D9" s="21"/>
       <c r="E9" s="2"/>
@@ -12904,10 +12916,10 @@
       </c>
     </row>
     <row r="10" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="88"/>
-      <c r="B10" s="90"/>
+      <c r="A10" s="115"/>
+      <c r="B10" s="117"/>
       <c r="C10" s="60" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="4"/>
@@ -12954,10 +12966,10 @@
       </c>
     </row>
     <row r="11" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="88"/>
-      <c r="B11" s="90"/>
+      <c r="A11" s="115"/>
+      <c r="B11" s="117"/>
       <c r="C11" s="60" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="D11" s="21"/>
       <c r="E11" s="2"/>
@@ -13014,12 +13026,12 @@
       </c>
     </row>
     <row r="12" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="88"/>
-      <c r="B12" s="91" t="s">
-        <v>4</v>
+      <c r="A12" s="115"/>
+      <c r="B12" s="121" t="s">
+        <v>21</v>
       </c>
       <c r="C12" s="62" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D12" s="6"/>
       <c r="E12" s="6">
@@ -13098,10 +13110,10 @@
       </c>
     </row>
     <row r="13" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="88"/>
-      <c r="B13" s="92"/>
+      <c r="A13" s="115"/>
+      <c r="B13" s="122"/>
       <c r="C13" s="62" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D13" s="28"/>
       <c r="E13" s="8">
@@ -13156,10 +13168,10 @@
       </c>
     </row>
     <row r="14" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="88"/>
-      <c r="B14" s="92"/>
+      <c r="A14" s="115"/>
+      <c r="B14" s="122"/>
       <c r="C14" s="56" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D14" s="6">
         <v>195</v>
@@ -13224,10 +13236,10 @@
       </c>
     </row>
     <row r="15" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="88"/>
-      <c r="B15" s="93"/>
+      <c r="A15" s="115"/>
+      <c r="B15" s="123"/>
       <c r="C15" s="62" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="D15" s="51"/>
       <c r="E15" s="51"/>
@@ -13284,57 +13296,57 @@
       </c>
     </row>
     <row r="16" spans="1:37" ht="18.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="89"/>
-      <c r="B16" s="80" t="s">
-        <v>10</v>
-      </c>
-      <c r="C16" s="81"/>
-      <c r="D16" s="80">
+      <c r="A16" s="116"/>
+      <c r="B16" s="107" t="s">
+        <v>24</v>
+      </c>
+      <c r="C16" s="108"/>
+      <c r="D16" s="107">
         <f>SUM(D5:H15)+469</f>
         <v>1563</v>
       </c>
-      <c r="E16" s="81"/>
-      <c r="F16" s="81"/>
-      <c r="G16" s="81"/>
-      <c r="H16" s="82"/>
-      <c r="I16" s="80">
+      <c r="E16" s="108"/>
+      <c r="F16" s="108"/>
+      <c r="G16" s="108"/>
+      <c r="H16" s="109"/>
+      <c r="I16" s="107">
         <f>SUM(I5:O15)</f>
         <v>2230</v>
       </c>
-      <c r="J16" s="81"/>
-      <c r="K16" s="81"/>
-      <c r="L16" s="81"/>
-      <c r="M16" s="81"/>
-      <c r="N16" s="81"/>
-      <c r="O16" s="82"/>
-      <c r="P16" s="80">
+      <c r="J16" s="108"/>
+      <c r="K16" s="108"/>
+      <c r="L16" s="108"/>
+      <c r="M16" s="108"/>
+      <c r="N16" s="108"/>
+      <c r="O16" s="109"/>
+      <c r="P16" s="107">
         <f>SUM(P5:V15)</f>
         <v>1162</v>
       </c>
-      <c r="Q16" s="81"/>
-      <c r="R16" s="81"/>
-      <c r="S16" s="81"/>
-      <c r="T16" s="81"/>
-      <c r="U16" s="81"/>
-      <c r="V16" s="82"/>
-      <c r="W16" s="80">
+      <c r="Q16" s="108"/>
+      <c r="R16" s="108"/>
+      <c r="S16" s="108"/>
+      <c r="T16" s="108"/>
+      <c r="U16" s="108"/>
+      <c r="V16" s="109"/>
+      <c r="W16" s="107">
         <f>SUM(W5:AC15)</f>
         <v>1747</v>
       </c>
-      <c r="X16" s="81"/>
-      <c r="Y16" s="81"/>
-      <c r="Z16" s="81"/>
-      <c r="AA16" s="81"/>
-      <c r="AB16" s="81"/>
-      <c r="AC16" s="82"/>
-      <c r="AD16" s="80">
+      <c r="X16" s="108"/>
+      <c r="Y16" s="108"/>
+      <c r="Z16" s="108"/>
+      <c r="AA16" s="108"/>
+      <c r="AB16" s="108"/>
+      <c r="AC16" s="109"/>
+      <c r="AD16" s="107">
         <f>SUM(AD5:AH15)</f>
         <v>531</v>
       </c>
-      <c r="AE16" s="81"/>
-      <c r="AF16" s="81"/>
-      <c r="AG16" s="81"/>
-      <c r="AH16" s="82"/>
+      <c r="AE16" s="108"/>
+      <c r="AF16" s="108"/>
+      <c r="AG16" s="108"/>
+      <c r="AH16" s="109"/>
       <c r="AI16" s="53">
         <f t="shared" si="0"/>
         <v>218.19354838709677</v>
@@ -13349,158 +13361,146 @@
       </c>
     </row>
     <row r="17" spans="1:37" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="114" t="s">
+      <c r="A17" s="86" t="s">
+        <v>25</v>
+      </c>
+      <c r="B17" s="86"/>
+      <c r="C17" s="87"/>
+      <c r="D17" s="88">
+        <v>6949</v>
+      </c>
+      <c r="E17" s="89"/>
+      <c r="F17" s="89"/>
+      <c r="G17" s="89"/>
+      <c r="H17" s="89"/>
+      <c r="I17" s="89"/>
+      <c r="J17" s="89"/>
+      <c r="K17" s="89"/>
+      <c r="L17" s="89"/>
+      <c r="M17" s="89"/>
+      <c r="N17" s="89"/>
+      <c r="O17" s="89"/>
+      <c r="P17" s="89"/>
+      <c r="Q17" s="89"/>
+      <c r="R17" s="89"/>
+      <c r="S17" s="89"/>
+      <c r="T17" s="89"/>
+      <c r="U17" s="89"/>
+      <c r="V17" s="89"/>
+      <c r="W17" s="89"/>
+      <c r="X17" s="89"/>
+      <c r="Y17" s="89"/>
+      <c r="Z17" s="89"/>
+      <c r="AA17" s="89"/>
+      <c r="AB17" s="89"/>
+      <c r="AC17" s="89"/>
+      <c r="AD17" s="89"/>
+      <c r="AE17" s="89"/>
+      <c r="AF17" s="89"/>
+      <c r="AG17" s="89"/>
+      <c r="AH17" s="89"/>
+      <c r="AI17" s="90"/>
+      <c r="AJ17" s="91"/>
+      <c r="AK17" s="73"/>
+    </row>
+    <row r="18" spans="1:37" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="81" t="s">
         <v>26</v>
       </c>
-      <c r="B17" s="114"/>
-      <c r="C17" s="115"/>
-      <c r="D17" s="116">
-        <v>6949</v>
-      </c>
-      <c r="E17" s="117"/>
-      <c r="F17" s="117"/>
-      <c r="G17" s="117"/>
-      <c r="H17" s="117"/>
-      <c r="I17" s="117"/>
-      <c r="J17" s="117"/>
-      <c r="K17" s="117"/>
-      <c r="L17" s="117"/>
-      <c r="M17" s="117"/>
-      <c r="N17" s="117"/>
-      <c r="O17" s="117"/>
-      <c r="P17" s="117"/>
-      <c r="Q17" s="117"/>
-      <c r="R17" s="117"/>
-      <c r="S17" s="117"/>
-      <c r="T17" s="117"/>
-      <c r="U17" s="117"/>
-      <c r="V17" s="117"/>
-      <c r="W17" s="117"/>
-      <c r="X17" s="117"/>
-      <c r="Y17" s="117"/>
-      <c r="Z17" s="117"/>
-      <c r="AA17" s="117"/>
-      <c r="AB17" s="117"/>
-      <c r="AC17" s="117"/>
-      <c r="AD17" s="117"/>
-      <c r="AE17" s="117"/>
-      <c r="AF17" s="117"/>
-      <c r="AG17" s="117"/>
-      <c r="AH17" s="117"/>
-      <c r="AI17" s="118"/>
-      <c r="AJ17" s="119"/>
-      <c r="AK17" s="73"/>
-    </row>
-    <row r="18" spans="1:37" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="109" t="s">
-        <v>20</v>
-      </c>
-      <c r="B18" s="109"/>
-      <c r="C18" s="110"/>
-      <c r="D18" s="120">
+      <c r="B18" s="81"/>
+      <c r="C18" s="82"/>
+      <c r="D18" s="92">
         <f>((AJ3+AJ4+D17)-AJ16)-D17</f>
         <v>-4019</v>
       </c>
-      <c r="E18" s="118"/>
-      <c r="F18" s="118"/>
-      <c r="G18" s="118"/>
-      <c r="H18" s="118"/>
-      <c r="I18" s="118"/>
-      <c r="J18" s="118"/>
-      <c r="K18" s="118"/>
-      <c r="L18" s="118"/>
-      <c r="M18" s="118"/>
-      <c r="N18" s="118"/>
-      <c r="O18" s="118"/>
-      <c r="P18" s="118"/>
-      <c r="Q18" s="118"/>
-      <c r="R18" s="118"/>
-      <c r="S18" s="118"/>
-      <c r="T18" s="118"/>
-      <c r="U18" s="118"/>
-      <c r="V18" s="118"/>
-      <c r="W18" s="118"/>
-      <c r="X18" s="118"/>
-      <c r="Y18" s="118"/>
-      <c r="Z18" s="118"/>
-      <c r="AA18" s="118"/>
-      <c r="AB18" s="118"/>
-      <c r="AC18" s="118"/>
-      <c r="AD18" s="118"/>
-      <c r="AE18" s="118"/>
-      <c r="AF18" s="118"/>
-      <c r="AG18" s="118"/>
-      <c r="AH18" s="118"/>
-      <c r="AI18" s="118"/>
-      <c r="AJ18" s="119"/>
+      <c r="E18" s="90"/>
+      <c r="F18" s="90"/>
+      <c r="G18" s="90"/>
+      <c r="H18" s="90"/>
+      <c r="I18" s="90"/>
+      <c r="J18" s="90"/>
+      <c r="K18" s="90"/>
+      <c r="L18" s="90"/>
+      <c r="M18" s="90"/>
+      <c r="N18" s="90"/>
+      <c r="O18" s="90"/>
+      <c r="P18" s="90"/>
+      <c r="Q18" s="90"/>
+      <c r="R18" s="90"/>
+      <c r="S18" s="90"/>
+      <c r="T18" s="90"/>
+      <c r="U18" s="90"/>
+      <c r="V18" s="90"/>
+      <c r="W18" s="90"/>
+      <c r="X18" s="90"/>
+      <c r="Y18" s="90"/>
+      <c r="Z18" s="90"/>
+      <c r="AA18" s="90"/>
+      <c r="AB18" s="90"/>
+      <c r="AC18" s="90"/>
+      <c r="AD18" s="90"/>
+      <c r="AE18" s="90"/>
+      <c r="AF18" s="90"/>
+      <c r="AG18" s="90"/>
+      <c r="AH18" s="90"/>
+      <c r="AI18" s="90"/>
+      <c r="AJ18" s="91"/>
       <c r="AK18" s="31">
         <f>((AJ3+AJ4-AJ16)/(AJ3+AJ4))*100</f>
         <v>-146.41165755919855</v>
       </c>
     </row>
     <row r="19" spans="1:37" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="108" t="s">
+      <c r="A19" s="80" t="s">
         <v>27</v>
       </c>
-      <c r="B19" s="109"/>
-      <c r="C19" s="110"/>
-      <c r="D19" s="111">
+      <c r="B19" s="81"/>
+      <c r="C19" s="82"/>
+      <c r="D19" s="83">
         <f>(AJ3+AJ4+D17)-AJ16</f>
         <v>2930</v>
       </c>
-      <c r="E19" s="112"/>
-      <c r="F19" s="112"/>
-      <c r="G19" s="112"/>
-      <c r="H19" s="112"/>
-      <c r="I19" s="112"/>
-      <c r="J19" s="112"/>
-      <c r="K19" s="112"/>
-      <c r="L19" s="112"/>
-      <c r="M19" s="112"/>
-      <c r="N19" s="112"/>
-      <c r="O19" s="112"/>
-      <c r="P19" s="112"/>
-      <c r="Q19" s="112"/>
-      <c r="R19" s="112"/>
-      <c r="S19" s="112"/>
-      <c r="T19" s="112"/>
-      <c r="U19" s="112"/>
-      <c r="V19" s="112"/>
-      <c r="W19" s="112"/>
-      <c r="X19" s="112"/>
-      <c r="Y19" s="112"/>
-      <c r="Z19" s="112"/>
-      <c r="AA19" s="112"/>
-      <c r="AB19" s="112"/>
-      <c r="AC19" s="112"/>
-      <c r="AD19" s="112"/>
-      <c r="AE19" s="112"/>
-      <c r="AF19" s="112"/>
-      <c r="AG19" s="112"/>
-      <c r="AH19" s="112"/>
-      <c r="AI19" s="112"/>
-      <c r="AJ19" s="113"/>
+      <c r="E19" s="84"/>
+      <c r="F19" s="84"/>
+      <c r="G19" s="84"/>
+      <c r="H19" s="84"/>
+      <c r="I19" s="84"/>
+      <c r="J19" s="84"/>
+      <c r="K19" s="84"/>
+      <c r="L19" s="84"/>
+      <c r="M19" s="84"/>
+      <c r="N19" s="84"/>
+      <c r="O19" s="84"/>
+      <c r="P19" s="84"/>
+      <c r="Q19" s="84"/>
+      <c r="R19" s="84"/>
+      <c r="S19" s="84"/>
+      <c r="T19" s="84"/>
+      <c r="U19" s="84"/>
+      <c r="V19" s="84"/>
+      <c r="W19" s="84"/>
+      <c r="X19" s="84"/>
+      <c r="Y19" s="84"/>
+      <c r="Z19" s="84"/>
+      <c r="AA19" s="84"/>
+      <c r="AB19" s="84"/>
+      <c r="AC19" s="84"/>
+      <c r="AD19" s="84"/>
+      <c r="AE19" s="84"/>
+      <c r="AF19" s="84"/>
+      <c r="AG19" s="84"/>
+      <c r="AH19" s="84"/>
+      <c r="AI19" s="84"/>
+      <c r="AJ19" s="85"/>
       <c r="AK19" s="54"/>
     </row>
     <row r="24" spans="1:37" x14ac:dyDescent="0.3">
       <c r="S24" s="1" t="s">
-        <v>29</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="D19:AJ19"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="D17:AJ17"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="D18:AJ18"/>
-    <mergeCell ref="AI1:AI2"/>
-    <mergeCell ref="AJ1:AJ2"/>
-    <mergeCell ref="AK1:AK2"/>
-    <mergeCell ref="A3:B4"/>
-    <mergeCell ref="AI3:AI4"/>
-    <mergeCell ref="AK3:AK4"/>
     <mergeCell ref="I16:O16"/>
     <mergeCell ref="P16:V16"/>
     <mergeCell ref="W16:AC16"/>
@@ -13511,6 +13511,18 @@
     <mergeCell ref="B12:B15"/>
     <mergeCell ref="B16:C16"/>
     <mergeCell ref="D16:H16"/>
+    <mergeCell ref="AI1:AI2"/>
+    <mergeCell ref="AJ1:AJ2"/>
+    <mergeCell ref="AK1:AK2"/>
+    <mergeCell ref="A3:B4"/>
+    <mergeCell ref="AI3:AI4"/>
+    <mergeCell ref="AK3:AK4"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="D19:AJ19"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="D17:AJ17"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="D18:AJ18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -13526,123 +13538,123 @@
     <col min="2" max="2" width="6.140625" style="1" customWidth="1"/>
     <col min="3" max="3" width="19.28515625" style="1" customWidth="1"/>
     <col min="4" max="34" width="5.7109375" style="1" customWidth="1"/>
-    <col min="35" max="35" width="8.85546875" style="1" customWidth="1"/>
+    <col min="35" max="35" width="12" style="1" customWidth="1"/>
     <col min="36" max="36" width="10.140625" style="1" customWidth="1"/>
     <col min="37" max="37" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="83"/>
-      <c r="B1" s="83"/>
-      <c r="C1" s="84"/>
+      <c r="A1" s="110"/>
+      <c r="B1" s="110"/>
+      <c r="C1" s="111"/>
       <c r="D1" s="36" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E1" s="37" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="F1" s="55" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="G1" s="36" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="H1" s="37" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="I1" s="36" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="J1" s="36" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="K1" s="36" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="L1" s="37" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="M1" s="55" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="N1" s="36" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="O1" s="37" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="P1" s="36" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="Q1" s="36" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="R1" s="36" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="S1" s="37" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="T1" s="55" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="U1" s="36" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="V1" s="37" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="W1" s="36" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="X1" s="36" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="Y1" s="36" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="Z1" s="37" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="AA1" s="55" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="AB1" s="36" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="AC1" s="37" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="AD1" s="36" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="AE1" s="36" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="AF1" s="36" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="AG1" s="37" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="AH1" s="55" t="s">
-        <v>17</v>
-      </c>
-      <c r="AI1" s="94" t="s">
-        <v>23</v>
-      </c>
-      <c r="AJ1" s="96" t="s">
-        <v>18</v>
-      </c>
-      <c r="AK1" s="98" t="s">
-        <v>19</v>
+        <v>8</v>
+      </c>
+      <c r="AI1" s="93" t="s">
+        <v>28</v>
+      </c>
+      <c r="AJ1" s="95" t="s">
+        <v>29</v>
+      </c>
+      <c r="AK1" s="97" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="85"/>
-      <c r="B2" s="85"/>
-      <c r="C2" s="86"/>
+      <c r="A2" s="112"/>
+      <c r="B2" s="112"/>
+      <c r="C2" s="113"/>
       <c r="D2" s="11">
         <v>1</v>
       </c>
@@ -13736,17 +13748,17 @@
       <c r="AH2" s="12">
         <v>31</v>
       </c>
-      <c r="AI2" s="95"/>
-      <c r="AJ2" s="97"/>
-      <c r="AK2" s="99"/>
+      <c r="AI2" s="94"/>
+      <c r="AJ2" s="96"/>
+      <c r="AK2" s="98"/>
     </row>
     <row r="3" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="100" t="s">
+      <c r="A3" s="99" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="100"/>
+      <c r="C3" s="57" t="s">
         <v>0</v>
-      </c>
-      <c r="B3" s="101"/>
-      <c r="C3" s="57" t="s">
-        <v>1</v>
       </c>
       <c r="D3" s="14"/>
       <c r="E3" s="15"/>
@@ -13785,7 +13797,7 @@
       <c r="AF3" s="15"/>
       <c r="AG3" s="17"/>
       <c r="AH3" s="15"/>
-      <c r="AI3" s="104">
+      <c r="AI3" s="103">
         <f>(AJ3+AJ4)/31</f>
         <v>78.064516129032256</v>
       </c>
@@ -13793,15 +13805,15 @@
         <f>SUM(D3:AH3)</f>
         <v>2244</v>
       </c>
-      <c r="AK3" s="106">
+      <c r="AK3" s="105">
         <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="102"/>
-      <c r="B4" s="103"/>
+      <c r="A4" s="101"/>
+      <c r="B4" s="102"/>
       <c r="C4" s="58" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="D4" s="18"/>
       <c r="E4" s="18"/>
@@ -13856,22 +13868,22 @@
         <v>15</v>
       </c>
       <c r="AH4" s="18"/>
-      <c r="AI4" s="105"/>
+      <c r="AI4" s="104"/>
       <c r="AJ4" s="48">
         <f>SUM(D4:AH4)</f>
         <v>176</v>
       </c>
-      <c r="AK4" s="107"/>
+      <c r="AK4" s="106"/>
     </row>
     <row r="5" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="87" t="s">
-        <v>2</v>
-      </c>
-      <c r="B5" s="90" t="s">
-        <v>3</v>
+      <c r="A5" s="114" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="117" t="s">
+        <v>14</v>
       </c>
       <c r="C5" s="59" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="D5" s="21"/>
       <c r="E5" s="2"/>
@@ -13938,10 +13950,10 @@
       </c>
     </row>
     <row r="6" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="88"/>
-      <c r="B6" s="90"/>
+      <c r="A6" s="115"/>
+      <c r="B6" s="117"/>
       <c r="C6" s="60" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="4"/>
@@ -14022,10 +14034,10 @@
       </c>
     </row>
     <row r="7" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="88"/>
-      <c r="B7" s="90"/>
+      <c r="A7" s="115"/>
+      <c r="B7" s="117"/>
       <c r="C7" s="60" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D7" s="25"/>
       <c r="E7" s="4"/>
@@ -14074,10 +14086,10 @@
       </c>
     </row>
     <row r="8" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="88"/>
-      <c r="B8" s="90"/>
+      <c r="A8" s="115"/>
+      <c r="B8" s="117"/>
       <c r="C8" s="61" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D8" s="38"/>
       <c r="E8" s="39">
@@ -14128,10 +14140,10 @@
       </c>
     </row>
     <row r="9" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="88"/>
-      <c r="B9" s="90"/>
+      <c r="A9" s="115"/>
+      <c r="B9" s="117"/>
       <c r="C9" s="59" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D9" s="21"/>
       <c r="E9" s="2"/>
@@ -14180,10 +14192,10 @@
       </c>
     </row>
     <row r="10" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="88"/>
-      <c r="B10" s="90"/>
+      <c r="A10" s="115"/>
+      <c r="B10" s="117"/>
       <c r="C10" s="60" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="4"/>
@@ -14230,10 +14242,10 @@
       </c>
     </row>
     <row r="11" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="88"/>
-      <c r="B11" s="90"/>
+      <c r="A11" s="115"/>
+      <c r="B11" s="117"/>
       <c r="C11" s="60" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="D11" s="21"/>
       <c r="E11" s="2"/>
@@ -14286,12 +14298,12 @@
       </c>
     </row>
     <row r="12" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="88"/>
-      <c r="B12" s="91" t="s">
-        <v>4</v>
+      <c r="A12" s="115"/>
+      <c r="B12" s="121" t="s">
+        <v>21</v>
       </c>
       <c r="C12" s="62" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D12" s="6"/>
       <c r="E12" s="6"/>
@@ -14364,10 +14376,10 @@
       </c>
     </row>
     <row r="13" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="88"/>
-      <c r="B13" s="92"/>
+      <c r="A13" s="115"/>
+      <c r="B13" s="122"/>
       <c r="C13" s="62" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D13" s="28"/>
       <c r="E13" s="8"/>
@@ -14420,10 +14432,10 @@
       </c>
     </row>
     <row r="14" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="88"/>
-      <c r="B14" s="92"/>
+      <c r="A14" s="115"/>
+      <c r="B14" s="122"/>
       <c r="C14" s="56" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D14" s="6"/>
       <c r="E14" s="6"/>
@@ -14472,10 +14484,10 @@
       </c>
     </row>
     <row r="15" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="88"/>
-      <c r="B15" s="93"/>
+      <c r="A15" s="115"/>
+      <c r="B15" s="123"/>
       <c r="C15" s="62" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="D15" s="51"/>
       <c r="E15" s="51"/>
@@ -14534,56 +14546,56 @@
       </c>
     </row>
     <row r="16" spans="1:37" ht="18.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="89"/>
-      <c r="B16" s="80" t="s">
-        <v>10</v>
-      </c>
-      <c r="C16" s="81"/>
-      <c r="D16" s="80">
+      <c r="A16" s="116"/>
+      <c r="B16" s="107" t="s">
+        <v>24</v>
+      </c>
+      <c r="C16" s="108"/>
+      <c r="D16" s="107">
         <f>SUM(D5:E15)+531</f>
         <v>534</v>
       </c>
-      <c r="E16" s="82"/>
-      <c r="F16" s="80">
+      <c r="E16" s="109"/>
+      <c r="F16" s="107">
         <f>SUM(F5:L15)</f>
         <v>465</v>
       </c>
-      <c r="G16" s="81"/>
-      <c r="H16" s="81"/>
-      <c r="I16" s="81"/>
-      <c r="J16" s="81"/>
-      <c r="K16" s="81"/>
-      <c r="L16" s="82"/>
-      <c r="M16" s="80">
+      <c r="G16" s="108"/>
+      <c r="H16" s="108"/>
+      <c r="I16" s="108"/>
+      <c r="J16" s="108"/>
+      <c r="K16" s="108"/>
+      <c r="L16" s="109"/>
+      <c r="M16" s="107">
         <f>SUM(M5:S15)</f>
         <v>1011</v>
       </c>
-      <c r="N16" s="81"/>
-      <c r="O16" s="81"/>
-      <c r="P16" s="81"/>
-      <c r="Q16" s="81"/>
-      <c r="R16" s="81"/>
-      <c r="S16" s="82"/>
-      <c r="T16" s="80">
+      <c r="N16" s="108"/>
+      <c r="O16" s="108"/>
+      <c r="P16" s="108"/>
+      <c r="Q16" s="108"/>
+      <c r="R16" s="108"/>
+      <c r="S16" s="109"/>
+      <c r="T16" s="107">
         <f>SUM(T5:Z15)</f>
         <v>174</v>
       </c>
-      <c r="U16" s="81"/>
-      <c r="V16" s="81"/>
-      <c r="W16" s="81"/>
-      <c r="X16" s="81"/>
-      <c r="Y16" s="81"/>
-      <c r="Z16" s="82"/>
-      <c r="AA16" s="80">
+      <c r="U16" s="108"/>
+      <c r="V16" s="108"/>
+      <c r="W16" s="108"/>
+      <c r="X16" s="108"/>
+      <c r="Y16" s="108"/>
+      <c r="Z16" s="109"/>
+      <c r="AA16" s="107">
         <f>SUM(AA5:AG15)</f>
         <v>639</v>
       </c>
-      <c r="AB16" s="81"/>
-      <c r="AC16" s="81"/>
-      <c r="AD16" s="81"/>
-      <c r="AE16" s="81"/>
-      <c r="AF16" s="81"/>
-      <c r="AG16" s="82"/>
+      <c r="AB16" s="108"/>
+      <c r="AC16" s="108"/>
+      <c r="AD16" s="108"/>
+      <c r="AE16" s="108"/>
+      <c r="AF16" s="108"/>
+      <c r="AG16" s="109"/>
       <c r="AH16" s="75"/>
       <c r="AI16" s="53">
         <f t="shared" si="0"/>
@@ -14599,146 +14611,153 @@
       </c>
     </row>
     <row r="17" spans="1:37" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="114" t="s">
+      <c r="A17" s="86" t="s">
+        <v>25</v>
+      </c>
+      <c r="B17" s="86"/>
+      <c r="C17" s="87"/>
+      <c r="D17" s="88">
+        <v>2930</v>
+      </c>
+      <c r="E17" s="89"/>
+      <c r="F17" s="89"/>
+      <c r="G17" s="89"/>
+      <c r="H17" s="89"/>
+      <c r="I17" s="89"/>
+      <c r="J17" s="89"/>
+      <c r="K17" s="89"/>
+      <c r="L17" s="89"/>
+      <c r="M17" s="89"/>
+      <c r="N17" s="89"/>
+      <c r="O17" s="89"/>
+      <c r="P17" s="89"/>
+      <c r="Q17" s="89"/>
+      <c r="R17" s="89"/>
+      <c r="S17" s="89"/>
+      <c r="T17" s="89"/>
+      <c r="U17" s="89"/>
+      <c r="V17" s="89"/>
+      <c r="W17" s="89"/>
+      <c r="X17" s="89"/>
+      <c r="Y17" s="89"/>
+      <c r="Z17" s="89"/>
+      <c r="AA17" s="89"/>
+      <c r="AB17" s="89"/>
+      <c r="AC17" s="89"/>
+      <c r="AD17" s="89"/>
+      <c r="AE17" s="89"/>
+      <c r="AF17" s="89"/>
+      <c r="AG17" s="89"/>
+      <c r="AH17" s="89"/>
+      <c r="AI17" s="90"/>
+      <c r="AJ17" s="91"/>
+      <c r="AK17" s="74"/>
+    </row>
+    <row r="18" spans="1:37" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="81" t="s">
         <v>26</v>
       </c>
-      <c r="B17" s="114"/>
-      <c r="C17" s="115"/>
-      <c r="D17" s="116">
-        <v>2930</v>
-      </c>
-      <c r="E17" s="117"/>
-      <c r="F17" s="117"/>
-      <c r="G17" s="117"/>
-      <c r="H17" s="117"/>
-      <c r="I17" s="117"/>
-      <c r="J17" s="117"/>
-      <c r="K17" s="117"/>
-      <c r="L17" s="117"/>
-      <c r="M17" s="117"/>
-      <c r="N17" s="117"/>
-      <c r="O17" s="117"/>
-      <c r="P17" s="117"/>
-      <c r="Q17" s="117"/>
-      <c r="R17" s="117"/>
-      <c r="S17" s="117"/>
-      <c r="T17" s="117"/>
-      <c r="U17" s="117"/>
-      <c r="V17" s="117"/>
-      <c r="W17" s="117"/>
-      <c r="X17" s="117"/>
-      <c r="Y17" s="117"/>
-      <c r="Z17" s="117"/>
-      <c r="AA17" s="117"/>
-      <c r="AB17" s="117"/>
-      <c r="AC17" s="117"/>
-      <c r="AD17" s="117"/>
-      <c r="AE17" s="117"/>
-      <c r="AF17" s="117"/>
-      <c r="AG17" s="117"/>
-      <c r="AH17" s="117"/>
-      <c r="AI17" s="118"/>
-      <c r="AJ17" s="119"/>
-      <c r="AK17" s="74"/>
-    </row>
-    <row r="18" spans="1:37" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="109" t="s">
-        <v>20</v>
-      </c>
-      <c r="B18" s="109"/>
-      <c r="C18" s="110"/>
-      <c r="D18" s="120">
+      <c r="B18" s="81"/>
+      <c r="C18" s="82"/>
+      <c r="D18" s="92">
         <f>((AJ3+AJ4+D17)-AJ16)-D17</f>
         <v>48</v>
       </c>
-      <c r="E18" s="118"/>
-      <c r="F18" s="118"/>
-      <c r="G18" s="118"/>
-      <c r="H18" s="118"/>
-      <c r="I18" s="118"/>
-      <c r="J18" s="118"/>
-      <c r="K18" s="118"/>
-      <c r="L18" s="118"/>
-      <c r="M18" s="118"/>
-      <c r="N18" s="118"/>
-      <c r="O18" s="118"/>
-      <c r="P18" s="118"/>
-      <c r="Q18" s="118"/>
-      <c r="R18" s="118"/>
-      <c r="S18" s="118"/>
-      <c r="T18" s="118"/>
-      <c r="U18" s="118"/>
-      <c r="V18" s="118"/>
-      <c r="W18" s="118"/>
-      <c r="X18" s="118"/>
-      <c r="Y18" s="118"/>
-      <c r="Z18" s="118"/>
-      <c r="AA18" s="118"/>
-      <c r="AB18" s="118"/>
-      <c r="AC18" s="118"/>
-      <c r="AD18" s="118"/>
-      <c r="AE18" s="118"/>
-      <c r="AF18" s="118"/>
-      <c r="AG18" s="118"/>
-      <c r="AH18" s="118"/>
-      <c r="AI18" s="118"/>
-      <c r="AJ18" s="119"/>
+      <c r="E18" s="90"/>
+      <c r="F18" s="90"/>
+      <c r="G18" s="90"/>
+      <c r="H18" s="90"/>
+      <c r="I18" s="90"/>
+      <c r="J18" s="90"/>
+      <c r="K18" s="90"/>
+      <c r="L18" s="90"/>
+      <c r="M18" s="90"/>
+      <c r="N18" s="90"/>
+      <c r="O18" s="90"/>
+      <c r="P18" s="90"/>
+      <c r="Q18" s="90"/>
+      <c r="R18" s="90"/>
+      <c r="S18" s="90"/>
+      <c r="T18" s="90"/>
+      <c r="U18" s="90"/>
+      <c r="V18" s="90"/>
+      <c r="W18" s="90"/>
+      <c r="X18" s="90"/>
+      <c r="Y18" s="90"/>
+      <c r="Z18" s="90"/>
+      <c r="AA18" s="90"/>
+      <c r="AB18" s="90"/>
+      <c r="AC18" s="90"/>
+      <c r="AD18" s="90"/>
+      <c r="AE18" s="90"/>
+      <c r="AF18" s="90"/>
+      <c r="AG18" s="90"/>
+      <c r="AH18" s="90"/>
+      <c r="AI18" s="90"/>
+      <c r="AJ18" s="91"/>
       <c r="AK18" s="31">
         <f>((AJ3+AJ4-AJ16)/(AJ3+AJ4))*100</f>
         <v>1.9834710743801653</v>
       </c>
     </row>
     <row r="19" spans="1:37" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="108" t="s">
+      <c r="A19" s="80" t="s">
         <v>27</v>
       </c>
-      <c r="B19" s="109"/>
-      <c r="C19" s="110"/>
-      <c r="D19" s="111">
+      <c r="B19" s="81"/>
+      <c r="C19" s="82"/>
+      <c r="D19" s="83">
         <f>(AJ3+AJ4+D17)-AJ16</f>
         <v>2978</v>
       </c>
-      <c r="E19" s="112"/>
-      <c r="F19" s="112"/>
-      <c r="G19" s="112"/>
-      <c r="H19" s="112"/>
-      <c r="I19" s="112"/>
-      <c r="J19" s="112"/>
-      <c r="K19" s="112"/>
-      <c r="L19" s="112"/>
-      <c r="M19" s="112"/>
-      <c r="N19" s="112"/>
-      <c r="O19" s="112"/>
-      <c r="P19" s="112"/>
-      <c r="Q19" s="112"/>
-      <c r="R19" s="112"/>
-      <c r="S19" s="112"/>
-      <c r="T19" s="112"/>
-      <c r="U19" s="112"/>
-      <c r="V19" s="112"/>
-      <c r="W19" s="112"/>
-      <c r="X19" s="112"/>
-      <c r="Y19" s="112"/>
-      <c r="Z19" s="112"/>
-      <c r="AA19" s="112"/>
-      <c r="AB19" s="112"/>
-      <c r="AC19" s="112"/>
-      <c r="AD19" s="112"/>
-      <c r="AE19" s="112"/>
-      <c r="AF19" s="112"/>
-      <c r="AG19" s="112"/>
-      <c r="AH19" s="112"/>
-      <c r="AI19" s="112"/>
-      <c r="AJ19" s="113"/>
+      <c r="E19" s="84"/>
+      <c r="F19" s="84"/>
+      <c r="G19" s="84"/>
+      <c r="H19" s="84"/>
+      <c r="I19" s="84"/>
+      <c r="J19" s="84"/>
+      <c r="K19" s="84"/>
+      <c r="L19" s="84"/>
+      <c r="M19" s="84"/>
+      <c r="N19" s="84"/>
+      <c r="O19" s="84"/>
+      <c r="P19" s="84"/>
+      <c r="Q19" s="84"/>
+      <c r="R19" s="84"/>
+      <c r="S19" s="84"/>
+      <c r="T19" s="84"/>
+      <c r="U19" s="84"/>
+      <c r="V19" s="84"/>
+      <c r="W19" s="84"/>
+      <c r="X19" s="84"/>
+      <c r="Y19" s="84"/>
+      <c r="Z19" s="84"/>
+      <c r="AA19" s="84"/>
+      <c r="AB19" s="84"/>
+      <c r="AC19" s="84"/>
+      <c r="AD19" s="84"/>
+      <c r="AE19" s="84"/>
+      <c r="AF19" s="84"/>
+      <c r="AG19" s="84"/>
+      <c r="AH19" s="84"/>
+      <c r="AI19" s="84"/>
+      <c r="AJ19" s="85"/>
       <c r="AK19" s="54"/>
     </row>
     <row r="24" spans="1:37" x14ac:dyDescent="0.3">
       <c r="S24" s="1" t="s">
-        <v>29</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="A1:C2"/>
+    <mergeCell ref="AI1:AI2"/>
+    <mergeCell ref="AJ1:AJ2"/>
+    <mergeCell ref="AK1:AK2"/>
+    <mergeCell ref="A3:B4"/>
+    <mergeCell ref="AI3:AI4"/>
+    <mergeCell ref="AK3:AK4"/>
     <mergeCell ref="A19:C19"/>
     <mergeCell ref="D19:AJ19"/>
     <mergeCell ref="D16:E16"/>
@@ -14754,13 +14773,6 @@
     <mergeCell ref="B5:B11"/>
     <mergeCell ref="B12:B15"/>
     <mergeCell ref="B16:C16"/>
-    <mergeCell ref="A1:C2"/>
-    <mergeCell ref="AI1:AI2"/>
-    <mergeCell ref="AJ1:AJ2"/>
-    <mergeCell ref="AK1:AK2"/>
-    <mergeCell ref="A3:B4"/>
-    <mergeCell ref="AI3:AI4"/>
-    <mergeCell ref="AK3:AK4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -14776,121 +14788,121 @@
     <col min="2" max="2" width="6.140625" style="1" customWidth="1"/>
     <col min="3" max="3" width="19.28515625" style="1" customWidth="1"/>
     <col min="4" max="34" width="5.7109375" style="1" customWidth="1"/>
-    <col min="35" max="35" width="8.85546875" style="1" customWidth="1"/>
+    <col min="35" max="35" width="12" style="1" customWidth="1"/>
     <col min="36" max="36" width="10.140625" style="1" customWidth="1"/>
     <col min="37" max="37" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="83"/>
-      <c r="B1" s="83"/>
-      <c r="C1" s="84"/>
+      <c r="A1" s="110"/>
+      <c r="B1" s="110"/>
+      <c r="C1" s="111"/>
       <c r="D1" s="36" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E1" s="37" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="F1" s="36" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="G1" s="36" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="H1" s="36" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="I1" s="37" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="J1" s="55" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="K1" s="36" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="L1" s="37" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="M1" s="36" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="N1" s="36" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="O1" s="36" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="P1" s="37" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="Q1" s="55" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="R1" s="36" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="S1" s="37" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="T1" s="36" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="U1" s="36" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="V1" s="36" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="W1" s="37" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="X1" s="55" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="Y1" s="36" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="Z1" s="37" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="AA1" s="36" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="AB1" s="36" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="AC1" s="36" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="AD1" s="37" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="AE1" s="55" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="AF1" s="36" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="AG1" s="37" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="AH1" s="55"/>
-      <c r="AI1" s="94" t="s">
-        <v>23</v>
-      </c>
-      <c r="AJ1" s="96" t="s">
-        <v>18</v>
-      </c>
-      <c r="AK1" s="98" t="s">
-        <v>19</v>
+      <c r="AI1" s="93" t="s">
+        <v>28</v>
+      </c>
+      <c r="AJ1" s="95" t="s">
+        <v>29</v>
+      </c>
+      <c r="AK1" s="97" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="85"/>
-      <c r="B2" s="85"/>
-      <c r="C2" s="86"/>
+      <c r="A2" s="112"/>
+      <c r="B2" s="112"/>
+      <c r="C2" s="113"/>
       <c r="D2" s="11">
         <v>1</v>
       </c>
@@ -14984,17 +14996,17 @@
       <c r="AH2" s="12">
         <v>31</v>
       </c>
-      <c r="AI2" s="95"/>
-      <c r="AJ2" s="97"/>
-      <c r="AK2" s="99"/>
+      <c r="AI2" s="94"/>
+      <c r="AJ2" s="96"/>
+      <c r="AK2" s="98"/>
     </row>
     <row r="3" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="100" t="s">
+      <c r="A3" s="99" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="100"/>
+      <c r="C3" s="57" t="s">
         <v>0</v>
-      </c>
-      <c r="B3" s="101"/>
-      <c r="C3" s="57" t="s">
-        <v>1</v>
       </c>
       <c r="D3" s="14"/>
       <c r="E3" s="15"/>
@@ -15033,7 +15045,7 @@
       <c r="AF3" s="15"/>
       <c r="AG3" s="17"/>
       <c r="AH3" s="15"/>
-      <c r="AI3" s="104">
+      <c r="AI3" s="103">
         <f>(AJ3+AJ4)/31</f>
         <v>97.225806451612897</v>
       </c>
@@ -15041,15 +15053,15 @@
         <f>SUM(D3:AH3)</f>
         <v>2383</v>
       </c>
-      <c r="AK3" s="106">
+      <c r="AK3" s="105">
         <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="102"/>
-      <c r="B4" s="103"/>
+      <c r="A4" s="101"/>
+      <c r="B4" s="102"/>
       <c r="C4" s="58" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="D4" s="18"/>
       <c r="E4" s="18"/>
@@ -15096,22 +15108,22 @@
       <c r="AF4" s="18"/>
       <c r="AG4" s="19"/>
       <c r="AH4" s="18"/>
-      <c r="AI4" s="105"/>
+      <c r="AI4" s="104"/>
       <c r="AJ4" s="48">
         <f>SUM(D4:AH4)</f>
         <v>631</v>
       </c>
-      <c r="AK4" s="107"/>
+      <c r="AK4" s="106"/>
     </row>
     <row r="5" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="87" t="s">
-        <v>2</v>
-      </c>
-      <c r="B5" s="90" t="s">
-        <v>3</v>
+      <c r="A5" s="114" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="117" t="s">
+        <v>14</v>
       </c>
       <c r="C5" s="59" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="D5" s="21"/>
       <c r="E5" s="2">
@@ -15184,10 +15196,10 @@
       </c>
     </row>
     <row r="6" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="88"/>
-      <c r="B6" s="90"/>
+      <c r="A6" s="115"/>
+      <c r="B6" s="117"/>
       <c r="C6" s="60" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="4">
@@ -15278,10 +15290,10 @@
       </c>
     </row>
     <row r="7" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="88"/>
-      <c r="B7" s="90"/>
+      <c r="A7" s="115"/>
+      <c r="B7" s="117"/>
       <c r="C7" s="60" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D7" s="25"/>
       <c r="E7" s="4"/>
@@ -15330,10 +15342,10 @@
       </c>
     </row>
     <row r="8" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="88"/>
-      <c r="B8" s="90"/>
+      <c r="A8" s="115"/>
+      <c r="B8" s="117"/>
       <c r="C8" s="61" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D8" s="38"/>
       <c r="E8" s="39"/>
@@ -15384,10 +15396,10 @@
       </c>
     </row>
     <row r="9" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="88"/>
-      <c r="B9" s="90"/>
+      <c r="A9" s="115"/>
+      <c r="B9" s="117"/>
       <c r="C9" s="59" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D9" s="21"/>
       <c r="E9" s="2"/>
@@ -15438,10 +15450,10 @@
       </c>
     </row>
     <row r="10" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="88"/>
-      <c r="B10" s="90"/>
+      <c r="A10" s="115"/>
+      <c r="B10" s="117"/>
       <c r="C10" s="60" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="4"/>
@@ -15490,10 +15502,10 @@
       </c>
     </row>
     <row r="11" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="88"/>
-      <c r="B11" s="90"/>
+      <c r="A11" s="115"/>
+      <c r="B11" s="117"/>
       <c r="C11" s="60" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="D11" s="21"/>
       <c r="E11" s="2"/>
@@ -15544,12 +15556,12 @@
       </c>
     </row>
     <row r="12" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="88"/>
-      <c r="B12" s="91" t="s">
-        <v>4</v>
+      <c r="A12" s="115"/>
+      <c r="B12" s="121" t="s">
+        <v>21</v>
       </c>
       <c r="C12" s="62" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D12" s="6">
         <v>50</v>
@@ -15610,10 +15622,10 @@
       </c>
     </row>
     <row r="13" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="88"/>
-      <c r="B13" s="92"/>
+      <c r="A13" s="115"/>
+      <c r="B13" s="122"/>
       <c r="C13" s="62" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D13" s="28"/>
       <c r="E13" s="8">
@@ -15664,10 +15676,10 @@
       </c>
     </row>
     <row r="14" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="88"/>
-      <c r="B14" s="92"/>
+      <c r="A14" s="115"/>
+      <c r="B14" s="122"/>
       <c r="C14" s="56" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D14" s="6"/>
       <c r="E14" s="6"/>
@@ -15722,10 +15734,10 @@
       </c>
     </row>
     <row r="15" spans="1:37" ht="18.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="88"/>
-      <c r="B15" s="93"/>
+      <c r="A15" s="115"/>
+      <c r="B15" s="123"/>
       <c r="C15" s="62" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="D15" s="51"/>
       <c r="E15" s="51">
@@ -15784,56 +15796,56 @@
       </c>
     </row>
     <row r="16" spans="1:37" ht="18.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="89"/>
-      <c r="B16" s="80" t="s">
-        <v>10</v>
-      </c>
-      <c r="C16" s="81"/>
-      <c r="D16" s="80">
+      <c r="A16" s="116"/>
+      <c r="B16" s="107" t="s">
+        <v>24</v>
+      </c>
+      <c r="C16" s="108"/>
+      <c r="D16" s="107">
         <f>SUM(D5:I15)+80</f>
         <v>884</v>
       </c>
-      <c r="E16" s="81"/>
-      <c r="F16" s="81"/>
-      <c r="G16" s="81"/>
-      <c r="H16" s="81"/>
-      <c r="I16" s="82"/>
-      <c r="J16" s="80">
+      <c r="E16" s="108"/>
+      <c r="F16" s="108"/>
+      <c r="G16" s="108"/>
+      <c r="H16" s="108"/>
+      <c r="I16" s="109"/>
+      <c r="J16" s="107">
         <f>SUM(J5:P15)</f>
         <v>434</v>
       </c>
-      <c r="K16" s="81"/>
-      <c r="L16" s="81"/>
-      <c r="M16" s="81"/>
-      <c r="N16" s="81"/>
-      <c r="O16" s="81"/>
-      <c r="P16" s="82"/>
-      <c r="Q16" s="80">
+      <c r="K16" s="108"/>
+      <c r="L16" s="108"/>
+      <c r="M16" s="108"/>
+      <c r="N16" s="108"/>
+      <c r="O16" s="108"/>
+      <c r="P16" s="109"/>
+      <c r="Q16" s="107">
         <f>SUM(Q5:W15)</f>
         <v>555</v>
       </c>
-      <c r="R16" s="81"/>
-      <c r="S16" s="81"/>
-      <c r="T16" s="81"/>
-      <c r="U16" s="81"/>
-      <c r="V16" s="81"/>
-      <c r="W16" s="82"/>
-      <c r="X16" s="80">
+      <c r="R16" s="108"/>
+      <c r="S16" s="108"/>
+      <c r="T16" s="108"/>
+      <c r="U16" s="108"/>
+      <c r="V16" s="108"/>
+      <c r="W16" s="109"/>
+      <c r="X16" s="107">
         <f>SUM(X5:AD15)</f>
         <v>754</v>
       </c>
-      <c r="Y16" s="81"/>
-      <c r="Z16" s="81"/>
-      <c r="AA16" s="81"/>
-      <c r="AB16" s="81"/>
-      <c r="AC16" s="81"/>
-      <c r="AD16" s="82"/>
-      <c r="AE16" s="80">
+      <c r="Y16" s="108"/>
+      <c r="Z16" s="108"/>
+      <c r="AA16" s="108"/>
+      <c r="AB16" s="108"/>
+      <c r="AC16" s="108"/>
+      <c r="AD16" s="109"/>
+      <c r="AE16" s="107">
         <f>SUM(AE5:AG15)</f>
         <v>387</v>
       </c>
-      <c r="AF16" s="81"/>
-      <c r="AG16" s="82"/>
+      <c r="AF16" s="108"/>
+      <c r="AG16" s="109"/>
       <c r="AH16" s="66"/>
       <c r="AI16" s="53">
         <f t="shared" si="0"/>
@@ -15849,153 +15861,146 @@
       </c>
     </row>
     <row r="17" spans="1:37" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="114" t="s">
+      <c r="A17" s="86" t="s">
+        <v>25</v>
+      </c>
+      <c r="B17" s="86"/>
+      <c r="C17" s="87"/>
+      <c r="D17" s="88">
+        <v>2978</v>
+      </c>
+      <c r="E17" s="89"/>
+      <c r="F17" s="89"/>
+      <c r="G17" s="89"/>
+      <c r="H17" s="89"/>
+      <c r="I17" s="89"/>
+      <c r="J17" s="89"/>
+      <c r="K17" s="89"/>
+      <c r="L17" s="89"/>
+      <c r="M17" s="89"/>
+      <c r="N17" s="89"/>
+      <c r="O17" s="89"/>
+      <c r="P17" s="89"/>
+      <c r="Q17" s="89"/>
+      <c r="R17" s="89"/>
+      <c r="S17" s="89"/>
+      <c r="T17" s="89"/>
+      <c r="U17" s="89"/>
+      <c r="V17" s="89"/>
+      <c r="W17" s="89"/>
+      <c r="X17" s="89"/>
+      <c r="Y17" s="89"/>
+      <c r="Z17" s="89"/>
+      <c r="AA17" s="89"/>
+      <c r="AB17" s="89"/>
+      <c r="AC17" s="89"/>
+      <c r="AD17" s="89"/>
+      <c r="AE17" s="89"/>
+      <c r="AF17" s="89"/>
+      <c r="AG17" s="89"/>
+      <c r="AH17" s="89"/>
+      <c r="AI17" s="90"/>
+      <c r="AJ17" s="91"/>
+      <c r="AK17" s="76"/>
+    </row>
+    <row r="18" spans="1:37" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="81" t="s">
         <v>26</v>
       </c>
-      <c r="B17" s="114"/>
-      <c r="C17" s="115"/>
-      <c r="D17" s="116">
-        <v>2978</v>
-      </c>
-      <c r="E17" s="117"/>
-      <c r="F17" s="117"/>
-      <c r="G17" s="117"/>
-      <c r="H17" s="117"/>
-      <c r="I17" s="117"/>
-      <c r="J17" s="117"/>
-      <c r="K17" s="117"/>
-      <c r="L17" s="117"/>
-      <c r="M17" s="117"/>
-      <c r="N17" s="117"/>
-      <c r="O17" s="117"/>
-      <c r="P17" s="117"/>
-      <c r="Q17" s="117"/>
-      <c r="R17" s="117"/>
-      <c r="S17" s="117"/>
-      <c r="T17" s="117"/>
-      <c r="U17" s="117"/>
-      <c r="V17" s="117"/>
-      <c r="W17" s="117"/>
-      <c r="X17" s="117"/>
-      <c r="Y17" s="117"/>
-      <c r="Z17" s="117"/>
-      <c r="AA17" s="117"/>
-      <c r="AB17" s="117"/>
-      <c r="AC17" s="117"/>
-      <c r="AD17" s="117"/>
-      <c r="AE17" s="117"/>
-      <c r="AF17" s="117"/>
-      <c r="AG17" s="117"/>
-      <c r="AH17" s="117"/>
-      <c r="AI17" s="118"/>
-      <c r="AJ17" s="119"/>
-      <c r="AK17" s="76"/>
-    </row>
-    <row r="18" spans="1:37" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="109" t="s">
-        <v>20</v>
-      </c>
-      <c r="B18" s="109"/>
-      <c r="C18" s="110"/>
-      <c r="D18" s="120">
+      <c r="B18" s="81"/>
+      <c r="C18" s="82"/>
+      <c r="D18" s="92">
         <f>((AJ3+AJ4+D17)-AJ16)-D17</f>
         <v>80</v>
       </c>
-      <c r="E18" s="118"/>
-      <c r="F18" s="118"/>
-      <c r="G18" s="118"/>
-      <c r="H18" s="118"/>
-      <c r="I18" s="118"/>
-      <c r="J18" s="118"/>
-      <c r="K18" s="118"/>
-      <c r="L18" s="118"/>
-      <c r="M18" s="118"/>
-      <c r="N18" s="118"/>
-      <c r="O18" s="118"/>
-      <c r="P18" s="118"/>
-      <c r="Q18" s="118"/>
-      <c r="R18" s="118"/>
-      <c r="S18" s="118"/>
-      <c r="T18" s="118"/>
-      <c r="U18" s="118"/>
-      <c r="V18" s="118"/>
-      <c r="W18" s="118"/>
-      <c r="X18" s="118"/>
-      <c r="Y18" s="118"/>
-      <c r="Z18" s="118"/>
-      <c r="AA18" s="118"/>
-      <c r="AB18" s="118"/>
-      <c r="AC18" s="118"/>
-      <c r="AD18" s="118"/>
-      <c r="AE18" s="118"/>
-      <c r="AF18" s="118"/>
-      <c r="AG18" s="118"/>
-      <c r="AH18" s="118"/>
-      <c r="AI18" s="118"/>
-      <c r="AJ18" s="119"/>
+      <c r="E18" s="90"/>
+      <c r="F18" s="90"/>
+      <c r="G18" s="90"/>
+      <c r="H18" s="90"/>
+      <c r="I18" s="90"/>
+      <c r="J18" s="90"/>
+      <c r="K18" s="90"/>
+      <c r="L18" s="90"/>
+      <c r="M18" s="90"/>
+      <c r="N18" s="90"/>
+      <c r="O18" s="90"/>
+      <c r="P18" s="90"/>
+      <c r="Q18" s="90"/>
+      <c r="R18" s="90"/>
+      <c r="S18" s="90"/>
+      <c r="T18" s="90"/>
+      <c r="U18" s="90"/>
+      <c r="V18" s="90"/>
+      <c r="W18" s="90"/>
+      <c r="X18" s="90"/>
+      <c r="Y18" s="90"/>
+      <c r="Z18" s="90"/>
+      <c r="AA18" s="90"/>
+      <c r="AB18" s="90"/>
+      <c r="AC18" s="90"/>
+      <c r="AD18" s="90"/>
+      <c r="AE18" s="90"/>
+      <c r="AF18" s="90"/>
+      <c r="AG18" s="90"/>
+      <c r="AH18" s="90"/>
+      <c r="AI18" s="90"/>
+      <c r="AJ18" s="91"/>
       <c r="AK18" s="31">
         <f>((AJ3+AJ4-AJ16)/(AJ3+AJ4))*100</f>
         <v>2.6542800265428004</v>
       </c>
     </row>
     <row r="19" spans="1:37" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="108" t="s">
+      <c r="A19" s="80" t="s">
         <v>27</v>
       </c>
-      <c r="B19" s="109"/>
-      <c r="C19" s="110"/>
-      <c r="D19" s="111">
+      <c r="B19" s="81"/>
+      <c r="C19" s="82"/>
+      <c r="D19" s="83">
         <f>(AJ3+AJ4+D17)-AJ16</f>
         <v>3058</v>
       </c>
-      <c r="E19" s="112"/>
-      <c r="F19" s="112"/>
-      <c r="G19" s="112"/>
-      <c r="H19" s="112"/>
-      <c r="I19" s="112"/>
-      <c r="J19" s="112"/>
-      <c r="K19" s="112"/>
-      <c r="L19" s="112"/>
-      <c r="M19" s="112"/>
-      <c r="N19" s="112"/>
-      <c r="O19" s="112"/>
-      <c r="P19" s="112"/>
-      <c r="Q19" s="112"/>
-      <c r="R19" s="112"/>
-      <c r="S19" s="112"/>
-      <c r="T19" s="112"/>
-      <c r="U19" s="112"/>
-      <c r="V19" s="112"/>
-      <c r="W19" s="112"/>
-      <c r="X19" s="112"/>
-      <c r="Y19" s="112"/>
-      <c r="Z19" s="112"/>
-      <c r="AA19" s="112"/>
-      <c r="AB19" s="112"/>
-      <c r="AC19" s="112"/>
-      <c r="AD19" s="112"/>
-      <c r="AE19" s="112"/>
-      <c r="AF19" s="112"/>
-      <c r="AG19" s="112"/>
-      <c r="AH19" s="112"/>
-      <c r="AI19" s="112"/>
-      <c r="AJ19" s="113"/>
+      <c r="E19" s="84"/>
+      <c r="F19" s="84"/>
+      <c r="G19" s="84"/>
+      <c r="H19" s="84"/>
+      <c r="I19" s="84"/>
+      <c r="J19" s="84"/>
+      <c r="K19" s="84"/>
+      <c r="L19" s="84"/>
+      <c r="M19" s="84"/>
+      <c r="N19" s="84"/>
+      <c r="O19" s="84"/>
+      <c r="P19" s="84"/>
+      <c r="Q19" s="84"/>
+      <c r="R19" s="84"/>
+      <c r="S19" s="84"/>
+      <c r="T19" s="84"/>
+      <c r="U19" s="84"/>
+      <c r="V19" s="84"/>
+      <c r="W19" s="84"/>
+      <c r="X19" s="84"/>
+      <c r="Y19" s="84"/>
+      <c r="Z19" s="84"/>
+      <c r="AA19" s="84"/>
+      <c r="AB19" s="84"/>
+      <c r="AC19" s="84"/>
+      <c r="AD19" s="84"/>
+      <c r="AE19" s="84"/>
+      <c r="AF19" s="84"/>
+      <c r="AG19" s="84"/>
+      <c r="AH19" s="84"/>
+      <c r="AI19" s="84"/>
+      <c r="AJ19" s="85"/>
       <c r="AK19" s="54"/>
     </row>
     <row r="24" spans="1:37" x14ac:dyDescent="0.3">
       <c r="S24" s="1" t="s">
-        <v>29</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="A1:C2"/>
-    <mergeCell ref="AI1:AI2"/>
-    <mergeCell ref="AJ1:AJ2"/>
-    <mergeCell ref="AK1:AK2"/>
-    <mergeCell ref="A3:B4"/>
-    <mergeCell ref="AI3:AI4"/>
-    <mergeCell ref="AK3:AK4"/>
     <mergeCell ref="A19:C19"/>
     <mergeCell ref="D19:AJ19"/>
     <mergeCell ref="D16:I16"/>
@@ -16011,6 +16016,13 @@
     <mergeCell ref="B5:B11"/>
     <mergeCell ref="B12:B15"/>
     <mergeCell ref="B16:C16"/>
+    <mergeCell ref="A1:C2"/>
+    <mergeCell ref="AI1:AI2"/>
+    <mergeCell ref="AJ1:AJ2"/>
+    <mergeCell ref="AK1:AK2"/>
+    <mergeCell ref="A3:B4"/>
+    <mergeCell ref="AI3:AI4"/>
+    <mergeCell ref="AK3:AK4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
